--- a/web/descargas/licitaciones.xlsx
+++ b/web/descargas/licitaciones.xlsx
@@ -219,286 +219,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1393093-98-LE26</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONTRATACIÓN DE SERV. DE DESA.SOFTWARE RENDICIONES</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Compras y Licitaciones</t>
-        </is>
-      </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de los Lagos </t>
-        </is>
-      </c>
-      <c r="G2" s="0"/>
-      <c r="H2" s="2">
-        <v>46269.399306</v>
-      </c>
-      <c r="I2" s="2">
-        <v>46286.666667</v>
-      </c>
-      <c r="J2" s="0">
-        <v>3</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LE</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Desarrolladores temporales de software</t>
-        </is>
-      </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 meses</t>
-        </is>
-      </c>
-      <c r="S2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T2" s="4"/>
-      <c r="U2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YESIKA DIAZ</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gestionar de manera sistemática, ordenada y oportuna la información asociada a ingresos, gastos (compras) y remuneraciones por establecimiento educacional (RBD) y por tipo de subvención, facilitando los procesos de control, seguimiento y rendición de cuentas ante la Superintendencia de Educación.</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=vYeS%2fnpeBm%2fuEQcmlyMsnYJwUCxqiS8j3R2dMynTyRK%2bkic%2fhjPNAz6mhiy8GlP86hbodqkAm2IiV8Jz6k4YAEGBQz2t%2bLqiS17Hlh8axsHvDJsD9pzJvLN6s8X1cyShAm7VcYZB%2fqQNfZiJwWPdcXpoWUIOMiLkkKpKkWYbV0GwPYG7KqoavFDvIY2%2bkkAmQGxW3OwuqxgET05XoanIOsqydZZCC5lDw%2bUCq6LzCvSFJQ5PR5f%2bsD5xIe0XyQ%2f%2bOadqas5YbH9xkbxGkBfId0li80ObpeC2yDteyd4GZVvLjJ0IXirWsTnPopumeujE","descargar bases")</f>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1575-15-LE26</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MANTENCION DE EQUIPOS INFORMATICOS</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JUNTA NACIONAL DE JARDINES         INFANTILES</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Junji - VI Región</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Libertador General Bernardo O´Higgins</t>
-        </is>
-      </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rancagua</t>
-        </is>
-      </c>
-      <c r="H3" s="2">
-        <v>46282.520417</v>
-      </c>
-      <c r="I3" s="2">
-        <v>46294.625</v>
-      </c>
-      <c r="J3" s="0">
-        <v>11</v>
-      </c>
-      <c r="K3" s="3">
-        <v>22000000.0</v>
-      </c>
-      <c r="L3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LE</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipos, accesorios y suministros de oficina / Maquinarias, suministros y accesorios de oficina / Multicopistas, fotocopiadoras, fax y multifuncionales</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Fotocopiadoras</t>
-        </is>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 meses</t>
-        </is>
-      </c>
-      <c r="S3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MYRIAM POBLETE</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La Junta Nacional de Jardines Infantiles, en adelante (JUNJI), requiere la “CONTRATO DE SUMINISTRO DE MANTENCION Y REPARACION DE IMPRESORAS, ESCANERS, PLOTTERS, PROYECTORES PARA JARDINES INFANTILES Y OFICINAS PARA JUNJI DE LA REGIÓN DE O´HIGGINS”.</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=wU4MDrgKqWaKDooFSdi3SvTmXasqYfZAqvBwNJ5sWSdexlALTsg6MrDjp7f36OnPeeLtEgfep6bZEIKK%2bqL%2bQkv2OT4B%2bmQ42nAR17TdAZVmqjNXzspzTsLbwBmOEIX%2fKKQwNtjaFTI5gNTvRvpBblLTC6Oh0yXEL%2fs65gV7Xz01tzlIv4z7WlTxe030P8z%2b9QuRRelzjsQXhQIgOTzqgU2f1aPsVH3rIyC9SHhfKc%2f9VWCPgQpC4f6A1DJ7F%2b5YhVmeSGZNGanyCuEZ46ZJs23jw95yOXP001sVIdZEkysj0jphdH%2beJEEWvQX2AKEz","descargar bases")</f>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2667-71-LR26</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARRIENDO SOPORTE Y MANTENCIÓN DE CENTRAL TELEFONICA IP TELEFONOS IP Y PLATAFORMA DE CONTACT CENTER</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE VITACURA</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SECPLA</t>
-        </is>
-      </c>
-      <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vitacura</t>
-        </is>
-      </c>
-      <c r="H4" s="2">
-        <v>46282.54353</v>
-      </c>
-      <c r="I4" s="2">
-        <v>46318.625</v>
-      </c>
-      <c r="J4" s="0">
-        <v>35</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLF</t>
-        </is>
-      </c>
-      <c r="M4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LR</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipos y suministros de defensa, orden público, protección y seguridad / Seguridad, vigilancia y detección / Equipo de vigilancia y detección</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Global · Sistemas de alarma</t>
-        </is>
-      </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48 meses</t>
-        </is>
-      </c>
-      <c r="S4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gonzalo Fuentes Osses</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La presente licitación tiene por objeto dar a conocer los requerimientos administrativos y técnicos para la renovación y modernización del servicio telefónico de la Municipalidad de Vitacura. Para ello, se contempla la contratación, bajo modalidad de arriendo, de una Central Telefónica IP, equipos telefónicos y una plataforma de contact center para todas sus dependencias.
-El servicio deberá incluir la instalación, puesta en marcha, soporte y mantención de la solución, por un período de 48 meses (4 años), de acuerdo con lo establecido en las presentes Bases Técnicas (BT), Bases Administrativas Especiales (BAE) y demás documentos que forman parte del presente proceso licitatorio.</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=ihuqP%2bM0KqCBcoHtJlWiShvDHHKbTRTjyTT45lrPkmzz%2fbZy2w1DyM23VYv30j8xL4KW4qPhrlUaXivls%2fmkF5SxOLp0xizyX%2foYJuPB4fgISe3%2b28Zx6l4EqTnyxyyGAef75QnQqOFr0vEg2GyDPT8Iov3U6AZMr01O%2bX55FpiCN6iC06JHJ1ZqEoPF9i7YilkG2TVCtMUE9gvRHvBRmAwOsvxXJJ0cwuUcN4XnMw91ZklxVzZnxjEZDTNOLtTIswBzxwFWUalIs0t0A%2fz7YsVwMGjw41c2SmdNQfI2UvQ9tDQuxIQ57KiWgNed0B0Y","descargar bases")</f>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W4"/>
+  <autoFilter ref="A1:W1"/>
 </worksheet>
 </file>
 
@@ -690,7 +412,7 @@
         <v>46286.625</v>
       </c>
       <c r="J2" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" s="3">
         <v>2400000.0</v>
@@ -777,7 +499,7 @@
         <v>46286.625694</v>
       </c>
       <c r="J3" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" s="3">
         <v>177000000.0</v>
@@ -872,7 +594,7 @@
         <v>46286.625694</v>
       </c>
       <c r="J4" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="3">
         <v>22700000.0</v>
@@ -931,12 +653,12 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2483-242-CO26</t>
+          <t xml:space="preserve">2345-148-LE26</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
+          <t xml:space="preserve">ADQUISICIÓN DE CAMIÓN CON CARROCERIA Y PLATAFORMA DE ELEVACIÓN</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -946,12 +668,12 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE QUILICURA</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO COMPRAS PÚBLICAS</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
@@ -959,15 +681,19 @@
           <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="G5" s="0"/>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las Condes</t>
+        </is>
+      </c>
       <c r="H5" s="2">
-        <v>46273.365613</v>
+        <v>46269.376991</v>
       </c>
       <c r="I5" s="2">
         <v>46286.625694</v>
       </c>
       <c r="J5" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="0" t="inlineStr">
@@ -977,17 +703,17 @@
       </c>
       <c r="M5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CO</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ropa, maletas y productos de aseo personal / Ropa / Uniformes</t>
+          <t xml:space="preserve">Equipamiento para manejo y estiba de materiales / Maquinaria para manejo de materiales / Camiones, carros y carretillas industriales</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Paquete · Uniformes varios</t>
+          <t xml:space="preserve">1 Unidad · Camión volcador</t>
         </is>
       </c>
       <c r="P5" s="2"/>
@@ -1001,27 +727,27 @@
       <c r="T5" s="4"/>
       <c r="U5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dirección de Asesoría Jurídica</t>
+          <t xml:space="preserve">Servicios Generales</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN, MANTENCIÓN, EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD, MUNICIPALIDAD DE QUILICURA" DECRETO ALCALDICIO E. N°3401 APRUEBA LICITACIÓN PRIVADA</t>
+          <t xml:space="preserve">El objetivo de este proceso de licitación es la adquisición de un camión nuevo con carrocería y plataforma de elevación para realizar trabajos en altura</t>
         </is>
       </c>
       <c r="W5" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=mCvoX1kcS6QUPN3Y10ODxINgIzaveQ5FWF0BTELAMlQ5XFah9czxmYveDig6we7FwMfw00IFMBtvKEh4KtC0q5m%2binFtPrYaXo8KEZptEJfzDTH916IAMcqKCWWuuxu0Reh9GFaOfQ6Hz%2bIRdfFJwTl4wqhHJNVI37qagWkMHABEBIfJD5UbgB9F1OLjZl0s2CmfW3IWJGCdRTlpbPf0dtCxFxXi3%2bLEHYD6kO8KV2gYa8A3WgKFe5sDBYU5bUosKWwDSUyL%2ffQ3%2bG3m9JrbNx8l6szfa4SrlAXV37VPMxYIoYtq3g%2fRj3I2QASXUyD3","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=UJJI%2bzX%2bYk727nNV7Suz20u25m3Ho7Ki8iae%2bQV%2fwQtBbItkrEnsI1u779HlkU8ZqztzY3ys5ar1Pc3G9clAKHs5xk%2feoMLMesADs8AOmNPpVezhHeCpmxo0Oo%2bMJrhBoGSLEc%2bBvL1U9mJcIh3beyFdXjsLHTF29VBMyPOUrYU5Mi69C3hbpLB9Fa%2bdNs4M7BpzZlg8PdLawa7hbE82g2QUOi3ZNdGLF1vavModLv1bw%2bRPLoZRvTA32xPMZxIk2IUZwN9bsFZlr332KOB4G016hsPBKB7LOTiFJ7cQxkUyjGIic%2bmq3%2b%2b%2fyavvoHUL","descargar bases")</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2710-55-LE26</t>
+          <t xml:space="preserve">2483-242-CO26</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO TOTEM</t>
+          <t xml:space="preserve">“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -1031,36 +757,30 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MUNICIPALIDAD DE OVALLE</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Depto. de Salud e Higiene Ambiental</t>
+          <t xml:space="preserve">DEPARTAMENTO COMPRAS PÚBLICAS</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
-        </is>
-      </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ovalle</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G6" s="0"/>
       <c r="H6" s="2">
-        <v>46273.562859</v>
+        <v>46273.365613</v>
       </c>
       <c r="I6" s="2">
         <v>46286.625694</v>
       </c>
       <c r="J6" s="0">
-        <v>3</v>
-      </c>
-      <c r="K6" s="3">
-        <v>9999998.0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -1068,26 +788,22 @@
       </c>
       <c r="M6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">CO</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Pantallas o monitores de computador</t>
+          <t xml:space="preserve">Ropa, maletas y productos de aseo personal / Ropa / Uniformes</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Monitores de pantalla táctil</t>
+          <t xml:space="preserve">1 Paquete · Uniformes varios</t>
         </is>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 meses</t>
-        </is>
-      </c>
+      <c r="R6" s="0"/>
       <c r="S6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -1096,27 +812,27 @@
       <c r="T6" s="4"/>
       <c r="U6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA OLIVAREZ AGUILUZ</t>
+          <t xml:space="preserve">Dirección de Asesoría Jurídica</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO TOTEM , TV y LICENCIA DE SISTEMA GESTOR DE FILA PARA TOTEM EN CENTROS DE SALUD</t>
+          <t xml:space="preserve">“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN, MANTENCIÓN, EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD, MUNICIPALIDAD DE QUILICURA" DECRETO ALCALDICIO E. N°3401 APRUEBA LICITACIÓN PRIVADA</t>
         </is>
       </c>
       <c r="W6" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=dMwqsLy4yWhPvUl5wzJC132KOngz0ZQg%2f7qy%2beOKXbJnMeb1RVy%2fNwR2tJ3ZQ7OhlR2h1ye9ue3Qeex2J6bZxXNMZvRDqEy%2boaLbP4licGpa%2b%2fkF75EmeMqm6duPIuP9agHdiAYPzs%2b0QbIXGzHxV3%2f5ygwzF02xJmjEVdzPuKdOGAHXDs67Cg9uXJ%2fKpAillPDNQvkswl%2f4%2bkQuAhI4GClsuwkWFGKQ9fAZyW8VgA8kqQfdKs70qolvdJNvKYXPr5QNNVEdofECtJ9a41pgQsQBcOpBOV1lxakU0mFyko3N5sIqHcGJX27TF3Rgi9oA","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=mCvoX1kcS6QUPN3Y10ODxINgIzaveQ5FWF0BTELAMlQ5XFah9czxmYveDig6we7FwMfw00IFMBtvKEh4KtC0q5m%2binFtPrYaXo8KEZptEJfzDTH916IAMcqKCWWuuxu0Reh9GFaOfQ6Hz%2bIRdfFJwTl4wqhHJNVI37qagWkMHABEBIfJD5UbgB9F1OLjZl0s2CmfW3IWJGCdRTlpbPf0dtCxFxXi3%2bLEHYD6kO8KV2gYa8A3WgKFe5sDBYU5bUosKWwDSUyL%2ffQ3%2bG3m9JrbNx8l6szfa4SrlAXV37VPMxYIoYtq3g%2fRj3I2QASXUyD3","descargar bases")</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2785-78-LE26</t>
+          <t xml:space="preserve">2710-55-LE26</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SDA 6375 SERVICIOS DE PUBLICIDAD Y DIFUSIÓN GESTIÓN MUNICIPAL EN MEDIOS DIGITALES Y PANTALLA LED</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO TOTEM</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -1126,35 +842,35 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t xml:space="preserve">MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t xml:space="preserve">Depto. de Salud e Higiene Ambiental</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t xml:space="preserve">Región de Coquimbo </t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Pedro de La Paz</t>
+          <t xml:space="preserve">Ovalle</t>
         </is>
       </c>
       <c r="H7" s="2">
-        <v>46269.724884</v>
+        <v>46273.562859</v>
       </c>
       <c r="I7" s="2">
         <v>46286.625694</v>
       </c>
       <c r="J7" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" s="3">
-        <v>19800000.0</v>
+        <v>9999998.0</v>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
@@ -1168,19 +884,19 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios editoriales, de diseño, publicidad, gráficos y artistas / Publicidad / Agencias de publicidad, Servicios editoriales, de diseño, publicidad, gráficos y artistas / Publicidad / Publicidad en medios no impresos</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Pantallas o monitores de computador</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 Mes · Campañas publicitarias · 2 Mes · Publicidad en Internet</t>
+          <t xml:space="preserve">1 Unidad · Monitores de pantalla táctil</t>
         </is>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 meses</t>
+          <t xml:space="preserve">12 meses</t>
         </is>
       </c>
       <c r="S7" s="0" t="inlineStr">
@@ -1191,16 +907,16 @@
       <c r="T7" s="4"/>
       <c r="U7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDRES BUSTAMANTE CONTRERAS</t>
+          <t xml:space="preserve">VALERIA OLIVAREZ AGUILUZ</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIOS DE PUBLICIDAD Y DIFUSIÓN GESTIÓN MUNICIPAL, SOLICITADOS POR EL DEPARTAMENTO DE COMUNICACIONES, PERIODO OCTUBRE DICIEMBRE 2026, SEGUN REQUERIMIENTOS EN BASES ADMINISTRATIVAS Y TECNICAS</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO TOTEM , TV y LICENCIA DE SISTEMA GESTOR DE FILA PARA TOTEM EN CENTROS DE SALUD</t>
         </is>
       </c>
       <c r="W7" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=CHXur1HaQdPbEx3DZ%2fGV6bv50CQY0WgIJnsi1iVA6U7X7Gx6wuUZ8ATwyoFAlt4Vnr%2fdqlgSUluWkOmRDfWKzNsN%2f7vaCvR9U%2bFyRIiBq%2fhG3cLcQ1bvuo%2fuFDKCKV1m0MTROR7bZgyK1lMPX21nGzuh5IMVje%2fS%2fGa2DcvhZqg5n5UCFf5sBSOb2%2bJayjBDcsKKqTwenvHkkq9bZPvoantZizbd1paD7zRYiGVQ7IHc0GNevdUCPp4MvvuiwoD%2bwUZGyhykVJJaQwMd4pzVBMfM6DjN2HvoMTO0oeh61fsREmH0s6U8%2fK%2b5h%2fedrgE0","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=dMwqsLy4yWhPvUl5wzJC132KOngz0ZQg%2f7qy%2beOKXbJnMeb1RVy%2fNwR2tJ3ZQ7OhlR2h1ye9ue3Qeex2J6bZxXNMZvRDqEy%2boaLbP4licGpa%2b%2fkF75EmeMqm6duPIuP9agHdiAYPzs%2b0QbIXGzHxV3%2f5ygwzF02xJmjEVdzPuKdOGAHXDs67Cg9uXJ%2fKpAillPDNQvkswl%2f4%2bkQuAhI4GClsuwkWFGKQ9fAZyW8VgA8kqQfdKs70qolvdJNvKYXPr5QNNVEdofECtJ9a41pgQsQBcOpBOV1lxakU0mFyko3N5sIqHcGJX27TF3Rgi9oA","descargar bases")</f>
       </c>
     </row>
     <row r="8">
@@ -1246,7 +962,7 @@
         <v>46286.625694</v>
       </c>
       <c r="J8" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" s="3">
         <v>18000000.0</v>
@@ -1333,7 +1049,7 @@
         <v>46286.625694</v>
       </c>
       <c r="J9" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" s="3">
         <v>10620000.0</v>
@@ -1388,12 +1104,12 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">875-7-LE26</t>
+          <t xml:space="preserve">598-20-LE26</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. INFORMES Y PLATAFORMA DE PROYECTOS INVERSIÓN</t>
+          <t xml:space="preserve">Adquisición Licencias de Software para DIPRECA</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -1403,12 +1119,12 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
+          <t xml:space="preserve">DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agencia de Promoción de la Inversión Extranjera</t>
+          <t xml:space="preserve">Unidad de Abastecimiento DIPRECA</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
@@ -1422,20 +1138,18 @@
         </is>
       </c>
       <c r="H10" s="2">
-        <v>46273.666088</v>
+        <v>46268.704167</v>
       </c>
       <c r="I10" s="2">
         <v>46286.625694</v>
       </c>
       <c r="J10" s="0">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3">
-        <v>440.0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K10" s="3"/>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLF</t>
+          <t xml:space="preserve">CLP</t>
         </is>
       </c>
       <c r="M10" s="0" t="inlineStr">
@@ -1445,19 +1159,19 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Productos impresos y publicaciones / Medios impresos / Publicaciones impresas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Publicaciones periódicas</t>
+          <t xml:space="preserve">1 Unidad · Software de gestión de licencias · 3 Unidad · Software de gestión de licencias · 4 Unidad · Software de gestión de licencias · y 1 más</t>
         </is>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 meses</t>
+          <t xml:space="preserve">36 meses</t>
         </is>
       </c>
       <c r="S10" s="0" t="inlineStr">
@@ -1468,27 +1182,27 @@
       <c r="T10" s="4"/>
       <c r="U10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ana Karina Duarte</t>
+          <t xml:space="preserve">Alex Saavedra Carrasco</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ELABORACIÓN Y ENTREGA DE INFORMES DE PROYECTOS DE INVERSIÓN EN CHILE Y ACCESO A UNA PLATAFORMA ONLINE DE SEGUIMIENTO DE PROYECTOS DE INVERSIÓN PARA LA AGENCIA DE PROMOCIÓN DE LA INVERSIÓN EXTRANJERA</t>
+          <t xml:space="preserve">Contratación del licenciamiento de CLOUDFLARE BUSINESS, CROWDSEC, INTELLIJ SOFTWARE PACK COMPLETO DE 11 IDE, SEGÚN DETALLE ADJUNTO, TRAE IA, ENTORNO DE DESARROLLO INTEGRADO ULTRA, que permitirán a Dipreca contar con herramientas avanzadas de edición, creación y gestión de documentos PDF.</t>
         </is>
       </c>
       <c r="W10" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=Jg8jPgTJl2oW4tgofuLXSd0ybKSst%2fhAS8BqKxsBV4X%2bi10UPQilMc%2f%2frXl%2f82L2m8bnRDCD%2bpmcoSsmzMEnOE332P3ByyQXnL94M6IB6xjXK2KY5KdU%2f5sPs%2fqIaIaogzpTIS%2fMZP4wYkxLzwf07z1M2tVyKh%2bJl3j9ZVscdgg3pMdfh9YtrH4EKst2t6DIgkB3PWxPHlTBD0b1vqsd5sI7h44bclU9YJs%2beRrVzq7D%2br9sSV4fbk51fK5hwBt6KSBDczOeTgA4bAP7MIU7pgLHzGbHfuJA4L824TR6U0Vp%2bnwOeH8CPnkm1a4dgDYP","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=wxzqfYsqGaiiTtLfxTterPH9Zcu1K3klGgv2URdsf6K%2blesLJ1NAAKuv6v8iNVTCZPdvDGh1LMYb%2bqK3GEKBLybZ2yt3giGfO8DYkaE72AqEEGEomHFZLwEl42DEMU43pt7rciHC6ahYmB87asTPrHxM4jvL%2bQWpWWQOy%2bFjUbcmvWin1RE1cXVsBvVkY6XcFMKU3SrBlTN4UYgQpJZCzid538wTP%2b%2foKK9adORufeeRwE9CNkeQad%2bhFzglf4SKdhrfi6UBzboaA181xGFGDwRl1aLmM33hEK0sBr4TyyFBP8D9FrGYhtixIksZuOkG","descargar bases")</f>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345-148-LE26</t>
+          <t xml:space="preserve">875-7-LE26</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE CAMIÓN CON CARROCERIA Y PLATAFORMA DE ELEVACIÓN</t>
+          <t xml:space="preserve">SERV. INFORMES Y PLATAFORMA DE PROYECTOS INVERSIÓN</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -1498,12 +1212,12 @@
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE LAS CONDES</t>
+          <t xml:space="preserve">AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE LAS CONDES</t>
+          <t xml:space="preserve">Agencia de Promoción de la Inversión Extranjera</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
@@ -1513,22 +1227,24 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Condes</t>
+          <t xml:space="preserve">Santiago</t>
         </is>
       </c>
       <c r="H11" s="2">
-        <v>46269.376991</v>
+        <v>46273.666088</v>
       </c>
       <c r="I11" s="2">
         <v>46286.625694</v>
       </c>
       <c r="J11" s="0">
-        <v>3</v>
-      </c>
-      <c r="K11" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="K11" s="3">
+        <v>440.0</v>
+      </c>
       <c r="L11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">CLF</t>
         </is>
       </c>
       <c r="M11" s="0" t="inlineStr">
@@ -1538,17 +1254,21 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento para manejo y estiba de materiales / Maquinaria para manejo de materiales / Camiones, carros y carretillas industriales</t>
+          <t xml:space="preserve">Productos impresos y publicaciones / Medios impresos / Publicaciones impresas</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Camión volcador</t>
+          <t xml:space="preserve">1 Unidad · Publicaciones periódicas</t>
         </is>
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
-      <c r="R11" s="0"/>
+      <c r="R11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 meses</t>
+        </is>
+      </c>
       <c r="S11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -1557,27 +1277,27 @@
       <c r="T11" s="4"/>
       <c r="U11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios Generales</t>
+          <t xml:space="preserve">Ana Karina Duarte</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El objetivo de este proceso de licitación es la adquisición de un camión nuevo con carrocería y plataforma de elevación para realizar trabajos en altura</t>
+          <t xml:space="preserve">SERVICIO DE ELABORACIÓN Y ENTREGA DE INFORMES DE PROYECTOS DE INVERSIÓN EN CHILE Y ACCESO A UNA PLATAFORMA ONLINE DE SEGUIMIENTO DE PROYECTOS DE INVERSIÓN PARA LA AGENCIA DE PROMOCIÓN DE LA INVERSIÓN EXTRANJERA</t>
         </is>
       </c>
       <c r="W11" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=UJJI%2bzX%2bYk727nNV7Suz20u25m3Ho7Ki8iae%2bQV%2fwQtBbItkrEnsI1u779HlkU8ZqztzY3ys5ar1Pc3G9clAKHs5xk%2feoMLMesADs8AOmNPpVezhHeCpmxo0Oo%2bMJrhBoGSLEc%2bBvL1U9mJcIh3beyFdXjsLHTF29VBMyPOUrYU5Mi69C3hbpLB9Fa%2bdNs4M7BpzZlg8PdLawa7hbE82g2QUOi3ZNdGLF1vavModLv1bw%2bRPLoZRvTA32xPMZxIk2IUZwN9bsFZlr332KOB4G016hsPBKB7LOTiFJ7cQxkUyjGIic%2bmq3%2b%2b%2fyavvoHUL","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=Jg8jPgTJl2oW4tgofuLXSd0ybKSst%2fhAS8BqKxsBV4X%2bi10UPQilMc%2f%2frXl%2f82L2m8bnRDCD%2bpmcoSsmzMEnOE332P3ByyQXnL94M6IB6xjXK2KY5KdU%2f5sPs%2fqIaIaogzpTIS%2fMZP4wYkxLzwf07z1M2tVyKh%2bJl3j9ZVscdgg3pMdfh9YtrH4EKst2t6DIgkB3PWxPHlTBD0b1vqsd5sI7h44bclU9YJs%2beRrVzq7D%2br9sSV4fbk51fK5hwBt6KSBDczOeTgA4bAP7MIU7pgLHzGbHfuJA4L824TR6U0Vp%2bnwOeH8CPnkm1a4dgDYP","descargar bases")</f>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">598-20-LE26</t>
+          <t xml:space="preserve">2785-78-LE26</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición Licencias de Software para DIPRECA</t>
+          <t xml:space="preserve">SDA 6375 SERVICIOS DE PUBLICIDAD Y DIFUSIÓN GESTIÓN MUNICIPAL EN MEDIOS DIGITALES Y PANTALLA LED</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -1587,34 +1307,36 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad de Abastecimiento DIPRECA</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región del Biobío </t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santiago</t>
+          <t xml:space="preserve">San Pedro de La Paz</t>
         </is>
       </c>
       <c r="H12" s="2">
-        <v>46268.704167</v>
+        <v>46269.724884</v>
       </c>
       <c r="I12" s="2">
         <v>46286.625694</v>
       </c>
       <c r="J12" s="0">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="3">
+        <v>19800000.0</v>
+      </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -1627,19 +1349,19 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios editoriales, de diseño, publicidad, gráficos y artistas / Publicidad / Agencias de publicidad, Servicios editoriales, de diseño, publicidad, gráficos y artistas / Publicidad / Publicidad en medios no impresos</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de licencias · 3 Unidad · Software de gestión de licencias · 4 Unidad · Software de gestión de licencias · y 1 más</t>
+          <t xml:space="preserve">3 Mes · Campañas publicitarias · 2 Mes · Publicidad en Internet</t>
         </is>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">36 meses</t>
+          <t xml:space="preserve">3 meses</t>
         </is>
       </c>
       <c r="S12" s="0" t="inlineStr">
@@ -1650,16 +1372,16 @@
       <c r="T12" s="4"/>
       <c r="U12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Saavedra Carrasco</t>
+          <t xml:space="preserve">ANDRES BUSTAMANTE CONTRERAS</t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación del licenciamiento de CLOUDFLARE BUSINESS, CROWDSEC, INTELLIJ SOFTWARE PACK COMPLETO DE 11 IDE, SEGÚN DETALLE ADJUNTO, TRAE IA, ENTORNO DE DESARROLLO INTEGRADO ULTRA, que permitirán a Dipreca contar con herramientas avanzadas de edición, creación y gestión de documentos PDF.</t>
+          <t xml:space="preserve">SERVICIOS DE PUBLICIDAD Y DIFUSIÓN GESTIÓN MUNICIPAL, SOLICITADOS POR EL DEPARTAMENTO DE COMUNICACIONES, PERIODO OCTUBRE DICIEMBRE 2026, SEGUN REQUERIMIENTOS EN BASES ADMINISTRATIVAS Y TECNICAS</t>
         </is>
       </c>
       <c r="W12" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=wxzqfYsqGaiiTtLfxTterPH9Zcu1K3klGgv2URdsf6K%2blesLJ1NAAKuv6v8iNVTCZPdvDGh1LMYb%2bqK3GEKBLybZ2yt3giGfO8DYkaE72AqEEGEomHFZLwEl42DEMU43pt7rciHC6ahYmB87asTPrHxM4jvL%2bQWpWWQOy%2bFjUbcmvWin1RE1cXVsBvVkY6XcFMKU3SrBlTN4UYgQpJZCzid538wTP%2b%2foKK9adORufeeRwE9CNkeQad%2bhFzglf4SKdhrfi6UBzboaA181xGFGDwRl1aLmM33hEK0sBr4TyyFBP8D9FrGYhtixIksZuOkG","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=ccI5U4jksk6CvHXY%2bWLelpoDJj35EVgrO1zRXJHgZXW7QmNJbHnVXjrYwOYgMLST8oV01QZn3kAg6tFd%2b3y%2bftO1qk8dtT4yXRyNT%2fUGj3WW0D1wdqrS6aqFAMS8en2FzK9TwvaCY3dD2duUJmKnHkMnyqgnJpPwHm1LGRFUwv4fGrTINs%2bksrPziTy2wI7Fxj2APc5JkyLwtxBsAPsJF9yDNByXudaiEIkh5HSOUbFTKPVMsodCOMJ9wmlF%2fFHI2CKBvGGHtPe%2fimGC6dY38R3T9AkwKgp8ggZC2km7TM%2f2g5X9pH9lD3ADa8XIEeAH","descargar bases")</f>
       </c>
     </row>
     <row r="13">
@@ -1705,7 +1427,7 @@
         <v>46286.645833</v>
       </c>
       <c r="J13" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" s="3">
         <v>35750000.0</v>
@@ -1796,7 +1518,7 @@
         <v>46286.645833</v>
       </c>
       <c r="J14" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="3">
         <v>180329688.0</v>
@@ -1887,7 +1609,7 @@
         <v>46286.645833</v>
       </c>
       <c r="J15" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" s="3">
         <v>192000000.0</v>
@@ -1982,7 +1704,7 @@
         <v>46286.645833</v>
       </c>
       <c r="J16" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" s="3">
         <v>56000000.0</v>
@@ -2037,12 +1759,12 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1393093-103-LE26</t>
+          <t xml:space="preserve">1393093-98-LE26</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
+          <t xml:space="preserve">CONTRATACIÓN DE SERV. DE DESA.SOFTWARE RENDICIONES</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -2067,13 +1789,13 @@
       </c>
       <c r="G17" s="0"/>
       <c r="H17" s="2">
-        <v>46276.545428</v>
+        <v>46269.399306</v>
       </c>
       <c r="I17" s="2">
         <v>46286.666667</v>
       </c>
       <c r="J17" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="0" t="inlineStr">
@@ -2088,19 +1810,19 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">120 Unidad · Software de gestión de licencias · 130 Unidad · Software de gestión de licencias · 5 Unidad · Software de gestión de licencias · y 4 más</t>
+          <t xml:space="preserve">1 Unidad · Desarrolladores temporales de software</t>
         </is>
       </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 meses</t>
+          <t xml:space="preserve">24 meses</t>
         </is>
       </c>
       <c r="S17" s="0" t="inlineStr">
@@ -2111,18 +1833,16 @@
       <c r="T17" s="4"/>
       <c r="U17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco Echeverria</t>
+          <t xml:space="preserve">YESIKA DIAZ</t>
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cubrir las necesidades de
-seguridad informática, gestión y recuperación de equipos, diseño y edición audiovisual y
-soporte remoto del Servicio Local de Educación Pública de Chiloé</t>
+          <t xml:space="preserve">Gestionar de manera sistemática, ordenada y oportuna la información asociada a ingresos, gastos (compras) y remuneraciones por establecimiento educacional (RBD) y por tipo de subvención, facilitando los procesos de control, seguimiento y rendición de cuentas ante la Superintendencia de Educación.</t>
         </is>
       </c>
       <c r="W17" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=0a55f9aL9KnjCZt9F2sWFMt9rr1b%2bPwIClxv9m%2fUaj19oslpVH0qfXJ6kNIVP8eyyLkamAF8x1ZlzGK0xEaMJGzmQtMB7fy2YT8PNVSCn8xTV0ERDx3dfUJqajIB0%2byJl%2fsBdas3r245eqyyy9G3ACGcoQaAqXjB8iggMnntAdvYwqdlSY%2fUPzbbDmYYtHibh0aHeeq2V%2fm4XHoaIwXJ7078h4humuP1tMzdsepnyVsIHJyVDmhc2R5cvTx0WSexd9I1NXJrclZQ2ywqeHdfLk1TpTBaMFcPBokAuxR9Tz2hpIr%2fogu0vJMZG7u%2bqu2R","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=vYeS%2fnpeBm%2fuEQcmlyMsnYJwUCxqiS8j3R2dMynTyRK%2bkic%2fhjPNAz6mhiy8GlP86hbodqkAm2IiV8Jz6k4YAEGBQz2t%2bLqiS17Hlh8axsHvDJsD9pzJvLN6s8X1cyShAm7VcYZB%2fqQNfZiJwWPdcXpoWUIOMiLkkKpKkWYbV0GwPYG7KqoavFDvIY2%2bkkAmQGxW3OwuqxgET05XoanIOsqydZZCC5lDw%2bUCq6LzCvSFJQ5PR5f%2bsD5xIe0XyQ%2f%2bOadqas5YbH9xkbxGkBfId0li80ObpeC2yDteyd4GZVvLjJ0IXirWsTnPopumeujE","descargar bases")</f>
       </c>
     </row>
     <row r="18">
@@ -2168,7 +1888,7 @@
         <v>46286.666667</v>
       </c>
       <c r="J18" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="0" t="inlineStr">
@@ -2264,7 +1984,7 @@
         <v>46286.666667</v>
       </c>
       <c r="J19" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="0" t="inlineStr">
@@ -2357,7 +2077,7 @@
         <v>46286.666667</v>
       </c>
       <c r="J20" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="3">
         <v>95000000.0</v>
@@ -2452,7 +2172,7 @@
         <v>46286.666667</v>
       </c>
       <c r="J21" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" s="3">
         <v>4522419.0</v>
@@ -2500,12 +2220,12 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1393093-98-LE26</t>
+          <t xml:space="preserve">1393093-103-LE26</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DE SERV. DE DESA.SOFTWARE RENDICIONES</t>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -2530,13 +2250,13 @@
       </c>
       <c r="G22" s="0"/>
       <c r="H22" s="2">
-        <v>46269.399306</v>
+        <v>46276.545428</v>
       </c>
       <c r="I22" s="2">
         <v>46286.666667</v>
       </c>
       <c r="J22" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="0" t="inlineStr">
@@ -2551,19 +2271,19 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Desarrolladores temporales de software</t>
+          <t xml:space="preserve">120 Unidad · Software de gestión de licencias · 130 Unidad · Software de gestión de licencias · 5 Unidad · Software de gestión de licencias · y 4 más</t>
         </is>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 meses</t>
+          <t xml:space="preserve">14 meses</t>
         </is>
       </c>
       <c r="S22" s="0" t="inlineStr">
@@ -2574,16 +2294,18 @@
       <c r="T22" s="4"/>
       <c r="U22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">YESIKA DIAZ</t>
+          <t xml:space="preserve">Marco Echeverria</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestionar de manera sistemática, ordenada y oportuna la información asociada a ingresos, gastos (compras) y remuneraciones por establecimiento educacional (RBD) y por tipo de subvención, facilitando los procesos de control, seguimiento y rendición de cuentas ante la Superintendencia de Educación.</t>
+          <t xml:space="preserve">Cubrir las necesidades de
+seguridad informática, gestión y recuperación de equipos, diseño y edición audiovisual y
+soporte remoto del Servicio Local de Educación Pública de Chiloé</t>
         </is>
       </c>
       <c r="W22" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=vYeS%2fnpeBm%2fuEQcmlyMsnYJwUCxqiS8j3R2dMynTyRK%2bkic%2fhjPNAz6mhiy8GlP86hbodqkAm2IiV8Jz6k4YAEGBQz2t%2bLqiS17Hlh8axsHvDJsD9pzJvLN6s8X1cyShAm7VcYZB%2fqQNfZiJwWPdcXpoWUIOMiLkkKpKkWYbV0GwPYG7KqoavFDvIY2%2bkkAmQGxW3OwuqxgET05XoanIOsqydZZCC5lDw%2bUCq6LzCvSFJQ5PR5f%2bsD5xIe0XyQ%2f%2bOadqas5YbH9xkbxGkBfId0li80ObpeC2yDteyd4GZVvLjJ0IXirWsTnPopumeujE","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=%2fFPtLa9bg9tcD%2fWtPcCviHOr2UHJifwxEM4uAcQ9%2foMgRfBiaLJxtAmlvVGza74pglkXz2dkFMVl09TZh7JhZCGvLCO2AGuSPmgG6iUjnuwik5NxzFOOlab%2bB1ZEoykavK6Z2GT9Mrf4src3owzCXoFC3JU25yBniVHwOXkbSyd4FUBXb5GlaocV%2fgXjXKRHrLfn3RlsXDf7Indnmc5Kg6o%2bTMnbzx1gdPciLZ5AXRY5n50ntXragTotmILlhHyns9x0BOTFMZwbMZyoZvVGjiLGauw2hpcKzF1U9ptVEPyrYB11nfFyW%2fALCLJPBtKJ","descargar bases")</f>
       </c>
     </row>
     <row r="23">
@@ -2625,7 +2347,7 @@
         <v>46286.708333</v>
       </c>
       <c r="J23" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" s="3">
         <v>9999784.0</v>
@@ -2716,7 +2438,7 @@
         <v>46286.75</v>
       </c>
       <c r="J24" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24" s="3">
         <v>154800005.0</v>
@@ -2811,7 +2533,7 @@
         <v>46286.778472</v>
       </c>
       <c r="J25" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K25" s="3">
         <v>19500000.0</v>
@@ -2902,7 +2624,7 @@
         <v>46286.833333</v>
       </c>
       <c r="J26" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" s="3">
         <v>45000000.0</v>
@@ -3000,7 +2722,7 @@
         <v>46287.375</v>
       </c>
       <c r="J27" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K27" s="3">
         <v>10565838.0</v>
@@ -3049,7 +2771,7 @@
         </is>
       </c>
       <c r="W27" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=8lH5GqMpv3msrkvPvC2ynWLPaUWWWbizbxscUrIHa5RLDNMZ9Yf1vuVBCmJ99qoU4wZ31brUdXzABoXTTytTfv39dvdAtQKNpUIB8EOHqrrKJhxPayVrMrGKDjGPsawwcnXq68QSLmpCmGxfeqiX4k3bJ0EdZTBvtfxnN8kkyHmRstNGkYswjJPNlGb%2f%2bGpJ12P6qo5zlajmlfQXfq%2bulbGr4UiFLtXk3FJ2lkBrW8OxTvWGBwkeUBPfToVM8trWLqynlZA8wQJUu07Dl3yWEJkH4gCvWong4PMlL%2fsZczDWpDNiBdduqjGY%2fmhf1UrP","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=dA7cchcA4I1l6XpUfnKagTs8W8%2beSzk5KlADB2VGqDqWkQpTRItZfPVmc%2fFZm0ggmKS6jatY80A%2f3V6HEsOiX4ogrheeJngq5e3o9XDj16fMUBB51dR9GXoSDgK1QSWaMhe9xk2MLDlKFc6ndbZPELO059rop%2fQTiIgv%2fcskhQ%2f9WiaWkxL1zVxEeU8HFFIVO9yCyvER7kZHSGqIDkwj0%2bwpRfUbndUgg27nbWZgCP9akQEsKhHYq9knndy%2fF7F2LTqiirR7086q9423N8yoVfhBdNEVBo2NkcJD5woOwXRqLGibkZl7QQDYX7ivFWdO","descargar bases")</f>
       </c>
     </row>
     <row r="28">
@@ -3095,7 +2817,7 @@
         <v>46287.377083</v>
       </c>
       <c r="J28" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="0" t="inlineStr">
@@ -3184,7 +2906,7 @@
         <v>46287.625</v>
       </c>
       <c r="J29" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>366678654.0</v>
@@ -3280,7 +3002,7 @@
         <v>46287.625</v>
       </c>
       <c r="J30" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="0" t="inlineStr">
@@ -3369,7 +3091,7 @@
         <v>46287.625</v>
       </c>
       <c r="J31" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="0" t="inlineStr">
@@ -3466,7 +3188,7 @@
         <v>46287.625694</v>
       </c>
       <c r="J32" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>10177597.0</v>
@@ -3553,7 +3275,7 @@
         <v>46287.625694</v>
       </c>
       <c r="J33" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>10000000.0</v>
@@ -3608,12 +3330,12 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">837-101-LP26</t>
+          <t xml:space="preserve">5413-71-LE26</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CDP 477 SERVICIO DE OPERACIÓN SISTEMA DE CONTROL CENTRALIZADO BMS Y SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL DE EDIFICIO INSTITUCIONAL SML SANTIAGO</t>
+          <t xml:space="preserve">SERVICIO DE PLATAFORMA DE LIBROS CONTABLES Y AUXILIARES ELECTRÓNICOS Y DOCUMENTOS TRIBUTARIOS ELECTRÓNICOS DTE PARA LA UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -3623,32 +3345,34 @@
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO MEDICO LEGAL</t>
+          <t xml:space="preserve">UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO MEDICO LEGAL</t>
+          <t xml:space="preserve">CAMPUS OSORNO</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G34" s="0"/>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Osorno</t>
+        </is>
+      </c>
       <c r="H34" s="2">
-        <v>46265.419491</v>
+        <v>46269.381134</v>
       </c>
       <c r="I34" s="2">
         <v>46287.645833</v>
       </c>
       <c r="J34" s="0">
-        <v>4</v>
-      </c>
-      <c r="K34" s="3">
-        <v>346885000.0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K34" s="3"/>
       <c r="L34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -3656,24 +3380,24 @@
       </c>
       <c r="M34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipos y suministros de defensa, orden público, protección y seguridad / Seguridad, vigilancia y detección / Equipo de vigilancia y detección, Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas, Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 Mes · Software de administración · 12 Mes · Sistemas de control de acceso o de seguridad</t>
+          <t xml:space="preserve">36 Mes · Mantenimiento y soporte de sistemas propietarios · 36 Mes · Desarrolladores de software · 36 Mes · Desarrolladores de software</t>
         </is>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 meses</t>
+          <t xml:space="preserve">36 meses</t>
         </is>
       </c>
       <c r="S34" s="0" t="inlineStr">
@@ -3684,27 +3408,28 @@
       <c r="T34" s="4"/>
       <c r="U34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicente Muñoz, profesional DLI</t>
+          <t xml:space="preserve">Sandra Peñailillo</t>
         </is>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere contar con el SERVICIO DE OPERACIÓN PARA EL SISTEMA DE CONTROL CENTRALIZADO (BMS) SOFTWARE ENTELIWEB Y EL SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL) Y SU EQUIPAMIENTO ASOCIADO PERTENECIENTES AL EDIFICIO INSTITUCIONAL DEL SERVICIO MÉDICO LEGAL METROPOLITANO (SML), con el objeto de asegurar su correcta operación, revisión de instalaciones y programación en los sistemas y equipamiento instalados</t>
+          <t xml:space="preserve">UNIVERSIDAD DE LOS LAGOS, REQUIERE SERVICIO DE PLATAFORMA DE LIBROS CONTABLES Y AUXILIARES ELECTRÓNICOS Y DOCUMENTOS TRIBUTARIOS ELECTRÓNICOS (DTE) PARA LA UNIVERSIDAD DE LOS LAGOS.
+SEGÚN SASERVI N°83203.</t>
         </is>
       </c>
       <c r="W34" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=IM35Jz%2bE%2byjfWJlxZY25iT8zJDzug9UbfdKLKx29PJD2ig4Sx89CfDkpvoRZhTafHa1Vy8CipF%2bGGs0JMOUCtqSoy%2bJuIY9uDxcvvEpqkestgXCoiEuwWe5ys3xLXqGMD0IJuoNL%2fVpJG%2f53N7R7ILxwdl0yTtwG1fCVs39xa%2fg3OC%2bNdTn1FVlJOq%2fVD8%2bZzjKtevgdBH2iuGXrmo745Havm1u0VwzGEV1lC7PPh1i1HoOWOXvPY8cynuy7hA1o2x9O2mE0sxyc7Z9c5c1XAkjb0cDS9Yxmvm9A6e0iHfWb3A0OV5MNBCFKSQ%2b10c3Z","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=7vPEdpc4n%2bYEQz0OFmo%2bYZBvAnH4KPmDKfKm%2f2Pp9mWuirpIUPWCJDYksVQePCcKU2EIAKiYz7zFKyWW2YXHg9g7yerHdzYwIBV6gyEk90dO1cvDf7j8FxM0m%2fsz68I22N%2bTpwmXJ7RYP%2flJJmw76HYfoI2%2fwXSjDlJfiDYQBcD%2bsBTtm9mmcni05WZPD5BnUVh%2flhyZRM6XGIGhlxrBU%2faxbjasCsD2MSjFsLdvsPyUDKDRBZ8Rj8RoZ2zI%2f0XMGEmidFZtLcdpy%2fdLeu6DqU4W1mKkU6e9IoV%2beL4RpMTWC9Vcfag23PSIPeNoW8IC","descargar bases")</f>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413-71-LE26</t>
+          <t xml:space="preserve">837-101-LP26</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE PLATAFORMA DE LIBROS CONTABLES Y AUXILIARES ELECTRÓNICOS Y DOCUMENTOS TRIBUTARIOS ELECTRÓNICOS DTE PARA LA UNIVERSIDAD DE LOS LAGOS</t>
+          <t xml:space="preserve">CDP 477 SERVICIO DE OPERACIÓN SISTEMA DE CONTROL CENTRALIZADO BMS Y SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL DE EDIFICIO INSTITUCIONAL SML SANTIAGO</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -3714,34 +3439,32 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIVERSIDAD DE LOS LAGOS</t>
+          <t xml:space="preserve">SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPUS OSORNO</t>
+          <t xml:space="preserve">SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
-        </is>
-      </c>
-      <c r="G35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Osorno</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G35" s="0"/>
       <c r="H35" s="2">
-        <v>46269.381134</v>
+        <v>46265.419491</v>
       </c>
       <c r="I35" s="2">
         <v>46287.645833</v>
       </c>
       <c r="J35" s="0">
-        <v>4</v>
-      </c>
-      <c r="K35" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="K35" s="3">
+        <v>346885000.0</v>
+      </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -3749,24 +3472,24 @@
       </c>
       <c r="M35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas, Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Equipos y suministros de defensa, orden público, protección y seguridad / Seguridad, vigilancia y detección / Equipo de vigilancia y detección, Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">36 Mes · Mantenimiento y soporte de sistemas propietarios · 36 Mes · Desarrolladores de software · 36 Mes · Desarrolladores de software</t>
+          <t xml:space="preserve">12 Mes · Software de administración · 12 Mes · Sistemas de control de acceso o de seguridad</t>
         </is>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">36 meses</t>
+          <t xml:space="preserve">12 meses</t>
         </is>
       </c>
       <c r="S35" s="0" t="inlineStr">
@@ -3777,28 +3500,27 @@
       <c r="T35" s="4"/>
       <c r="U35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandra Peñailillo</t>
+          <t xml:space="preserve">Vicente Muñoz, profesional DLI</t>
         </is>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIVERSIDAD DE LOS LAGOS, REQUIERE SERVICIO DE PLATAFORMA DE LIBROS CONTABLES Y AUXILIARES ELECTRÓNICOS Y DOCUMENTOS TRIBUTARIOS ELECTRÓNICOS (DTE) PARA LA UNIVERSIDAD DE LOS LAGOS.
-SEGÚN SASERVI N°83203.</t>
+          <t xml:space="preserve">Se requiere contar con el SERVICIO DE OPERACIÓN PARA EL SISTEMA DE CONTROL CENTRALIZADO (BMS) SOFTWARE ENTELIWEB Y EL SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL) Y SU EQUIPAMIENTO ASOCIADO PERTENECIENTES AL EDIFICIO INSTITUCIONAL DEL SERVICIO MÉDICO LEGAL METROPOLITANO (SML), con el objeto de asegurar su correcta operación, revisión de instalaciones y programación en los sistemas y equipamiento instalados</t>
         </is>
       </c>
       <c r="W35" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=7vPEdpc4n%2bYEQz0OFmo%2bYZBvAnH4KPmDKfKm%2f2Pp9mWuirpIUPWCJDYksVQePCcKU2EIAKiYz7zFKyWW2YXHg9g7yerHdzYwIBV6gyEk90dO1cvDf7j8FxM0m%2fsz68I22N%2bTpwmXJ7RYP%2flJJmw76HYfoI2%2fwXSjDlJfiDYQBcD%2bsBTtm9mmcni05WZPD5BnUVh%2flhyZRM6XGIGhlxrBU%2faxbjasCsD2MSjFsLdvsPyUDKDRBZ8Rj8RoZ2zI%2f0XMGEmidFZtLcdpy%2fdLeu6DqU4W1mKkU6e9IoV%2beL4RpMTWC9Vcfag23PSIPeNoW8IC","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=IM35Jz%2bE%2byjfWJlxZY25iT8zJDzug9UbfdKLKx29PJD2ig4Sx89CfDkpvoRZhTafHa1Vy8CipF%2bGGs0JMOUCtqSoy%2bJuIY9uDxcvvEpqkestgXCoiEuwWe5ys3xLXqGMD0IJuoNL%2fVpJG%2f53N7R7ILxwdl0yTtwG1fCVs39xa%2fg3OC%2bNdTn1FVlJOq%2fVD8%2bZzjKtevgdBH2iuGXrmo745Havm1u0VwzGEV1lC7PPh1i1HoOWOXvPY8cynuy7hA1o2x9O2mE0sxyc7Z9c5c1XAkjb0cDS9Yxmvm9A6e0iHfWb3A0OV5MNBCFKSQ%2b10c3Z","descargar bases")</f>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098-142-LE26</t>
+          <t xml:space="preserve">4778-14-LP26</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
+          <t xml:space="preserve">SERV. ADMINISTRADO CONTACT CENTER OMNICANAL CON IA</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -3813,31 +3535,29 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospital Curanilahue</t>
+          <t xml:space="preserve">Compras de Insumos y Servicios Generales</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t xml:space="preserve">Región Aysén del General Carlos Ibáñez del Campo</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curanilahue</t>
+          <t xml:space="preserve">Coyhaique</t>
         </is>
       </c>
       <c r="H36" s="2">
-        <v>46276.658981</v>
+        <v>46254.698611</v>
       </c>
       <c r="I36" s="2">
         <v>46287.666667</v>
       </c>
       <c r="J36" s="0">
-        <v>4</v>
-      </c>
-      <c r="K36" s="3">
-        <v>23152000.0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K36" s="3"/>
       <c r="L36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -3845,51 +3565,59 @@
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artículos de electrónica / Circuitos electrónicos / Circuitos integrados, memorias y microprocesadores, Artículos de fabricación y producción / Artículos de ferretería / Soportes y puntales, Artículos de fabricación y producción / Cintas adhesivas y selladores / Cinta adhesiva, Artículos eléctricos y de iluminación / Equipamiento y artículos eléctricos / Equipamiento para distribución y transformación eléctrica, Equipos, accesorios y suministros de oficina / Accesorios de oficina y escritorio / Tableros o pizarras, Herramientas y maquinaria en general / Herramientas manuales / Herramientas de corte, estaje y punzones, Herramientas y maquinaria en general / Herramientas manuales / Prensas y herramientas especiales, Maquinaria para fabricación y transformación industrial / Maquinaria y suministros de procesos industriales / Dispositivos de guía, posicionamiento y sujeción</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 Unidad · Fuentes de alimentación continua · 100 Unidad · Fuentes de alimentación continua · 30 Unidad · Fuentes de alimentación continua · y 38 más</t>
+          <t xml:space="preserve">24 Unidad · Software para centrales de comunicación digital</t>
         </is>
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
-      <c r="R36" s="0"/>
+      <c r="R36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 meses</t>
+        </is>
+      </c>
       <c r="S36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T36" s="4"/>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ver Bases Administrativas Especiales, punto 3.</t>
+        </is>
+      </c>
       <c r="U36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS VEGA</t>
+          <t xml:space="preserve">Carolina Pérez Alfaro</t>
         </is>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conforme a Ley de Compras Públicas Nº19.886, el reglamento, sus modificaciones y su modernización, el Hospital Dr. Rafael Avaria Valenzuela de Curanilahue a través del Departamento de Abastecimiento y Logística, invita a los oferentes, personas naturales o jurídicas y Uniones Temporales de Proveedores, a participar en la licitación pública para contar con una Empresa externa, que provea de bienes o servicios, para el Hospital de Curanilahue y la red del Servicio de Salud, determinado los requisitos administrativos mínimos para participar en la propuesta y garantizar con este mismo instrumento la calidad y entrega del servicio requerido.</t>
+          <t xml:space="preserve">Servicio Administrado de Contact Center Omnicanal con Inteligencia Artificial para la Gestión Integral de la Contactabilidad de Usuarios del Hospital Regional Coyhaique.</t>
         </is>
       </c>
       <c r="W36" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=dUdx77rbseNLLMnQjfLScxPlzDCf7ZO5VbR1Ylzrv8A818cKzSdydNtJThEvARzIrIRiIKsESy0infak9ONdM9Bh5P86%2fHJqlJyhWomI%2fkChVEu4pH61QBBe8WVZwIVnOBys3NVBK%2b%2fD9hCpkoufXko%2fYvWwsOIAg8Uzo4zpGjIdPpU4wgsYDg6MHDptBqYOHW8Ork8gKMHo93KdxnnwjpFgpmkyejhEUGOBgXWLgpo%2baPCcBu0bcOZHjUZIOEkGEuv%2bUvRw9oOhDqrr6zv5YSXJQPubf3BC6fZc%2fyixMkpbu62Ox%2f4oThdhRtD%2fbBAB","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=0bdhNxuXo0yhJck3lJQQa4hM%2fiqVioa%2bZfKPiD186WrfCO7hP2ko0ICAaJJvFFfNqfuLoGJf5BeI52EPSSLZ5JgpJCt%2bVPH0LAhkZzjuxNsFQ5hoPGwQIrdsdtSz3lxE7SgZbTdH0qnZsB05yd4BJa74I0xEb9NO%2f05Eh2hH4kHkc6oTM0sDxtVKByqy5BBDFomSoOQcF%2fEwawhCwwWSPCp52D5JTBLc%2bw3etUoaMZcV0W9D6MWzRTsVv%2bGw0fBBOIAzas6epABmDRJK2ebjtSwws7w4TobxlV4ue%2bOVz9EHLGmB%2b%2fYeD2Q3A5%2bbDGrs","descargar bases")</f>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778-14-LP26</t>
+          <t xml:space="preserve">885-83-LE26</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. ADMINISTRADO CONTACT CENTER OMNICANAL CON IA</t>
+          <t xml:space="preserve">Servicios de soporte y mantenimiento de la plataforma de seguridad F5 de la Contraloría General de la República</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -3899,34 +3627,32 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t xml:space="preserve">CONTRALORIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras de Insumos y Servicios Generales</t>
+          <t xml:space="preserve">Contraloría General de la República</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Aysén del General Carlos Ibáñez del Campo</t>
-        </is>
-      </c>
-      <c r="G37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coyhaique</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G37" s="0"/>
       <c r="H37" s="2">
-        <v>46254.698611</v>
+        <v>46272.494688</v>
       </c>
       <c r="I37" s="2">
         <v>46287.666667</v>
       </c>
       <c r="J37" s="0">
-        <v>4</v>
-      </c>
-      <c r="K37" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="K37" s="3">
+        <v>16000000.0</v>
+      </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -3934,24 +3660,24 @@
       </c>
       <c r="M37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de seguridad de red</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 Unidad · Software para centrales de comunicación digital</t>
+          <t xml:space="preserve">1 Unidad · Equipo de seguridad de red de firewall</t>
         </is>
       </c>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 meses</t>
+          <t xml:space="preserve">12 meses</t>
         </is>
       </c>
       <c r="S37" s="0" t="inlineStr">
@@ -3959,34 +3685,30 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ver Bases Administrativas Especiales, punto 3.</t>
-        </is>
-      </c>
+      <c r="T37" s="4"/>
       <c r="U37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Pérez Alfaro</t>
+          <t xml:space="preserve">Cristian Leon</t>
         </is>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio Administrado de Contact Center Omnicanal con Inteligencia Artificial para la Gestión Integral de la Contactabilidad de Usuarios del Hospital Regional Coyhaique.</t>
+          <t xml:space="preserve">La Contraloría General de la República requiere contratar los servicios de soporte y mantenimiento de su plataforma de seguridad, correspondiente a Balanceador de carga y cortafuego de aplicaciones F5, para zona productiva por un periodo de 12 meses.</t>
         </is>
       </c>
       <c r="W37" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=0bdhNxuXo0yhJck3lJQQa4hM%2fiqVioa%2bZfKPiD186WrfCO7hP2ko0ICAaJJvFFfNqfuLoGJf5BeI52EPSSLZ5JgpJCt%2bVPH0LAhkZzjuxNsFQ5hoPGwQIrdsdtSz3lxE7SgZbTdH0qnZsB05yd4BJa74I0xEb9NO%2f05Eh2hH4kHkc6oTM0sDxtVKByqy5BBDFomSoOQcF%2fEwawhCwwWSPCp52D5JTBLc%2bw3etUoaMZcV0W9D6MWzRTsVv%2bGw0fBBOIAzas6epABmDRJK2ebjtSwws7w4TobxlV4ue%2bOVz9EHLGmB%2b%2fYeD2Q3A5%2bbDGrs","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=%2fRbzCKxkcHrm4e3lur%2fcNPp8pw5%2bkQ826%2bah%2fDRVhTC8DcuS9wJ9JMIAEnCUlE7lGL9XuRe%2bKLfPxqGq0deWrWClaMnTA%2b44G7Bwhn83lggEvZipXff3PjpY19UMU4y9Cz1bfC92p8U7YZI5kuSjDvvknBbbr4TmFH0Z2tn72%2fSFe7Q5Eczk2qYZRKmD%2feJX8Kvr%2bJhVKFlFfgoi6oqkS8NUxOXceKNh54WMfdSNqsyS3VnwvKuuBNALEhrSXINCkdPELwHhOFhZfNXTUSd0CyMKEjnIqGDYHz%2fWOmE6y1xKDAeBYFutnrhHRKnx07sW","descargar bases")</f>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">885-83-LE26</t>
+          <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de soporte y mantenimiento de la plataforma de seguridad F5 de la Contraloría General de la República</t>
+          <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -3996,31 +3718,35 @@
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRALORIA GENERAL DE LA REPUBLICA</t>
+          <t xml:space="preserve">SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contraloría General de la República</t>
+          <t xml:space="preserve">Hospital Curanilahue</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G38" s="0"/>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curanilahue</t>
+        </is>
+      </c>
       <c r="H38" s="2">
-        <v>46272.494688</v>
+        <v>46276.658981</v>
       </c>
       <c r="I38" s="2">
         <v>46287.666667</v>
       </c>
       <c r="J38" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K38" s="3">
-        <v>16000000.0</v>
+        <v>23152000.0</v>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
@@ -4034,21 +3760,17 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de seguridad de red</t>
+          <t xml:space="preserve">Artículos de electrónica / Circuitos electrónicos / Circuitos integrados, memorias y microprocesadores, Artículos de fabricación y producción / Artículos de ferretería / Soportes y puntales, Artículos de fabricación y producción / Cintas adhesivas y selladores / Cinta adhesiva, Artículos eléctricos y de iluminación / Equipamiento y artículos eléctricos / Equipamiento para distribución y transformación eléctrica, Equipos, accesorios y suministros de oficina / Accesorios de oficina y escritorio / Tableros o pizarras, Herramientas y maquinaria en general / Herramientas manuales / Herramientas de corte, estaje y punzones, Herramientas y maquinaria en general / Herramientas manuales / Prensas y herramientas especiales, Maquinaria para fabricación y transformación industrial / Maquinaria y suministros de procesos industriales / Dispositivos de guía, posicionamiento y sujeción</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Equipo de seguridad de red de firewall</t>
+          <t xml:space="preserve">30 Unidad · Fuentes de alimentación continua · 100 Unidad · Fuentes de alimentación continua · 30 Unidad · Fuentes de alimentación continua · y 38 más</t>
         </is>
       </c>
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
-      <c r="R38" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 meses</t>
-        </is>
-      </c>
+      <c r="R38" s="0"/>
       <c r="S38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -4057,16 +3779,16 @@
       <c r="T38" s="4"/>
       <c r="U38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristian Leon</t>
+          <t xml:space="preserve">LUIS VEGA</t>
         </is>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Contraloría General de la República requiere contratar los servicios de soporte y mantenimiento de su plataforma de seguridad, correspondiente a Balanceador de carga y cortafuego de aplicaciones F5, para zona productiva por un periodo de 12 meses.</t>
+          <t xml:space="preserve">Conforme a Ley de Compras Públicas Nº19.886, el reglamento, sus modificaciones y su modernización, el Hospital Dr. Rafael Avaria Valenzuela de Curanilahue a través del Departamento de Abastecimiento y Logística, invita a los oferentes, personas naturales o jurídicas y Uniones Temporales de Proveedores, a participar en la licitación pública para contar con una Empresa externa, que provea de bienes o servicios, para el Hospital de Curanilahue y la red del Servicio de Salud, determinado los requisitos administrativos mínimos para participar en la propuesta y garantizar con este mismo instrumento la calidad y entrega del servicio requerido.</t>
         </is>
       </c>
       <c r="W38" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=%2fRbzCKxkcHrm4e3lur%2fcNPp8pw5%2bkQ826%2bah%2fDRVhTC8DcuS9wJ9JMIAEnCUlE7lGL9XuRe%2bKLfPxqGq0deWrWClaMnTA%2b44G7Bwhn83lggEvZipXff3PjpY19UMU4y9Cz1bfC92p8U7YZI5kuSjDvvknBbbr4TmFH0Z2tn72%2fSFe7Q5Eczk2qYZRKmD%2feJX8Kvr%2bJhVKFlFfgoi6oqkS8NUxOXceKNh54WMfdSNqsyS3VnwvKuuBNALEhrSXINCkdPELwHhOFhZfNXTUSd0CyMKEjnIqGDYHz%2fWOmE6y1xKDAeBYFutnrhHRKnx07sW","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=GhxRuw0DwKRlrFqnnUTpM9l7Amaz03Fngf1u%2fLWFq57D0q6nAffUIXLAbHUXyA1Q6k1atFl%2bosiGBGrQ%2fFOockoddWQsmYmhuVyJ2rg%2be7T97Haepx81fNaqInmqVBdDl7q68NorUJzdPVjfkHq3OIyqQP1%2bksCP7cx3HnCUDcHkdjZvEzKF3ZRTZzaPQZfpV5KJjhVTI3oW7c4EHMcbT8Z0SGLJ55zcnDWovWrtKrOYtWa9MAYH6g%2bj1SAjd42nRW3WqMAQEUXYCTqV2TdDncxUWe1FsgqqFtFn626EEnONwdY%2bz0QUo0PigP%2bDCHdd","descargar bases")</f>
       </c>
     </row>
     <row r="39">
@@ -4112,7 +3834,7 @@
         <v>46288.375</v>
       </c>
       <c r="J39" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K39" s="3">
         <v>22000000.0</v>
@@ -4207,7 +3929,7 @@
         <v>46288.5</v>
       </c>
       <c r="J40" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K40" s="3">
         <v>30000000.0</v>
@@ -4306,7 +4028,7 @@
         <v>46288.5</v>
       </c>
       <c r="J41" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K41" s="3">
         <v>170000000.0</v>
@@ -4397,7 +4119,7 @@
         <v>46288.625694</v>
       </c>
       <c r="J42" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K42" s="3">
         <v>2458862.0</v>
@@ -4484,7 +4206,7 @@
         <v>46288.625694</v>
       </c>
       <c r="J43" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>30000000.0</v>
@@ -4583,7 +4305,7 @@
         <v>46288.625694</v>
       </c>
       <c r="J44" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="0" t="inlineStr">
@@ -4680,7 +4402,7 @@
         <v>46288.6875</v>
       </c>
       <c r="J45" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>2750000.0</v>
@@ -4771,7 +4493,7 @@
         <v>46288.708333</v>
       </c>
       <c r="J46" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K46" s="3">
         <v>4000000.0</v>
@@ -4858,7 +4580,7 @@
         <v>46289.555556</v>
       </c>
       <c r="J47" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="0" t="inlineStr">
@@ -4944,7 +4666,7 @@
         <v>46289.625</v>
       </c>
       <c r="J48" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K48" s="3">
         <v>295121.0</v>
@@ -5043,7 +4765,7 @@
         <v>46289.625</v>
       </c>
       <c r="J49" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K49" s="3">
         <v>30000000.0</v>
@@ -5142,7 +4864,7 @@
         <v>46289.625</v>
       </c>
       <c r="J50" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="0" t="inlineStr">
@@ -5238,7 +4960,7 @@
         <v>46289.625</v>
       </c>
       <c r="J51" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K51" s="3">
         <v>40000000.0</v>
@@ -5333,7 +5055,7 @@
         <v>46289.625</v>
       </c>
       <c r="J52" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="0" t="inlineStr">
@@ -5427,7 +5149,7 @@
         <v>46289.635417</v>
       </c>
       <c r="J53" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K53" s="3">
         <v>18688829.0</v>
@@ -5526,7 +5248,7 @@
         <v>46289.666667</v>
       </c>
       <c r="J54" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K54" s="3">
         <v>28000000.0</v>
@@ -5617,7 +5339,7 @@
         <v>46289.708333</v>
       </c>
       <c r="J55" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="0" t="inlineStr">
@@ -5710,7 +5432,7 @@
         <v>46289.729167</v>
       </c>
       <c r="J56" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56" s="3">
         <v>414000000.0</v>
@@ -5807,7 +5529,7 @@
         <v>46290.45625</v>
       </c>
       <c r="J57" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="0" t="inlineStr">
@@ -5860,12 +5582,12 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239-2-LR26</t>
+          <t xml:space="preserve">2048-57-LP26</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio Marco Desarrollo de software</t>
+          <t xml:space="preserve">Convenio de Software de Gestión de Mantenimiento</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -5875,57 +5597,57 @@
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t xml:space="preserve">SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">División de Convenio Marco</t>
+          <t xml:space="preserve">Hospital de Ancud</t>
         </is>
       </c>
       <c r="F58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G58" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santiago</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="G58" s="0"/>
       <c r="H58" s="2">
-        <v>46217.7375</v>
+        <v>46269.407778</v>
       </c>
       <c r="I58" s="2">
         <v>46290.625</v>
       </c>
       <c r="J58" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UTM</t>
+          <t xml:space="preserve">CLP</t>
         </is>
       </c>
       <c r="M58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
+          <t xml:space="preserve">1 Unidad no definida · Software de administración</t>
         </is>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" s="2"/>
-      <c r="R58" s="0"/>
+      <c r="R58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60 meses</t>
+        </is>
+      </c>
       <c r="S58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -5933,32 +5655,33 @@
       </c>
       <c r="T58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">De conformidad con el artículo 126 del Reglamento de la Ley N° 19.886, el proveedor no podrá ceder ni transferir en forma alguna, total ni parcialmente, los derechos y obligaciones que nacen del desarrollo de esta licitación y de los respectivos contrato</t>
+          <t xml:space="preserve">El adjudicatario no podrá ceder ni transferir en forma alguna, total ni parcialmente los derechos y obligaciones que nacen del desarrollo de la licitación. No se permite subcontratación</t>
         </is>
       </c>
       <c r="U58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio Marco</t>
+          <t xml:space="preserve">Gissela Arriagada Vilches</t>
         </is>
       </c>
       <c r="V58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio Marco para la adquisición de los Servicios de Desarrollo y Mantención de Software, Servicios Profesionales TI y Cloud Computing</t>
+          <t xml:space="preserve">El Hospital de Ancud ha confeccionado las siguientes Bases Administrativas, las que establecen las disposiciones administrativas que regirán la Licitación Pública a través del portal www.mercadopublico.cl y posterior contrato que celebre el Hospital de Ancud para el “SOFTWARE DE GESTION DE MANTENIMIENTO”, ID N° 2048-57-LP26.
+La descripción específica del requerimiento que se licita en este proceso se detalla en las Bases Técnicas y Anexo Técnico N°1, "ESPECIFICACIONES TÉCNICAS". Debiendo la oferta ceñirse a las descripciones y especificaciones señaladas.</t>
         </is>
       </c>
       <c r="W58" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=W1Vwpp%2fJdhNOY0y41QANMFQCinrxUJeJedneWBkOyhNN%2bXfsUXGa6o%2ftjtz6EbP%2ff2SKvWZ8q4QBssCvJQ9%2bDFw3lbLbgQw1HNTZnLz1RaX%2fgrdRtD32VKc9KO97pU1tOY0Fkz6uqnQAn6guV0F53oSjPxUfHVjWW49IVxiwl8iTC9XMKxQ6Gj6O6CpIHG6JPn48o%2fm6uoCwKlVvs2FC0fjhzhIEcyhZ925Ht83AMrjVaiyoHm3tvjiHm1LFnDz2%2bZek5ovYYqEEmsSxfZ6YUlLm4cx29xgzNSpBEbVLWCCYirUExFUR1LwAHaRCnc06","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=mWRpye04BNEzAuQq%2f355L70QpZVY9ve08qnde9H1LW%2f%2bKKdjDfSeTJ4XAn%2fkrGInnerd9y6d6Pk4uCxIPLpndy%2b1CQwd1E4U%2bBdubFkvp1y2plswtsUwXZk5XWRaaHP%2bmfH4bjRIITOg8U%2fmJAQlhXvnZdnFBg3RB%2fs5nfG5FtwylsbMA6dHdZVuMdXaMLLrjfNvyXIztk9VUmJzRb3%2bxkQltaJ2CJbqZg%2fzeplBYfbWBn6vNcTwNPkSpppeJ5EyVVCSv2LScCqxuETeKQ7RFWBJBz%2f%2bnQFiIEDrEpIkE41aw%2bnKnk1y%2f9fH5PgeHnUd","descargar bases")</f>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2563-34-LR26</t>
+          <t xml:space="preserve">2239-2-LR26</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
+          <t xml:space="preserve">Convenio Marco Desarrollo de software</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -5968,12 +5691,12 @@
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t xml:space="preserve">DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIDAD DE COMPRA CONTRATOS NACIONALES</t>
+          <t xml:space="preserve">División de Convenio Marco</t>
         </is>
       </c>
       <c r="F59" s="0" t="inlineStr">
@@ -5983,24 +5706,22 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Providencia</t>
+          <t xml:space="preserve">Santiago</t>
         </is>
       </c>
       <c r="H59" s="2">
-        <v>46254.63125</v>
+        <v>46217.7375</v>
       </c>
       <c r="I59" s="2">
         <v>46290.625</v>
       </c>
       <c r="J59" s="0">
-        <v>7</v>
-      </c>
-      <c r="K59" s="3">
-        <v>453590167.0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K59" s="3"/>
       <c r="L59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">UTM</t>
         </is>
       </c>
       <c r="M59" s="0" t="inlineStr">
@@ -6010,12 +5731,12 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 Unidad · Cajas de conmutación de computadores · 11 Unidad · Cajas de conmutación de computadores · 1 Unidad · Cajas de conmutación de computadores · y 14 más</t>
+          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
         </is>
       </c>
       <c r="P59" s="2"/>
@@ -6026,30 +5747,34 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T59" s="4"/>
+      <c r="T59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">De conformidad con el artículo 126 del Reglamento de la Ley N° 19.886, el proveedor no podrá ceder ni transferir en forma alguna, total ni parcialmente, los derechos y obligaciones que nacen del desarrollo de esta licitación y de los respectivos contrato</t>
+        </is>
+      </c>
       <c r="U59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Javier Pacheco Barahona</t>
+          <t xml:space="preserve">Convenio Marco</t>
         </is>
       </c>
       <c r="V59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE EQUIPOS DE COMUNICACIONES PARA REDES INFORMÁTICAS Y LICENCIAS DE SOFTWARE MODALIDAD LLAVE EN MANO, PARA EL PROYECTO CONTROL DE ACCESO A LA RED Y PROYECTOS AEROPORTUARIOS PARA LA DIRECCIÓN GENERAL DE AERONÁUTICA CIVIL</t>
+          <t xml:space="preserve">Convenio Marco para la adquisición de los Servicios de Desarrollo y Mantención de Software, Servicios Profesionales TI y Cloud Computing</t>
         </is>
       </c>
       <c r="W59" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=nf%2fo9avVpdX8ue7eio6GOkB9OgY420PcygOiVQtqGqgGBGwP4c%2fHd64fAn3SCLt2Rpmtp8Rr55BMGmyLJSmORZtrVw4H2bRWbAMp1afVqVVRIS2Vmk4ZYYxhvOAuv4MlDLui3tkVGEtxBiGB3bzk6Z%2bZwTmR8xaLXtb2isLET0RtgoYsT4yPyaJQq%2bpmBrSNoI61D0%2bYuV1Z2HYROfQOzsV2954l%2b5QS7ptvkr53piQFuOXLtYdDJAODCGVa1UpfoCOX0hmkkXrPJevmlnYJaDu6vd1zaPxt%2fGr2IRMbP7fo26QjZctVnQvaqZR6l%2bva","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=W1Vwpp%2fJdhNOY0y41QANMFQCinrxUJeJedneWBkOyhNN%2bXfsUXGa6o%2ftjtz6EbP%2ff2SKvWZ8q4QBssCvJQ9%2bDFw3lbLbgQw1HNTZnLz1RaX%2fgrdRtD32VKc9KO97pU1tOY0Fkz6uqnQAn6guV0F53oSjPxUfHVjWW49IVxiwl8iTC9XMKxQ6Gj6O6CpIHG6JPn48o%2fm6uoCwKlVvs2FC0fjhzhIEcyhZ925Ht83AMrjVaiyoHm3tvjiHm1LFnDz2%2bZek5ovYYqEEmsSxfZ6YUlLm4cx29xgzNSpBEbVLWCCYirUExFUR1LwAHaRCnc06","descargar bases")</f>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2785-80-LE26</t>
+          <t xml:space="preserve">2563-34-LR26</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“Servicios móviles de comunicaciones de voz y datos internet para la Municipalidad San Pedro de la Paz”</t>
+          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -6059,34 +5784,36 @@
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t xml:space="preserve">DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t xml:space="preserve">UNIDAD DE COMPRA CONTRATOS NACIONALES</t>
         </is>
       </c>
       <c r="F60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Pedro de La Paz</t>
+          <t xml:space="preserve">Providencia</t>
         </is>
       </c>
       <c r="H60" s="2">
-        <v>46276.658449</v>
+        <v>46254.63125</v>
       </c>
       <c r="I60" s="2">
         <v>46290.625</v>
       </c>
       <c r="J60" s="0">
-        <v>7</v>
-      </c>
-      <c r="K60" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="K60" s="3">
+        <v>453590167.0</v>
+      </c>
       <c r="L60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -6094,26 +5821,22 @@
       </c>
       <c r="M60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LR</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios básicos y de información pública / Telecomunicaciones / Telefonía local y de larga distancia</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Servicio telefónico local</t>
+          <t xml:space="preserve">10 Unidad · Cajas de conmutación de computadores · 11 Unidad · Cajas de conmutación de computadores · 1 Unidad · Cajas de conmutación de computadores · y 14 más</t>
         </is>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
-      <c r="R60" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 meses</t>
-        </is>
-      </c>
+      <c r="R60" s="0"/>
       <c r="S60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -6122,16 +5845,16 @@
       <c r="T60" s="4"/>
       <c r="U60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claudia Seguel Cerna</t>
+          <t xml:space="preserve">Javier Pacheco Barahona</t>
         </is>
       </c>
       <c r="V60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El objetivo de la presente licitación es contratar el equipamiento como también servicio de voz y datos móviles a directivos y/o funcionarios de la Municipalidad que sean necesarios. Esto, de acuerdo a lo establecido en las especificaciones técnicas.</t>
+          <t xml:space="preserve">ADQUISICIÓN DE EQUIPOS DE COMUNICACIONES PARA REDES INFORMÁTICAS Y LICENCIAS DE SOFTWARE MODALIDAD LLAVE EN MANO, PARA EL PROYECTO CONTROL DE ACCESO A LA RED Y PROYECTOS AEROPORTUARIOS PARA LA DIRECCIÓN GENERAL DE AERONÁUTICA CIVIL</t>
         </is>
       </c>
       <c r="W60" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=9XGglk04QQBQgN7bY4UA%2fvnuS1M2QNGMLXU5Dtg9y7VOIJ5e7YV8SGAcljJbgtE9FUeWFyEQqwy9cZplVsxFMf%2bQyOZLPgo3hbFUinEcmEonYXzKtp1KhdMul59rkRDlT%2fT0tBMW1e8ISXfj5iR6epWw52wRQ%2bt%2fe6PBDOeCXH%2fGznBU7NZL%2bRYwox6sdYS6ctoWtpM5oFBGuBQ16%2f0BoyXWLAtr2spkSAnJxHEdz8IDexfQKbBKcyVF6EMgdquuylnD1Z9SgsJvR2LgTi77tJbIY2yzA5BVW2lsyLZMNti63F7lCBhPoQqWEw65rzTu","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=nf%2fo9avVpdX8ue7eio6GOkB9OgY420PcygOiVQtqGqgGBGwP4c%2fHd64fAn3SCLt2Rpmtp8Rr55BMGmyLJSmORZtrVw4H2bRWbAMp1afVqVVRIS2Vmk4ZYYxhvOAuv4MlDLui3tkVGEtxBiGB3bzk6Z%2bZwTmR8xaLXtb2isLET0RtgoYsT4yPyaJQq%2bpmBrSNoI61D0%2bYuV1Z2HYROfQOzsV2954l%2b5QS7ptvkr53piQFuOXLtYdDJAODCGVa1UpfoCOX0hmkkXrPJevmlnYJaDu6vd1zaPxt%2fGr2IRMbP7fo26QjZctVnQvaqZR6l%2bva","descargar bases")</f>
       </c>
     </row>
     <row r="61">
@@ -6177,7 +5900,7 @@
         <v>46290.625</v>
       </c>
       <c r="J61" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K61" s="3">
         <v>10800000.0</v>
@@ -6268,7 +5991,7 @@
         <v>46290.625</v>
       </c>
       <c r="J62" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K62" s="3">
         <v>16333332.0</v>
@@ -6367,7 +6090,7 @@
         <v>46290.625</v>
       </c>
       <c r="J63" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K63" s="3">
         <v>12000000.0</v>
@@ -6418,12 +6141,12 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2048-57-LP26</t>
+          <t xml:space="preserve">2785-80-LE26</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio de Software de Gestión de Mantenimiento</t>
+          <t xml:space="preserve">“Servicios móviles de comunicaciones de voz y datos internet para la Municipalidad San Pedro de la Paz”</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -6433,28 +6156,32 @@
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE SALUD CHILOE</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospital de Ancud</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="F64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
-        </is>
-      </c>
-      <c r="G64" s="0"/>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Pedro de La Paz</t>
+        </is>
+      </c>
       <c r="H64" s="2">
-        <v>46269.407778</v>
+        <v>46276.658449</v>
       </c>
       <c r="I64" s="2">
         <v>46290.625</v>
       </c>
       <c r="J64" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="0" t="inlineStr">
@@ -6464,24 +6191,24 @@
       </c>
       <c r="M64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
+          <t xml:space="preserve">Servicios básicos y de información pública / Telecomunicaciones / Telefonía local y de larga distancia</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad no definida · Software de administración</t>
+          <t xml:space="preserve">1 Unidad · Servicio telefónico local</t>
         </is>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
       <c r="R64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">60 meses</t>
+          <t xml:space="preserve">24 meses</t>
         </is>
       </c>
       <c r="S64" s="0" t="inlineStr">
@@ -6489,24 +6216,19 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El adjudicatario no podrá ceder ni transferir en forma alguna, total ni parcialmente los derechos y obligaciones que nacen del desarrollo de la licitación. No se permite subcontratación</t>
-        </is>
-      </c>
+      <c r="T64" s="4"/>
       <c r="U64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gissela Arriagada Vilches</t>
+          <t xml:space="preserve">Claudia Seguel Cerna</t>
         </is>
       </c>
       <c r="V64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Hospital de Ancud ha confeccionado las siguientes Bases Administrativas, las que establecen las disposiciones administrativas que regirán la Licitación Pública a través del portal www.mercadopublico.cl y posterior contrato que celebre el Hospital de Ancud para el “SOFTWARE DE GESTION DE MANTENIMIENTO”, ID N° 2048-57-LP26.
-La descripción específica del requerimiento que se licita en este proceso se detalla en las Bases Técnicas y Anexo Técnico N°1, "ESPECIFICACIONES TÉCNICAS". Debiendo la oferta ceñirse a las descripciones y especificaciones señaladas.</t>
+          <t xml:space="preserve">El objetivo de la presente licitación es contratar el equipamiento como también servicio de voz y datos móviles a directivos y/o funcionarios de la Municipalidad que sean necesarios. Esto, de acuerdo a lo establecido en las especificaciones técnicas.</t>
         </is>
       </c>
       <c r="W64" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=mWRpye04BNEzAuQq%2f355L70QpZVY9ve08qnde9H1LW%2f%2bKKdjDfSeTJ4XAn%2fkrGInnerd9y6d6Pk4uCxIPLpndy%2b1CQwd1E4U%2bBdubFkvp1y2plswtsUwXZk5XWRaaHP%2bmfH4bjRIITOg8U%2fmJAQlhXvnZdnFBg3RB%2fs5nfG5FtwylsbMA6dHdZVuMdXaMLLrjfNvyXIztk9VUmJzRb3%2bxkQltaJ2CJbqZg%2fzeplBYfbWBn6vNcTwNPkSpppeJ5EyVVCSv2LScCqxuETeKQ7RFWBJBz%2f%2bnQFiIEDrEpIkE41aw%2bnKnk1y%2f9fH5PgeHnUd","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=oaE3vvwiTIlFDSSw0YqricjyH2Wq%2bUK0bEL4YPWdgOctW1ki8NIQRUUYq6JsY7P9jIbHatuiIHKeXygbN9v2tC4lk8trnGkaO5x4sHEueFHju3j7NplCEXCuT0taRZZWt1YsIVBEVfX8l0zKuGdx12Bu0X7gD7guv5ZOAoaq8PmjeqC6O50gkgre0yFRztFiS0U%2fuapxKxuJrhjUVI%2frSC4n4j1KIwjxAdlg7U664%2b3HYiCpSm7IFtDKutGbqgBegytKZ3uiRfWvfwJkrmPFMqE3iqoyd40LUK%2fPe9juqBg3QbBqpoCAyK2sQ5iXnTf5","descargar bases")</f>
       </c>
     </row>
     <row r="65">
@@ -6552,7 +6274,7 @@
         <v>46290.625694</v>
       </c>
       <c r="J65" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K65" s="3"/>
       <c r="L65" s="0" t="inlineStr">
@@ -6645,7 +6367,7 @@
         <v>46290.625694</v>
       </c>
       <c r="J66" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="0" t="inlineStr">
@@ -6743,7 +6465,7 @@
         <v>46290.636111</v>
       </c>
       <c r="J67" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K67" s="3">
         <v>3201100.0</v>
@@ -6830,7 +6552,7 @@
         <v>46290.645833</v>
       </c>
       <c r="J68" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K68" s="3">
         <v>12000000.0</v>
@@ -6926,7 +6648,7 @@
         <v>46290.666667</v>
       </c>
       <c r="J69" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="0" t="inlineStr">
@@ -7015,7 +6737,7 @@
         <v>46290.666667</v>
       </c>
       <c r="J70" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K70" s="3">
         <v>35000000.0</v>
@@ -7110,7 +6832,7 @@
         <v>46293.625</v>
       </c>
       <c r="J71" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K71" s="3">
         <v>75000000.0</v>
@@ -7209,7 +6931,7 @@
         <v>46293.625</v>
       </c>
       <c r="J72" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="0" t="inlineStr">
@@ -7298,7 +7020,7 @@
         <v>46293.625</v>
       </c>
       <c r="J73" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K73" s="3">
         <v>37984000.0</v>
@@ -7389,7 +7111,7 @@
         <v>46293.625694</v>
       </c>
       <c r="J74" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K74" s="3"/>
       <c r="L74" s="0" t="inlineStr">
@@ -7478,7 +7200,7 @@
         <v>46293.625694</v>
       </c>
       <c r="J75" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K75" s="3"/>
       <c r="L75" s="0" t="inlineStr">
@@ -7576,7 +7298,7 @@
         <v>46293.631944</v>
       </c>
       <c r="J76" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K76" s="3"/>
       <c r="L76" s="0" t="inlineStr">
@@ -7673,7 +7395,7 @@
         <v>46293.645833</v>
       </c>
       <c r="J77" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K77" s="3">
         <v>450000000.0</v>
@@ -7768,7 +7490,7 @@
         <v>46293.645833</v>
       </c>
       <c r="J78" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K78" s="3">
         <v>60000000.0</v>
@@ -7827,12 +7549,12 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">726931-1-LE26</t>
+          <t xml:space="preserve">948354-135-LP26</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLATAFORMA INTEGRAL ALUMNI Y EMPLEABILIDAD UTA</t>
+          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE UNA CABINA SANITARIA CON EQUIPO MAMÓGRAFO PARA USO DE MAMOGRAFÍA DIGITALIZADA PORTÁTIL PARA EL HOSPITAL DIPRECA</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -7842,36 +7564,34 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIVERSIDAD DE TARAPACA</t>
+          <t xml:space="preserve">FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direccion General de  Vinculacion con el Medio</t>
+          <t xml:space="preserve">Unidad de Compra de Bienes y Servicios</t>
         </is>
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Arica y Parinacota</t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arica</t>
+          <t xml:space="preserve">Las Condes</t>
         </is>
       </c>
       <c r="H79" s="2">
-        <v>46269.717674</v>
+        <v>46272.689421</v>
       </c>
       <c r="I79" s="2">
         <v>46293.666667</v>
       </c>
       <c r="J79" s="0">
-        <v>10</v>
-      </c>
-      <c r="K79" s="3">
-        <v>15000000.0</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K79" s="3"/>
       <c r="L79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -7879,55 +7599,55 @@
       </c>
       <c r="M79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Productos para imágenes y de medicina nuclear / Artículos radiográficos de diagnóstico médico</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Software de desarrollo de plataforma Web</t>
+          <t xml:space="preserve">12 Mes · Equipo para radiografías mamográficas</t>
         </is>
       </c>
       <c r="P79" s="2"/>
       <c r="Q79" s="2"/>
-      <c r="R79" s="0"/>
+      <c r="R79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 meses</t>
+        </is>
+      </c>
       <c r="S79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">De acuerdo al Capítulo VIII Contrato de suministro y servicio, párrafo 4 Cesión y subcontratación, Artículo 128. Subcontratación del reglamento de Ley Nº 19.886 sobre compras públicas.</t>
-        </is>
-      </c>
+      <c r="T79" s="4"/>
       <c r="U79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniela González Erber</t>
+          <t xml:space="preserve">Dra. Constanza Damm Araneda</t>
         </is>
       </c>
       <c r="V79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Universidad de Tarapacá solicita la adquisición de servicio de plataforma integral ALUMNI y empleabilidad por un periodo de 24 meses de duración, según especificaciones técnicas descritas en el Anexo N°1. Asociada a la SC N° 2026070283.</t>
+          <t xml:space="preserve">El Hospital de la Dirección de Previsión de Carabineros de Chile, ubicado en Vital Apoquindo N°1.200, Comuna de Las Condes, Región Metropolitana, en adelante “EL HOSPITAL”, llama a licitación pública para la Contratación del Servicio de Arriendo de una Cabina Sanitaria con Equipo Mamógrafo para Uso de Mamografía Digitalizada Portátil, en adelante “EL SERVICIO”, para un período de 12 meses, esta contratación se ejecutará bajo la modalidad de Contrato de Suministro para el referido Centro Asistencial, cuyas características y requisitos técnicos constan en las Bases Administrativas y Técnicas de esta Licitación con sus respectivos anexos.</t>
         </is>
       </c>
       <c r="W79" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=%2bQn%2fyIJgMzfIWIthkfmNwZyh7gLcVYGBN8fomuDHc8fSfTV8t2axLXyNFvplUuczuZAEbWptYaQUVkwGdaJ2wgsW4LAJL6BPXkEBWDoYdc%2bXwDATB3nftlfJ62C%2bgbJz0jJO2zuO%2f%2bLkWTWrVgs9iy0RebjVhy2NehKKtrVem%2ftEGiCupnyncGnBWKcli09HFpWgc%2bOiuV0IxAvU2arBEX4i3ielepljVJc9dZ%2forJgqrbrAt%2fOozRU%2fY37j8r3HwyZ5AhCNzcESv5pyHE%2b1UPmkTVm12do39dmcCei3RsWD956is9h5OhcotHGkQC5o","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=PizkyRsEyLHQbR4bpkP53HNmo%2fTtu1%2btSenUTCoJTTxS7O3sMVkt7xQyhBtcv6RkiQF7vXZnVNyzWX%2bnbOmKaFRPFkG2jLdJU6JTfbibKweBaLDvtDHmRv3y5dfz%2bdhjmqQrGr7amkkGLUKArjPxiHSkS6k8djZ4lC3tTrLr0NkQxSz%2f28dNUhAvQSP83IS26aZVh2yonclCpBtpE%2fwo9fVuuN22ZMt1FTDbXkUARGcqGfkzfs01yjFLt3v50430tOEOb%2fSNbShiv03VAFhM9c70IknkqiKHk6a2lPfMj5wBvRxZnqCnKGY6BGhWfnYd","descargar bases")</f>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">948354-135-LP26</t>
+          <t xml:space="preserve">726931-1-LE26</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE UNA CABINA SANITARIA CON EQUIPO MAMÓGRAFO PARA USO DE MAMOGRAFÍA DIGITALIZADA PORTÁTIL PARA EL HOSPITAL DIPRECA</t>
+          <t xml:space="preserve">PLATAFORMA INTEGRAL ALUMNI Y EMPLEABILIDAD UTA</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -7937,34 +7657,36 @@
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t xml:space="preserve">UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad de Compra de Bienes y Servicios</t>
+          <t xml:space="preserve">Direccion General de  Vinculacion con el Medio</t>
         </is>
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de Arica y Parinacota</t>
         </is>
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Condes</t>
+          <t xml:space="preserve">Arica</t>
         </is>
       </c>
       <c r="H80" s="2">
-        <v>46272.689421</v>
+        <v>46269.717674</v>
       </c>
       <c r="I80" s="2">
         <v>46293.666667</v>
       </c>
       <c r="J80" s="0">
-        <v>10</v>
-      </c>
-      <c r="K80" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="K80" s="3">
+        <v>15000000.0</v>
+      </c>
       <c r="L80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -7972,44 +7694,44 @@
       </c>
       <c r="M80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento y suministros médicos / Productos para imágenes y de medicina nuclear / Artículos radiográficos de diagnóstico médico</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 Mes · Equipo para radiografías mamográficas</t>
+          <t xml:space="preserve">1 Global · Software de desarrollo de plataforma Web</t>
         </is>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" s="2"/>
-      <c r="R80" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 meses</t>
-        </is>
-      </c>
+      <c r="R80" s="0"/>
       <c r="S80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T80" s="4"/>
+      <c r="T80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">De acuerdo al Capítulo VIII Contrato de suministro y servicio, párrafo 4 Cesión y subcontratación, Artículo 128. Subcontratación del reglamento de Ley Nº 19.886 sobre compras públicas.</t>
+        </is>
+      </c>
       <c r="U80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dra. Constanza Damm Araneda</t>
+          <t xml:space="preserve">Daniela González Erber</t>
         </is>
       </c>
       <c r="V80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Hospital de la Dirección de Previsión de Carabineros de Chile, ubicado en Vital Apoquindo N°1.200, Comuna de Las Condes, Región Metropolitana, en adelante “EL HOSPITAL”, llama a licitación pública para la Contratación del Servicio de Arriendo de una Cabina Sanitaria con Equipo Mamógrafo para Uso de Mamografía Digitalizada Portátil, en adelante “EL SERVICIO”, para un período de 12 meses, esta contratación se ejecutará bajo la modalidad de Contrato de Suministro para el referido Centro Asistencial, cuyas características y requisitos técnicos constan en las Bases Administrativas y Técnicas de esta Licitación con sus respectivos anexos.</t>
+          <t xml:space="preserve">La Universidad de Tarapacá solicita la adquisición de servicio de plataforma integral ALUMNI y empleabilidad por un periodo de 24 meses de duración, según especificaciones técnicas descritas en el Anexo N°1. Asociada a la SC N° 2026070283.</t>
         </is>
       </c>
       <c r="W80" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=PizkyRsEyLHQbR4bpkP53HNmo%2fTtu1%2btSenUTCoJTTxS7O3sMVkt7xQyhBtcv6RkiQF7vXZnVNyzWX%2bnbOmKaFRPFkG2jLdJU6JTfbibKweBaLDvtDHmRv3y5dfz%2bdhjmqQrGr7amkkGLUKArjPxiHSkS6k8djZ4lC3tTrLr0NkQxSz%2f28dNUhAvQSP83IS26aZVh2yonclCpBtpE%2fwo9fVuuN22ZMt1FTDbXkUARGcqGfkzfs01yjFLt3v50430tOEOb%2fSNbShiv03VAFhM9c70IknkqiKHk6a2lPfMj5wBvRxZnqCnKGY6BGhWfnYd","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=z4zzwn4HqD7VLNVdcGhb%2bgdzQZ13GW%2bQLVGq4GmUSs2ZDqo9LPg8a0TknPHTpt57fTf9BM2rD7ORg8vsaAiGUNReVrzkKj1rWnMiIgq4fTT7MxhSi%2faw5y9Jyuos94oBBIIIZ6XsImLbfDvNY%2bqP3lfbTaw%2bj4gV5Oi2d%2bpeYtUmrYi2J6uLx3V6oG3fvSEzJNCTryqvTKuVGPE229BH0keak8Aq1tpYFxfiW%2f76cWL9oBsgWGoVKhTj5Molzsh2NLq3VhFeAJEdGMJt6NPgEGOJz4aA%2bUZYoCafIVKTuNDA7UVfKb96k7D8TFuEZu70","descargar bases")</f>
       </c>
     </row>
     <row r="81">
@@ -8055,7 +7777,7 @@
         <v>46293.708333</v>
       </c>
       <c r="J81" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K81" s="3">
         <v>60000000.0</v>
@@ -8150,7 +7872,7 @@
         <v>46293.708333</v>
       </c>
       <c r="J82" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K82" s="3">
         <v>20000000.0</v>
@@ -8195,7 +7917,7 @@
         </is>
       </c>
       <c r="W82" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=yq1a6kEfiEcOW%2baW%2fcAs89NSir8xI6v%2bMR6us%2bJYnYxSmFHKkAkffybhGbZwSeMrz8o%2b8YdrBasej%2fGMqM9igy02C7WOSssZCfYk37ehe3ijIx0g8FYWQdtFKLWlT4i%2bnQsfty%2ft2yBOEL0Lut6iuWsuNFaoMReSb9Y%2fCjH6ptPXLIDGiINm%2br9E3yUumrtUGj1ZUhAmKE41lAby%2fBv31%2fMNS%2bUHkpiKTpCmHYU9djWHqZFLFLt2ccwznplRnERaV11vnEgkcuYVpsMoIBWsOJxzWfB5I7zSfwbyYI9%2bUJ1D6dqNKP56ObJ8iH6A1s34","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=d2LokpfJX16u1NpHBIWwNwmbPemjQJAnArhPZ4D3RCdAz0xc7tnhzTvCuvj2UbwhMgE1kyB9AxXwjzqHhUUa8eW3g2D%2fhCE4WtD6J4B591j3blXWsfKuRNsZ289jKRnga%2b%2bLi2fGjXuLW4c3bk1IUcArA35M89rgdvlJWQjD81dnFrwIfETmJFBqNMePfQgyOj8l%2bHmBltTJhYHS3XTFWJYq406CGI4AgzKqx6UjNLmnm%2bEti202GJu3t2bqMYoh7rinUweGj1dtAqz4pWUEEXORXwXcYtCh9K8R8sYIrFX41f%2bRTvXSHJJRqNeB9Ps5","descargar bases")</f>
       </c>
     </row>
     <row r="83">
@@ -8237,7 +7959,7 @@
         <v>46293.75</v>
       </c>
       <c r="J83" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K83" s="3"/>
       <c r="L83" s="0" t="inlineStr">
@@ -8335,7 +8057,7 @@
         <v>46294.5</v>
       </c>
       <c r="J84" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K84" s="3">
         <v>58000000.0</v>
@@ -8426,7 +8148,7 @@
         <v>46294.625</v>
       </c>
       <c r="J85" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K85" s="3">
         <v>240000000.0</v>
@@ -8485,12 +8207,12 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3970-8-LE26</t>
+          <t xml:space="preserve">1575-15-LE26</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">01 SISTEMA DE EVIDENCIA DIGITAL Y ACCESORIOS OS9</t>
+          <t xml:space="preserve">MANTENCION DE EQUIPOS INFORMATICOS</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -8500,35 +8222,35 @@
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t xml:space="preserve">JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Depto.I.O.Crim.O.S.9</t>
+          <t xml:space="preserve">Junji - VI Región</t>
         </is>
       </c>
       <c r="F86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ñuñoa</t>
+          <t xml:space="preserve">Rancagua</t>
         </is>
       </c>
       <c r="H86" s="2">
-        <v>46272.691389</v>
+        <v>46282.520417</v>
       </c>
       <c r="I86" s="2">
         <v>46294.625</v>
       </c>
       <c r="J86" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K86" s="3">
-        <v>15111040.0</v>
+        <v>22000000.0</v>
       </c>
       <c r="L86" s="0" t="inlineStr">
         <is>
@@ -8542,17 +8264,21 @@
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Componentes para tecnología de la información, difusión o telecomunicaciones / Módulos, interfaces, procesadores y placas de sistema</t>
+          <t xml:space="preserve">Equipos, accesorios y suministros de oficina / Maquinarias, suministros y accesorios de oficina / Multicopistas, fotocopiadoras, fax y multifuncionales</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Adaptadores de telefonía o hardware</t>
+          <t xml:space="preserve">1 Unidad · Fotocopiadoras</t>
         </is>
       </c>
       <c r="P86" s="2"/>
       <c r="Q86" s="2"/>
-      <c r="R86" s="0"/>
+      <c r="R86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 meses</t>
+        </is>
+      </c>
       <c r="S86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -8561,27 +8287,27 @@
       <c r="T86" s="4"/>
       <c r="U86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDO BOZO MARTINEZ</t>
+          <t xml:space="preserve">MYRIAM POBLETE</t>
         </is>
       </c>
       <c r="V86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOFTWARE DE EXTRACCION DE INFORMACION DIVERSOS SISTEMAS DIGITALES CON SUS ACCESORIOS DE ADAPTADORES COMPLETOS</t>
+          <t xml:space="preserve">La Junta Nacional de Jardines Infantiles, en adelante (JUNJI), requiere la “CONTRATO DE SUMINISTRO DE MANTENCION Y REPARACION DE IMPRESORAS, ESCANERS, PLOTTERS, PROYECTORES PARA JARDINES INFANTILES Y OFICINAS PARA JUNJI DE LA REGIÓN DE O´HIGGINS”.</t>
         </is>
       </c>
       <c r="W86" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=nN%2bgbeGBHb%2bfYhHLvbDdiiMEzq2dzfxw3BLnf9UeXwOpQLZmdtxWCwcBrfC3ZFA3NgNL4Fcs1XI3EXMZn5qg2sZQTudMloMvao7tB727UtcCbmvmRPVJCxlXDm%2fZ%2fV%2fQ1JDjklR3sCW25N9wcjVfYYrAvZONxuR%2fIccnu5Zo2uuJfAVy3rHL6pXQ%2fDbfzC2iK8VNeyoldCaDq281ZCKOt7HPZSjkuYphF0RicrwhbKdhKFmmHK0j2vq8%2bRdszuhAjc9SmvPSS3tLUqYiWDBZISDrv1Fggo0zceaZPNl%2byWC6JTU1YcZQm5RQX0d9gliw","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=wU4MDrgKqWaKDooFSdi3SvTmXasqYfZAqvBwNJ5sWSdexlALTsg6MrDjp7f36OnPeeLtEgfep6bZEIKK%2bqL%2bQkv2OT4B%2bmQ42nAR17TdAZVmqjNXzspzTsLbwBmOEIX%2fKKQwNtjaFTI5gNTvRvpBblLTC6Oh0yXEL%2fs65gV7Xz01tzlIv4z7WlTxe030P8z%2b9QuRRelzjsQXhQIgOTzqgU2f1aPsVH3rIyC9SHhfKc%2f9VWCPgQpC4f6A1DJ7F%2b5YhVmeSGZNGanyCuEZ46ZJs23jw95yOXP001sVIdZEkysj0jphdH%2beJEEWvQX2AKEz","descargar bases")</f>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5394-22-LE26</t>
+          <t xml:space="preserve">3970-8-LE26</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE CONSULTORÍA DE CIBERSEGURIDAD UMAG</t>
+          <t xml:space="preserve">01 SISTEMA DE EVIDENCIA DIGITAL Y ACCESORIOS OS9</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -8591,35 +8317,35 @@
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIVERSIDAD DE MAGALLANES</t>
+          <t xml:space="preserve">DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROYECTOS CON TERCEROS (D/583)</t>
+          <t xml:space="preserve">Depto.I.O.Crim.O.S.9</t>
         </is>
       </c>
       <c r="F87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Magallanes y de la Antártica</t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Punta Arenas</t>
+          <t xml:space="preserve">Ñuñoa</t>
         </is>
       </c>
       <c r="H87" s="2">
-        <v>46274.672569</v>
+        <v>46272.691389</v>
       </c>
       <c r="I87" s="2">
         <v>46294.625</v>
       </c>
       <c r="J87" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K87" s="3">
-        <v>20000000.0</v>
+        <v>15111040.0</v>
       </c>
       <c r="L87" s="0" t="inlineStr">
         <is>
@@ -8633,55 +8359,46 @@
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Consultorías o asesorías en gestión empresarial / Servicios de consultoría en gestión de empresas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Componentes para tecnología de la información, difusión o telecomunicaciones / Módulos, interfaces, procesadores y placas de sistema</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Asesorías Informáticas</t>
+          <t xml:space="preserve">1 Unidad · Adaptadores de telefonía o hardware</t>
         </is>
       </c>
       <c r="P87" s="2"/>
       <c r="Q87" s="2"/>
-      <c r="R87" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 semanas</t>
-        </is>
-      </c>
+      <c r="R87" s="0"/>
       <c r="S87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9. SUBCONTRATACION
-Por la naturaleza de los servicios, no se permite la subcontratación en la presente licitación.</t>
-        </is>
-      </c>
+      <c r="T87" s="4"/>
       <c r="U87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIDAD ABASTECIMIENTO</t>
+          <t xml:space="preserve">FERNANDO BOZO MARTINEZ</t>
         </is>
       </c>
       <c r="V87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La presente contratación de Servicios de Consultoría para la realización de un Diagnóstico del estado de Ciberseguridad Institucional, la cual se enmarca en la ejecución del Convenio de Desempeño Fortalecimiento de la Gestión Administrativa Institucional: Desarrollo de Capacidades Institucionales para una Gestión Orientada a la Calidad, Código MAG24992.</t>
+          <t xml:space="preserve">SOFTWARE DE EXTRACCION DE INFORMACION DIVERSOS SISTEMAS DIGITALES CON SUS ACCESORIOS DE ADAPTADORES COMPLETOS</t>
         </is>
       </c>
       <c r="W87" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=z%2fpEvmEuspgV6wD0VH7PNbswhYuSbUcAFmu%2fKmZPgUO3%2fENbxzbNi0G0PvKWmt%2f4gV4vsR%2fSBvWxmtXQlvBrRFkK6m1%2fTCsGuvAFnTIX%2fZ7xYrPLGd1w4iWdA6cRQTMeAs%2fUeNYnHDm%2bCtJn9kwLS7q2OpBKbj8kxi5YMpb9d8FalfySVCimTKY07qoANRrag4BTiPS6ybLXHSFVmaVO7VFQcHcvN6oBeckl16Y29L1UeKgmzilwTdz%2fIDi%2fLQeuikHScwZx1XA01DdOHYmHO7Vmuc%2frY%2fkRsmIpSUiE5ECMYQ1FR076r4yM4cunO5vP","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=nN%2bgbeGBHb%2bfYhHLvbDdiiMEzq2dzfxw3BLnf9UeXwOpQLZmdtxWCwcBrfC3ZFA3NgNL4Fcs1XI3EXMZn5qg2sZQTudMloMvao7tB727UtcCbmvmRPVJCxlXDm%2fZ%2fV%2fQ1JDjklR3sCW25N9wcjVfYYrAvZONxuR%2fIccnu5Zo2uuJfAVy3rHL6pXQ%2fDbfzC2iK8VNeyoldCaDq281ZCKOt7HPZSjkuYphF0RicrwhbKdhKFmmHK0j2vq8%2bRdszuhAjc9SmvPSS3tLUqYiWDBZISDrv1Fggo0zceaZPNl%2byWC6JTU1YcZQm5RQX0d9gliw","descargar bases")</f>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575-15-LE26</t>
+          <t xml:space="preserve">5394-22-LE26</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANTENCION DE EQUIPOS INFORMATICOS</t>
+          <t xml:space="preserve">SERVICIO DE CONSULTORÍA DE CIBERSEGURIDAD UMAG</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -8691,35 +8408,35 @@
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t xml:space="preserve">UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junji - VI Región</t>
+          <t xml:space="preserve">PROYECTOS CON TERCEROS (D/583)</t>
         </is>
       </c>
       <c r="F88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Libertador General Bernardo O´Higgins</t>
+          <t xml:space="preserve">Región de Magallanes y de la Antártica</t>
         </is>
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rancagua</t>
+          <t xml:space="preserve">Punta Arenas</t>
         </is>
       </c>
       <c r="H88" s="2">
-        <v>46282.520417</v>
+        <v>46274.672569</v>
       </c>
       <c r="I88" s="2">
         <v>46294.625</v>
       </c>
       <c r="J88" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K88" s="3">
-        <v>22000000.0</v>
+        <v>20000000.0</v>
       </c>
       <c r="L88" s="0" t="inlineStr">
         <is>
@@ -8733,19 +8450,19 @@
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipos, accesorios y suministros de oficina / Maquinarias, suministros y accesorios de oficina / Multicopistas, fotocopiadoras, fax y multifuncionales</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Consultorías o asesorías en gestión empresarial / Servicios de consultoría en gestión de empresas</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Fotocopiadoras</t>
+          <t xml:space="preserve">1 Global · Asesorías Informáticas</t>
         </is>
       </c>
       <c r="P88" s="2"/>
       <c r="Q88" s="2"/>
       <c r="R88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 meses</t>
+          <t xml:space="preserve">12 semanas</t>
         </is>
       </c>
       <c r="S88" s="0" t="inlineStr">
@@ -8753,19 +8470,24 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T88" s="4"/>
+      <c r="T88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. SUBCONTRATACION
+Por la naturaleza de los servicios, no se permite la subcontratación en la presente licitación.</t>
+        </is>
+      </c>
       <c r="U88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MYRIAM POBLETE</t>
+          <t xml:space="preserve">UNIDAD ABASTECIMIENTO</t>
         </is>
       </c>
       <c r="V88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Junta Nacional de Jardines Infantiles, en adelante (JUNJI), requiere la “CONTRATO DE SUMINISTRO DE MANTENCION Y REPARACION DE IMPRESORAS, ESCANERS, PLOTTERS, PROYECTORES PARA JARDINES INFANTILES Y OFICINAS PARA JUNJI DE LA REGIÓN DE O´HIGGINS”.</t>
+          <t xml:space="preserve">La presente contratación de Servicios de Consultoría para la realización de un Diagnóstico del estado de Ciberseguridad Institucional, la cual se enmarca en la ejecución del Convenio de Desempeño Fortalecimiento de la Gestión Administrativa Institucional: Desarrollo de Capacidades Institucionales para una Gestión Orientada a la Calidad, Código MAG24992.</t>
         </is>
       </c>
       <c r="W88" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=wU4MDrgKqWaKDooFSdi3SvTmXasqYfZAqvBwNJ5sWSdexlALTsg6MrDjp7f36OnPeeLtEgfep6bZEIKK%2bqL%2bQkv2OT4B%2bmQ42nAR17TdAZVmqjNXzspzTsLbwBmOEIX%2fKKQwNtjaFTI5gNTvRvpBblLTC6Oh0yXEL%2fs65gV7Xz01tzlIv4z7WlTxe030P8z%2b9QuRRelzjsQXhQIgOTzqgU2f1aPsVH3rIyC9SHhfKc%2f9VWCPgQpC4f6A1DJ7F%2b5YhVmeSGZNGanyCuEZ46ZJs23jw95yOXP001sVIdZEkysj0jphdH%2beJEEWvQX2AKEz","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=z%2fpEvmEuspgV6wD0VH7PNbswhYuSbUcAFmu%2fKmZPgUO3%2fENbxzbNi0G0PvKWmt%2f4gV4vsR%2fSBvWxmtXQlvBrRFkK6m1%2fTCsGuvAFnTIX%2fZ7xYrPLGd1w4iWdA6cRQTMeAs%2fUeNYnHDm%2bCtJn9kwLS7q2OpBKbj8kxi5YMpb9d8FalfySVCimTKY07qoANRrag4BTiPS6ybLXHSFVmaVO7VFQcHcvN6oBeckl16Y29L1UeKgmzilwTdz%2fIDi%2fLQeuikHScwZx1XA01DdOHYmHO7Vmuc%2frY%2fkRsmIpSUiE5ECMYQ1FR076r4yM4cunO5vP","descargar bases")</f>
       </c>
     </row>
     <row r="89">
@@ -8811,7 +8533,7 @@
         <v>46294.708333</v>
       </c>
       <c r="J89" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K89" s="3">
         <v>113050000.0</v>
@@ -8906,7 +8628,7 @@
         <v>46295.416667</v>
       </c>
       <c r="J90" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K90" s="3">
         <v>27000000.0</v>
@@ -8997,7 +8719,7 @@
         <v>46295.5</v>
       </c>
       <c r="J91" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K91" s="3">
         <v>94099000.0</v>
@@ -9092,7 +8814,7 @@
         <v>46295.625</v>
       </c>
       <c r="J92" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K92" s="3">
         <v>160000000.0</v>
@@ -9189,7 +8911,7 @@
         <v>46295.625</v>
       </c>
       <c r="J93" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K93" s="3">
         <v>24000.0</v>
@@ -9289,7 +9011,7 @@
         <v>46295.625694</v>
       </c>
       <c r="J94" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K94" s="3"/>
       <c r="L94" s="0" t="inlineStr">
@@ -9383,7 +9105,7 @@
         <v>46295.625694</v>
       </c>
       <c r="J95" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K95" s="3">
         <v>130132269.0</v>
@@ -9479,7 +9201,7 @@
         <v>46295.645833</v>
       </c>
       <c r="J96" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K96" s="3">
         <v>98588644.0</v>
@@ -9570,7 +9292,7 @@
         <v>46295.645833</v>
       </c>
       <c r="J97" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K97" s="3"/>
       <c r="L97" s="0" t="inlineStr">
@@ -9627,12 +9349,12 @@
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4051-16-LP26</t>
+          <t xml:space="preserve">591-26-LP26</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO ADMINISTRADO DE INTERNET RED DE DATOS Y</t>
+          <t xml:space="preserve">PLATAFORMA DE OBSERVABILIDAD AVANZADA MULTICLOUD PARA FONASA.</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
@@ -9642,37 +9364,33 @@
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE OLLAGUE</t>
+          <t xml:space="preserve">FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Municipalidad de Ollagüe</t>
+          <t xml:space="preserve">FONASA, Nivel Central</t>
         </is>
       </c>
       <c r="F98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
-        </is>
-      </c>
-      <c r="G98" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ollague</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G98" s="0"/>
       <c r="H98" s="2">
-        <v>46269.531944</v>
+        <v>46275.725197</v>
       </c>
       <c r="I98" s="2">
         <v>46295.666667</v>
       </c>
       <c r="J98" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K98" s="3"/>
       <c r="L98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLF</t>
+          <t xml:space="preserve">CLP</t>
         </is>
       </c>
       <c r="M98" s="0" t="inlineStr">
@@ -9682,19 +9400,19 @@
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Servicios para internet</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Proveedores de servicio de Internet (ISP)</t>
+          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
         </is>
       </c>
       <c r="P98" s="2"/>
       <c r="Q98" s="2"/>
       <c r="R98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">48 meses</t>
+          <t xml:space="preserve">15 meses</t>
         </is>
       </c>
       <c r="S98" s="0" t="inlineStr">
@@ -9705,27 +9423,27 @@
       <c r="T98" s="4"/>
       <c r="U98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jhean Ramírez Domínguez</t>
+          <t xml:space="preserve">Marcelo Gonzalez</t>
         </is>
       </c>
       <c r="V98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Municipio requiere contratar el Servicio Administrado de Internet, Red de Datos y Telefonía IP para la Ilustre Municipalidad de Ollagüe y que implica la ejecución de diseños preliminares, adquisición de materiales, instalación, montaje, configuración y puesta en servicio con el objeto de garantizar el funcionamiento óptimo de la infraestructura de red en las dependencias de la municipalidad.</t>
+          <t xml:space="preserve">El Oferente para la provisión de una plataforma de observabilidad SaaS y la prestación de servicios profesionales especializados para su configuración, despliegue multicloud y transferencia tecnológica</t>
         </is>
       </c>
       <c r="W98" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=bN%2fADaRl2ZA4kvbpevgjrWamBm254kc4R5MgM08YzaBzZu5%2biCLJUxZSe2aTO344tx%2bnJUfJiVLOxTbxjiBluzvTAJtHhN5JyBr5kuuLNv66vldFlvKGKSrYzGG963qRmSNv8CkZw2LezKCw4C1zRxH400012CKj0DUivwN7M3MrCs2xkVGnYqbZoDkkCO17czrn6wxJDf8p4tEhTAlLIJQYr4GdrMkc%2fZRRbsFc%2b2wO8fbZbuxYSUHIrgJ2XIB7elRZQgoyky49vIpHzDlVu0PE%2fVpJxIWxHk7qiUpDPICJTRbCh1sK1il6wgsPlHk3","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=2YWlXcmnfIyNPygiOlS%2fSWhbmqfI8mNI104%2b8fYRw1zEaNPhuYhWXGu7CkPqkCgK65B8wcmJW%2f9EUSYTT%2b3720CHCNAgUqCwzZLt0wBjC4iy0cyITJBHvo%2fT3Tz2G3b7%2fl96q5dr7xnGBKDa6LuQyVBoUaPQJpF10I8j9i3NKXMmCd6055pUxaXRCfinxw10eh1Gpifh1wEW6NmZtu14MMFA1V%2fFqTmUdXUF0%2foJHlr%2fp7ZExvSmp%2fV4W0%2fMOApllWUzcW2GQWzZykS1Uo8GYvRS2TU5OGz7LgKOrROhwVMo7SDor6PfaGuZkrmbzCF6","descargar bases")</f>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">591-26-LP26</t>
+          <t xml:space="preserve">885-84-LE26</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLATAFORMA DE OBSERVABILIDAD AVANZADA MULTICLOUD PARA FONASA.</t>
+          <t xml:space="preserve">Soporte mantención y monitoreo plataforma legacy IBM Spectrum para la Contraloría General de la República</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
@@ -9735,12 +9453,12 @@
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">FONDO NACIONAL DE SALUD</t>
+          <t xml:space="preserve">CONTRALORIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">FONASA, Nivel Central</t>
+          <t xml:space="preserve">Contraloría General de la República</t>
         </is>
       </c>
       <c r="F99" s="0" t="inlineStr">
@@ -9750,15 +9468,17 @@
       </c>
       <c r="G99" s="0"/>
       <c r="H99" s="2">
-        <v>46275.725197</v>
+        <v>46280.726771</v>
       </c>
       <c r="I99" s="2">
         <v>46295.666667</v>
       </c>
       <c r="J99" s="0">
-        <v>12</v>
-      </c>
-      <c r="K99" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="K99" s="3">
+        <v>30000000.0</v>
+      </c>
       <c r="L99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -9766,24 +9486,24 @@
       </c>
       <c r="M99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
+          <t xml:space="preserve">1 Global · Mantenimiento y soporte de hardware</t>
         </is>
       </c>
       <c r="P99" s="2"/>
       <c r="Q99" s="2"/>
       <c r="R99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 meses</t>
+          <t xml:space="preserve">12 meses</t>
         </is>
       </c>
       <c r="S99" s="0" t="inlineStr">
@@ -9794,27 +9514,27 @@
       <c r="T99" s="4"/>
       <c r="U99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcelo Gonzalez</t>
+          <t xml:space="preserve">Antonio Alejandro Alcázar Garrido</t>
         </is>
       </c>
       <c r="V99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Oferente para la provisión de una plataforma de observabilidad SaaS y la prestación de servicios profesionales especializados para su configuración, despliegue multicloud y transferencia tecnológica</t>
+          <t xml:space="preserve">Contratar el servicio de Soporte, Mantenimiento y Monitoreo de la plataforma de respaldo legacy de la Contraloría General de la República, la cual se encuentra integrada con servidores y librerías robotizadas, y dispone de políticas de acceso, reportes generales y personalizados, además de funciones de monitoreo. Este servicio resulta crítico para la conservación histórica de respaldos de los servicios TIC institucionales.</t>
         </is>
       </c>
       <c r="W99" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=2YWlXcmnfIyNPygiOlS%2fSWhbmqfI8mNI104%2b8fYRw1zEaNPhuYhWXGu7CkPqkCgK65B8wcmJW%2f9EUSYTT%2b3720CHCNAgUqCwzZLt0wBjC4iy0cyITJBHvo%2fT3Tz2G3b7%2fl96q5dr7xnGBKDa6LuQyVBoUaPQJpF10I8j9i3NKXMmCd6055pUxaXRCfinxw10eh1Gpifh1wEW6NmZtu14MMFA1V%2fFqTmUdXUF0%2foJHlr%2fp7ZExvSmp%2fV4W0%2fMOApllWUzcW2GQWzZykS1Uo8GYvRS2TU5OGz7LgKOrROhwVMo7SDor6PfaGuZkrmbzCF6","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=NYQGP9CcWinDn8pqeaxMvOtlho7qAx4znL6oDMM7IMIwYFdmWnG%2baPxiLJ5Cqcw6Mw9cMg72%2fH0QAwCzVn8FOBYjwAQ77O0JaMq3VbcDzfc1%2f0knpTNCBoytyWVwgVrsdFqVIUbGe9vcsLSmvMHpoyLHBejJ5azQbc5a%2fWm7UealyDfLdYRplw6kyzP3kf%2b52mG5iWBskGwc9WqcvgftiGGN50r3YghNqPhLcXqt4xf0qr5uQC1sbgb500WLnd28k2%2brl%2f1RCdCoA9BIQpkczz98EjCMjLk4SFxbqSyqCFyCgqdnicy9OLzUQAcOUxyU","descargar bases")</f>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">885-84-LE26</t>
+          <t xml:space="preserve">4051-16-LP26</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soporte mantención y monitoreo plataforma legacy IBM Spectrum para la Contraloría General de la República</t>
+          <t xml:space="preserve">SERVICIO ADMINISTRADO DE INTERNET RED DE DATOS Y</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
@@ -9824,57 +9544,59 @@
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRALORIA GENERAL DE LA REPUBLICA</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contraloría General de la República</t>
+          <t xml:space="preserve">Municipalidad de Ollagüe</t>
         </is>
       </c>
       <c r="F100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G100" s="0"/>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="G100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ollague</t>
+        </is>
+      </c>
       <c r="H100" s="2">
-        <v>46280.726771</v>
+        <v>46269.531944</v>
       </c>
       <c r="I100" s="2">
         <v>46295.666667</v>
       </c>
       <c r="J100" s="0">
-        <v>12</v>
-      </c>
-      <c r="K100" s="3">
-        <v>30000000.0</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="K100" s="3"/>
       <c r="L100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">CLF</t>
         </is>
       </c>
       <c r="M100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Servicios para internet</t>
         </is>
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Mantenimiento y soporte de hardware</t>
+          <t xml:space="preserve">1 Unidad · Proveedores de servicio de Internet (ISP)</t>
         </is>
       </c>
       <c r="P100" s="2"/>
       <c r="Q100" s="2"/>
       <c r="R100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 meses</t>
+          <t xml:space="preserve">48 meses</t>
         </is>
       </c>
       <c r="S100" s="0" t="inlineStr">
@@ -9885,16 +9607,16 @@
       <c r="T100" s="4"/>
       <c r="U100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antonio Alejandro Alcázar Garrido</t>
+          <t xml:space="preserve">Jhean Ramírez Domínguez</t>
         </is>
       </c>
       <c r="V100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratar el servicio de Soporte, Mantenimiento y Monitoreo de la plataforma de respaldo legacy de la Contraloría General de la República, la cual se encuentra integrada con servidores y librerías robotizadas, y dispone de políticas de acceso, reportes generales y personalizados, además de funciones de monitoreo. Este servicio resulta crítico para la conservación histórica de respaldos de los servicios TIC institucionales.</t>
+          <t xml:space="preserve">El Municipio requiere contratar el Servicio Administrado de Internet, Red de Datos y Telefonía IP para la Ilustre Municipalidad de Ollagüe y que implica la ejecución de diseños preliminares, adquisición de materiales, instalación, montaje, configuración y puesta en servicio con el objeto de garantizar el funcionamiento óptimo de la infraestructura de red en las dependencias de la municipalidad.</t>
         </is>
       </c>
       <c r="W100" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=NYQGP9CcWinDn8pqeaxMvOtlho7qAx4znL6oDMM7IMIwYFdmWnG%2baPxiLJ5Cqcw6Mw9cMg72%2fH0QAwCzVn8FOBYjwAQ77O0JaMq3VbcDzfc1%2f0knpTNCBoytyWVwgVrsdFqVIUbGe9vcsLSmvMHpoyLHBejJ5azQbc5a%2fWm7UealyDfLdYRplw6kyzP3kf%2b52mG5iWBskGwc9WqcvgftiGGN50r3YghNqPhLcXqt4xf0qr5uQC1sbgb500WLnd28k2%2brl%2f1RCdCoA9BIQpkczz98EjCMjLk4SFxbqSyqCFyCgqdnicy9OLzUQAcOUxyU","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=mqll1gFcjA4cdo%2fE471fJqOsSOn0opiti7MdwipHUyD5H%2fsHnq6yLIexkeF%2fP%2bqp4%2bfPypAGosTTIscqty%2foqXEt9k4Xtd96MwQ%2bbK%2bCsUPMgQ79JtbfXUGC%2f7zjJ4aIj6TM3tFSxkYes3uWjDS7TrSatlPZQm07kaqPVsn2Vad9y%2fGrNV%2bAfv%2bcvMaBHQi6gw%2bIuCrbvgkTEdasHPThQ837zYGpyRUbnM1gT9LR1caF3y%2bOz%2fZOtMBwcpmRyo7kKwa94jVk3zo9FI%2fksSNFl8baU9XoRv5OHqnWmBbQzYFK8VqprFPpcwkE3OY5ZWtw","descargar bases")</f>
       </c>
     </row>
     <row r="101">
@@ -9940,7 +9662,7 @@
         <v>46295.6875</v>
       </c>
       <c r="J101" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K101" s="3">
         <v>59757469.0</v>
@@ -10031,7 +9753,7 @@
         <v>46295.75</v>
       </c>
       <c r="J102" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K102" s="3">
         <v>135000000.0</v>
@@ -10127,7 +9849,7 @@
         <v>46296.416667</v>
       </c>
       <c r="J103" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K103" s="3">
         <v>108000000.0</v>
@@ -10226,7 +9948,7 @@
         <v>46296.458333</v>
       </c>
       <c r="J104" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K104" s="3"/>
       <c r="L104" s="0" t="inlineStr">
@@ -10311,7 +10033,7 @@
         <v>46296.625</v>
       </c>
       <c r="J105" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K105" s="3">
         <v>184212000.0</v>
@@ -10407,7 +10129,7 @@
         <v>46296.625694</v>
       </c>
       <c r="J106" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K106" s="3">
         <v>179063.0</v>
@@ -10498,7 +10220,7 @@
         <v>46296.708333</v>
       </c>
       <c r="J107" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K107" s="3">
         <v>98590386.0</v>
@@ -10551,7 +10273,7 @@
         </is>
       </c>
       <c r="W107" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=7hRenMrq4MRTnNc86ATIjzT2Nzl3M5RnCPZf2GlobGnmY4VNQWz%2fIi3Z8WlndcWYF5vQzzOhCpNpU1l7%2f8hPl5NXsVfCH0CZGosjXBhOXE%2bA%2fm0m53wZsXcslJ%2fNapdXJDYQAXiE%2f8f58dHhA1riH%2bQsDqhi2%2fElq0sPaktI6EdzPd09MU0KmZYwPT%2btAPCTTdYkXRImfwsSb7OKACwwrg%2b5UI3Gbi8YfxRyVgUUtZZytH%2fjUfPqGUN4wKgi%2b1VxZEHFvVYdkOqEfqj%2fuU11oO2W1xxFhRlJErC7hbccECnkC11CbBbs0uYyhGVofJ%2fv","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=iXwh7S7jTIrUrIukUZLFwHqvgQVrdMIOpH9UHCLgk18iVwJPfQc7FJqgSURpe4YvU%2bgXxbLQY6afSSyitsUzOlBzjiRNE6RXfiZ9%2bGhKQwnA2a2CY89M9tdpkCgwcx41MlwbAQZXm7FrA%2fOMeuh9WW8BUUlgsCFxqQpRy540mQBf0hVwNCplebZ5Lv5Fu0ozX8NvuZsLcqk5cCwjUATwdcaptzPSKDg1gAbESodcYRQlD3gZGQYlv1oohQ33o%2fgFK4KRq8kqcoUCnP8LSSLLHnJlPJ7Qj7CKnBBtmgrHXswx3boxfsRcDS4J3jwMoS2d","descargar bases")</f>
       </c>
     </row>
     <row r="108">
@@ -10597,7 +10319,7 @@
         <v>46297.395833</v>
       </c>
       <c r="J108" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K108" s="3">
         <v>142800000.0</v>
@@ -10692,7 +10414,7 @@
         <v>46297.416667</v>
       </c>
       <c r="J109" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K109" s="3"/>
       <c r="L109" s="0" t="inlineStr">
@@ -10781,7 +10503,7 @@
         <v>46297.479861</v>
       </c>
       <c r="J110" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K110" s="3">
         <v>118000000.0</v>
@@ -10830,7 +10552,7 @@
         </is>
       </c>
       <c r="W110" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=iWEy61t2Hv47n5Z6CEYvxx4HhMt%2bhZMKjNbi908Vo%2fsPoCZDbeGTWfcn3pMgxlnZIJ84fDoU0b7apHpdEqShSHSQTp4o5H0Gy%2b0BV7xeOXatn5EBi2BU%2biMaryx2UVjzDEpbA7OmFJs8oDzRPppeblFqfRqNLWO2GF0m8KyvcWatB35%2b2IRPiKFDc9dDbt%2foutgA2f21dGi3jCursrvTJweuURXFQENcnrJx9vBF%2bQFni3WHDNoi59BuXNyIO7kmhOwq0jGJXpkiPvq%2fwj8WdQAekV%2fSjXZIKZG1gt4LTQZH2Iflhipv5mg1uX4ine1o","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=WdOgZHaE%2flbVyESRMiRcRT1y%2bG6Nb3Gwr%2bWWwK7swjiQEJLGU9DuiwjaiZ5TRHEkaRniDxR3DcHcuZwY8FMf9aQxCdmkDakE3DDilMXHQJuHVa5fYDYbB1uSBp5IOw3VUrD%2flYr345CPZ%2bYPdS0dCulAlpy1YXZtVTB7jCRfMmgx1sO1qE8sG9Eiiqf6inQ2Y2Iq2JFzzhvi9PppZfgVn%2fKvWV2a6pXSZU1s3%2bUObGy8ZX8s4MYpyQDypxwA0n9Yizu6YgxoP7QhWfv%2f2CvoDDYKKf%2fJRV1BkQeuvg%2fJXbacX6%2b0FHSA8gLrUcj4tDQi","descargar bases")</f>
       </c>
     </row>
     <row r="111">
@@ -10876,7 +10598,7 @@
         <v>46297.625</v>
       </c>
       <c r="J111" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K111" s="3">
         <v>565250.0</v>
@@ -10975,7 +10697,7 @@
         <v>46297.625694</v>
       </c>
       <c r="J112" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K112" s="3"/>
       <c r="L112" s="0" t="inlineStr">
@@ -11068,7 +10790,7 @@
         <v>46300.625</v>
       </c>
       <c r="J113" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K113" s="3">
         <v>7500000.0</v>
@@ -11164,7 +10886,7 @@
         <v>46300.625</v>
       </c>
       <c r="J114" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K114" s="3">
         <v>235620000.0</v>
@@ -11259,7 +10981,7 @@
         <v>46300.625</v>
       </c>
       <c r="J115" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K115" s="3"/>
       <c r="L115" s="0" t="inlineStr">
@@ -11356,7 +11078,7 @@
         <v>46300.625694</v>
       </c>
       <c r="J116" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K116" s="3">
         <v>78172750.0</v>
@@ -11443,7 +11165,7 @@
         <v>46300.631944</v>
       </c>
       <c r="J117" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K117" s="3">
         <v>25000000.0</v>
@@ -11542,7 +11264,7 @@
         <v>46300.645833</v>
       </c>
       <c r="J118" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K118" s="3">
         <v>819072000.0</v>
@@ -11633,7 +11355,7 @@
         <v>46300.666667</v>
       </c>
       <c r="J119" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K119" s="3">
         <v>11000000.0</v>
@@ -11728,7 +11450,7 @@
         <v>46300.666667</v>
       </c>
       <c r="J120" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K120" s="3">
         <v>235000000.0</v>
@@ -11819,7 +11541,7 @@
         <v>46300.708333</v>
       </c>
       <c r="J121" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K121" s="3"/>
       <c r="L121" s="0" t="inlineStr">
@@ -11916,7 +11638,7 @@
         <v>46301.625</v>
       </c>
       <c r="J122" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K122" s="3">
         <v>11000.0</v>
@@ -12015,7 +11737,7 @@
         <v>46301.729167</v>
       </c>
       <c r="J123" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K123" s="3"/>
       <c r="L123" s="0" t="inlineStr">
@@ -12114,7 +11836,7 @@
         <v>46301.83125</v>
       </c>
       <c r="J124" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K124" s="3">
         <v>35706840.0</v>
@@ -12212,7 +11934,7 @@
         <v>46302.5</v>
       </c>
       <c r="J125" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K125" s="3">
         <v>165000000.0</v>
@@ -12304,7 +12026,7 @@
         <v>46302.645833</v>
       </c>
       <c r="J126" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K126" s="3"/>
       <c r="L126" s="0" t="inlineStr">
@@ -12393,7 +12115,7 @@
         <v>46303.666667</v>
       </c>
       <c r="J127" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K127" s="3">
         <v>232851.0</v>
@@ -12488,7 +12210,7 @@
         <v>46304.458333</v>
       </c>
       <c r="J128" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K128" s="3"/>
       <c r="L128" s="0" t="inlineStr">
@@ -12533,12 +12255,12 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-81-LP26</t>
+          <t xml:space="preserve">5482-101-LR26</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGF - PLATAFORMA INGLES</t>
+          <t xml:space="preserve">Plataforma IA para video y seguridad urbana</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
@@ -12548,12 +12270,12 @@
       </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comando Logístico</t>
+          <t xml:space="preserve">SECPLANUNOA</t>
         </is>
       </c>
       <c r="F129" s="0" t="inlineStr">
@@ -12563,42 +12285,46 @@
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Bosque</t>
+          <t xml:space="preserve">Ñuñoa</t>
         </is>
       </c>
       <c r="H129" s="2">
-        <v>46276.548981</v>
+        <v>46275.73022</v>
       </c>
       <c r="I129" s="2">
         <v>46308.625694</v>
       </c>
       <c r="J129" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K129" s="3"/>
       <c r="L129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">USD</t>
+          <t xml:space="preserve">CLF</t>
         </is>
       </c>
       <c r="M129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LR</t>
         </is>
       </c>
       <c r="N129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Sistemas educativos complementarios / Escuelas de idiomas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
         </is>
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Enseñanza conversacional de idiomas extranjeros</t>
+          <t xml:space="preserve">1 Global · Software de desarrollo de plataforma Web · 26 Mes · Software de desarrollo de plataforma Web</t>
         </is>
       </c>
       <c r="P129" s="2"/>
       <c r="Q129" s="2"/>
-      <c r="R129" s="0"/>
+      <c r="R129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26 meses</t>
+        </is>
+      </c>
       <c r="S129" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -12607,27 +12333,28 @@
       <c r="T129" s="4"/>
       <c r="U129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAULO ARELLANO WOLFF</t>
+          <t xml:space="preserve">Katherinne Ayala</t>
         </is>
       </c>
       <c r="V129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DE SERVICIO DE PLATAFORMA INTEGRAL DE CAPACITACIÓN EN IDIOMA INGLÉS MODALIDAD E-LEARNING CON TUTORIA</t>
+          <t xml:space="preserve">La presente licitación contempla como objetivo general, contratar el suministro,
+implementación, puesta en marcha y soporte continuo de una plataforma de Inteligencia Artificial para analítica de video y gestión inteligente de alertas, que opere sobre la red decámaras yo el sistema VMS ya existentes de la Municipalidad de Ñuñoa.</t>
         </is>
       </c>
       <c r="W129" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=Atq4xX4GSaC4iIq4Vy7bDVd8M0H%2fm0ucD%2feh6Txktf7J%2beApMZPQf2vGNruNYCNB0dXceZsBLd1lZRKbdLEMfz%2f5x2ZjTkgsH17bct88P%2b171lAtf7V5kPooIqBlP17xqax2H%2fpWnnIw5sh31D2l2nHsmHMlNFckRqrgVgdF9P0p0SymIwqdsi%2bMqZk5DqUNo%2bYImKvbxfdw7tZVG3TN9xTJUQL2ExyK39PLBnDsfXJsvLzC9w%2fJXEobQ2QiiwxBGqS%2b4WvtsF4A6Qvt2JbXxhW2ejsGeZb5TGAkQexBbY6w0deIYs315sL1u6WHOqNs","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=8yaW0NKjZzXQfukc3owYlyhGfZYiX5O4EXLCI3%2bsKY0Im6f8GkBzLDD%2bz613GpfcIVc3%2bNTA58MLxzx%2fLeAHvpboBb7oLCqphm5a%2fBK7PYWMqvoFwMKjjrodOT6OemXeTuVfTFZffegParSjyvBYNTP%2fsAZeM3j%2fN6xqcZLzsNGG%2bT9KnQxnla30JBkOHDdXwLdZm9TBM8OdH2PQ4kMKV0WWtLFKJdHWvXbB42SaSOkgesVk6mBatgBHmCtYOQZakuE%2fSav%2btz%2b%2fkd8J5JdqBqJ1BE4R%2bxGj1%2bqPmkREfqsZb%2f0jNWM8c44Ouic1Di6e","descargar bases")</f>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3447-145-LR26</t>
+          <t xml:space="preserve">29-81-LP26</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición e Implementación Plataforma Integral</t>
+          <t xml:space="preserve">AGF - PLATAFORMA INGLES</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
@@ -12637,61 +12364,57 @@
       </c>
       <c r="D130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t xml:space="preserve">FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direccion de Administracion y Finanzas</t>
+          <t xml:space="preserve">Comando Logístico</t>
         </is>
       </c>
       <c r="F130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alto Hospicio</t>
+          <t xml:space="preserve">El Bosque</t>
         </is>
       </c>
       <c r="H130" s="2">
-        <v>46276.643669</v>
+        <v>46276.548981</v>
       </c>
       <c r="I130" s="2">
         <v>46308.625694</v>
       </c>
       <c r="J130" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K130" s="3"/>
       <c r="L130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">USD</t>
         </is>
       </c>
       <c r="M130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Ingeniería en computación e informática</t>
+          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Sistemas educativos complementarios / Escuelas de idiomas</t>
         </is>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Servicios de programación de sistemas operativos</t>
+          <t xml:space="preserve">1 Global · Enseñanza conversacional de idiomas extranjeros</t>
         </is>
       </c>
       <c r="P130" s="2"/>
       <c r="Q130" s="2"/>
-      <c r="R130" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 meses</t>
-        </is>
-      </c>
+      <c r="R130" s="0"/>
       <c r="S130" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -12700,27 +12423,27 @@
       <c r="T130" s="4"/>
       <c r="U130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAIME AROS BINIMELIS</t>
+          <t xml:space="preserve">PAULO ARELLANO WOLFF</t>
         </is>
       </c>
       <c r="V130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Art. 9ºLa Municipalidad de Alto Hospicio llama a Licitación Pública denominada Adquisición e Implementación de Plataforma Integral de Gestión Municipal y Servicios Traspasados para la Municipalidad de Alto Hospicio, cuyo objeto es la adquisición, implementación, parametrización, integración, migración de datos, capacitación, puesta en marcha, soporte y mantenimiento de una Plataforma Integral de Gestión Municipal y de Servicios Traspasados, destinada a modernizar, digitalizar y automatizar los procesos institucionales, optimizando la gestión administrativa y operativa, fortaleciendo la interoperabilidad con los sistemas de los organismos de la Administración del Estado, mejorando la atención de los usuarios y asegurando el cumplimiento de la normativa vigente en materia de transformación digital, ciberseguridad y protección de datos personales. Lo anterior, de acuerdo con las características entregadas en las presentes bases administrativas y técnicas adjuntas, en virtud de una mejor y eficiente gestión municipal.</t>
+          <t xml:space="preserve">CONTRATACIÓN DE SERVICIO DE PLATAFORMA INTEGRAL DE CAPACITACIÓN EN IDIOMA INGLÉS MODALIDAD E-LEARNING CON TUTORIA</t>
         </is>
       </c>
       <c r="W130" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=LrPFLVbQf8nbDdTN654u6vEdQAYFqJDC2yqlkmCQdxi2G0aS4e7uKkve3pLUn5abqaDq4uzOsKl0UuS4yb2oaNsR2PuFqb%2b5gNj9pQBiHJJ4NlVuZeRLOqsLh%2f9SBOUFbz5JZLjhJEn7plOgPkVD%2fdM2VptWivencaUgKanJ%2fOgPoCM%2bzJ8ons6YXNuPGIMWQ31PhtFlp7Kg2MjdE9FnILZKd7Q6XZ3qr41noSoVwWzE1cH%2fy%2fLJi3Ah%2b%2f9F%2feo09lZRMKuxoevRFZAjqT0L5TxLxvOy2G5WHQRaMtwkfdF3lAns%2bkTgfaq7botsVvxR","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=tq80HlYTzmOkEsGRcQGOuaHSc4dVV2y3sMNLCRqOqnoNxCH3v%2fHghlcLJQE5wu0DEKxiI6NuNpEHcv8O3k8RUu%2bavPiGZL86RDGqdnIZA3XixB3xPiHQldAppx7Rd70WASPxFxFmJcROVe%2bY1Qt4ePE6m4mr%2bc8ORvCIacKZJ%2fQnXRu6IfN%2fclz9KRYchwl9zpqvbogniIWGv0MMOqdtXxXliL2wods1MXwHhI%2bMltwoRFLjpmSa8fQazq3OUalMdtVZPG9It3NfBm1shr%2b%2bgUBt9NNIDqsNPaz1RWUydq3TUrZbw2yAfHhqlAmZx287","descargar bases")</f>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5482-101-LR26</t>
+          <t xml:space="preserve">3447-145-LR26</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plataforma IA para video y seguridad urbana</t>
+          <t xml:space="preserve">Adquisición e Implementación Plataforma Integral</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
@@ -12730,37 +12453,37 @@
       </c>
       <c r="D131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE NUNOA</t>
+          <t xml:space="preserve">MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SECPLANUNOA</t>
+          <t xml:space="preserve">Direccion de Administracion y Finanzas</t>
         </is>
       </c>
       <c r="F131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de Tarapacá  </t>
         </is>
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ñuñoa</t>
+          <t xml:space="preserve">Alto Hospicio</t>
         </is>
       </c>
       <c r="H131" s="2">
-        <v>46275.73022</v>
+        <v>46276.643669</v>
       </c>
       <c r="I131" s="2">
         <v>46308.625694</v>
       </c>
       <c r="J131" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K131" s="3"/>
       <c r="L131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLF</t>
+          <t xml:space="preserve">CLP</t>
         </is>
       </c>
       <c r="M131" s="0" t="inlineStr">
@@ -12770,19 +12493,19 @@
       </c>
       <c r="N131" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Ingeniería en computación e informática</t>
         </is>
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Software de desarrollo de plataforma Web · 26 Mes · Software de desarrollo de plataforma Web</t>
+          <t xml:space="preserve">1 Global · Servicios de programación de sistemas operativos</t>
         </is>
       </c>
       <c r="P131" s="2"/>
       <c r="Q131" s="2"/>
       <c r="R131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">26 meses</t>
+          <t xml:space="preserve">24 meses</t>
         </is>
       </c>
       <c r="S131" s="0" t="inlineStr">
@@ -12793,17 +12516,16 @@
       <c r="T131" s="4"/>
       <c r="U131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherinne Ayala</t>
+          <t xml:space="preserve">JAIME AROS BINIMELIS</t>
         </is>
       </c>
       <c r="V131" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La presente licitación contempla como objetivo general, contratar el suministro,
-implementación, puesta en marcha y soporte continuo de una plataforma de Inteligencia Artificial para analítica de video y gestión inteligente de alertas, que opere sobre la red decámaras yo el sistema VMS ya existentes de la Municipalidad de Ñuñoa.</t>
+          <t xml:space="preserve">Art. 9ºLa Municipalidad de Alto Hospicio llama a Licitación Pública denominada Adquisición e Implementación de Plataforma Integral de Gestión Municipal y Servicios Traspasados para la Municipalidad de Alto Hospicio, cuyo objeto es la adquisición, implementación, parametrización, integración, migración de datos, capacitación, puesta en marcha, soporte y mantenimiento de una Plataforma Integral de Gestión Municipal y de Servicios Traspasados, destinada a modernizar, digitalizar y automatizar los procesos institucionales, optimizando la gestión administrativa y operativa, fortaleciendo la interoperabilidad con los sistemas de los organismos de la Administración del Estado, mejorando la atención de los usuarios y asegurando el cumplimiento de la normativa vigente en materia de transformación digital, ciberseguridad y protección de datos personales. Lo anterior, de acuerdo con las características entregadas en las presentes bases administrativas y técnicas adjuntas, en virtud de una mejor y eficiente gestión municipal.</t>
         </is>
       </c>
       <c r="W131" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=8yaW0NKjZzXQfukc3owYlyhGfZYiX5O4EXLCI3%2bsKY0Im6f8GkBzLDD%2bz613GpfcIVc3%2bNTA58MLxzx%2fLeAHvpboBb7oLCqphm5a%2fBK7PYWMqvoFwMKjjrodOT6OemXeTuVfTFZffegParSjyvBYNTP%2fsAZeM3j%2fN6xqcZLzsNGG%2bT9KnQxnla30JBkOHDdXwLdZm9TBM8OdH2PQ4kMKV0WWtLFKJdHWvXbB42SaSOkgesVk6mBatgBHmCtYOQZakuE%2fSav%2btz%2b%2fkd8J5JdqBqJ1BE4R%2bxGj1%2bqPmkREfqsZb%2f0jNWM8c44Ouic1Di6e","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/Attachment/ViewAttachment.aspx?enc=uZd%2bUJ8z7MmDjC%2b17J2zsut%2fIERXfciZmnin4aKqzLRAX3G%2f2j9Qyqoc3WnwhUsFup0ipWka41uxrajn%2bGamO88xM2rMpeHdM84VS3WGXuxsijk1CfqlVdVsqAF3D1Mf9HxxNdG8UBew4LgN6emrtRI8P8aDSyYgcy7t08sgv1FPkT11bHwBboek6nl0dkOwLnTGmtBBV%2fX6v2T7jaftXXGEEBsi22d8FDlGCeNuv%2b%2fwiIKBVyzDFF7T%2bGx6fmUQ4mFPiW6hWUqnOTHHMit%2fC0BJA%2btCQjb1IuQOnl9xhTjP7mu8GwI2dj8iw3E%2b9T2V","descargar bases")</f>
       </c>
     </row>
     <row r="132">
@@ -12849,7 +12571,7 @@
         <v>46310.625</v>
       </c>
       <c r="J132" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K132" s="3">
         <v>540000000.0</v>
@@ -12944,7 +12666,7 @@
         <v>46310.625</v>
       </c>
       <c r="J133" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K133" s="3">
         <v>606192000.0</v>
@@ -13039,7 +12761,7 @@
         <v>46310.686806</v>
       </c>
       <c r="J134" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K134" s="3">
         <v>675433201.0</v>
@@ -13136,7 +12858,7 @@
         <v>46311.666667</v>
       </c>
       <c r="J135" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K135" s="3">
         <v>450000000.0</v>
@@ -13231,7 +12953,7 @@
         <v>46314.625</v>
       </c>
       <c r="J136" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K136" s="3">
         <v>408000000.0</v>
@@ -13326,7 +13048,7 @@
         <v>46314.666667</v>
       </c>
       <c r="J137" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K137" s="3"/>
       <c r="L137" s="0" t="inlineStr">
@@ -13423,7 +13145,7 @@
         <v>46317.625</v>
       </c>
       <c r="J138" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K138" s="3">
         <v>8500.0</v>
@@ -13528,7 +13250,7 @@
         <v>46318.625</v>
       </c>
       <c r="J139" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K139" s="3"/>
       <c r="L139" s="0" t="inlineStr">
@@ -14186,12 +13908,12 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2483-242-CO26</t>
+          <t xml:space="preserve">2345-148-LE26</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
+          <t xml:space="preserve">ADQUISICIÓN DE CAMIÓN CON CARROCERIA Y PLATAFORMA DE ELEVACIÓN</t>
         </is>
       </c>
       <c r="C14" s="0">
@@ -14199,12 +13921,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uniformes varios</t>
+          <t xml:space="preserve">Camión volcador</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ropa, maletas y productos de aseo personal / Ropa / Uniformes</t>
+          <t xml:space="preserve">Equipamiento para manejo y estiba de materiales / Maquinaria para manejo de materiales / Camiones, carros y carretillas industriales</t>
         </is>
       </c>
       <c r="F14" s="0">
@@ -14212,276 +13934,10 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paquete</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2710-55-LE26</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO TOTEM</t>
-        </is>
-      </c>
-      <c r="C15" s="0">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monitores de pantalla táctil</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Pantallas o monitores de computador</t>
-        </is>
-      </c>
-      <c r="F15" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO TOTEM , TV y LICENCIA DE SISTEMA GESTOR DE FILA PARA TOTEM EN CENTROS DE SALUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2785-78-LE26</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SDA 6375 SERVICIOS DE PUBLICIDAD Y DIFUSIÓN GESTIÓN MUNICIPAL EN MEDIOS DIGITALES Y PANTALLA LED</t>
-        </is>
-      </c>
-      <c r="C16" s="0">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Campañas publicitarias</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios editoriales, de diseño, publicidad, gráficos y artistas / Publicidad / Agencias de publicidad</t>
-        </is>
-      </c>
-      <c r="F16" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mes</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ítem 2.1 Servicio de difusión y publicidad en pantallas LED, según requerimientos técnicos indicados en Bases Administrativas y Técnicas de la Licitación. Ingresar oferta con valor neto mensual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2785-78-LE26</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SDA 6375 SERVICIOS DE PUBLICIDAD Y DIFUSIÓN GESTIÓN MUNICIPAL EN MEDIOS DIGITALES Y PANTALLA LED</t>
-        </is>
-      </c>
-      <c r="C17" s="0">
-        <v>2</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicidad en Internet</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios editoriales, de diseño, publicidad, gráficos y artistas / Publicidad / Publicidad en medios no impresos</t>
-        </is>
-      </c>
-      <c r="F17" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mes</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ítem 2.2 Servicio de difusión y publicidad en medios digitales, según requerimientos técnicos indicados en Bases Administrativas y Técnicas de la Licitación. 2 Campañas de un mes cada una. Ingresar oferta con valor neto mensual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3810-23-LE26</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADQUISICION DE SOFTWARE DE DISEÑO CAD Y REVISION DE MODELOS BIM PARA LA DIRECCION DE OBRAS MUNICIPALES DE LA I. MUNICIPALIDAD DE PICHILEMU</t>
-        </is>
-      </c>
-      <c r="C18" s="0">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
-        </is>
-      </c>
-      <c r="F18" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">adquisición de software de diseño cad y revisión de modelos bim para la dirección de obras municipales de la I. municipalidad de Pichilemu</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45-48-LE26</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE MANTENCIÓN DE NUBES ACÚSTICAS PARA LAS DEPENDENCIAS DEL PRIMER PISO SENCE NIVEL CENTRAL</t>
-        </is>
-      </c>
-      <c r="C19" s="0">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios de control de la contaminación acústica</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios medioambientales / Servicios de seguimiento, control o rehabilitación de agentes contaminantes / Control de la contaminación acústica</t>
-        </is>
-      </c>
-      <c r="F19" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE MANTENCIÓN DE NUBES ACÚSTICAS PARA LAS DEPENDENCIAS DEL PRIMER PISO SENCE NIVEL CENTRAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">875-7-LE26</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERV. INFORMES Y PLATAFORMA DE PROYECTOS INVERSIÓN</t>
-        </is>
-      </c>
-      <c r="C20" s="0">
-        <v>1</v>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicaciones periódicas</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Productos impresos y publicaciones / Medios impresos / Publicaciones impresas</t>
-        </is>
-      </c>
-      <c r="F20" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE ELABORACIÓN Y ENTREGA DE INFORMES DE PROYECTOS DE INVERSIÓN EN CHILE Y ACCESO A UNA PLATAFORMA ONLINE DE SEGUIMIENTO DE PROYECTOS DE INVERSIÓN PARA LA AGENCIA DE PROMOCIÓN DE LA INVERSIÓN EXTRANJERA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2345-148-LE26</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADQUISICIÓN DE CAMIÓN CON CARROCERIA Y PLATAFORMA DE ELEVACIÓN</t>
-        </is>
-      </c>
-      <c r="C21" s="0">
-        <v>1</v>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Camión volcador</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipamiento para manejo y estiba de materiales / Maquinaria para manejo de materiales / Camiones, carros y carretillas industriales</t>
-        </is>
-      </c>
-      <c r="F21" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ANEXO N°3
 OFERTA ECONÓMICA NETA
@@ -14491,6 +13947,272 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2483-242-CO26</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">“ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
+        </is>
+      </c>
+      <c r="C15" s="0">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uniformes varios</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ropa, maletas y productos de aseo personal / Ropa / Uniformes</t>
+        </is>
+      </c>
+      <c r="F15" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paquete</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADQUISICIÓN DE UNIFORMES PARA FUNCIONARIOS DE MOVILIZACIÓN MANTENCIÓN EQUIPAMIENTO CLÍNICO E INFORMÁTICA DEL DEPARTAMENTO DE SALUD MUNICIPALIDAD DE QUILICURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2710-55-LE26</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO TOTEM</t>
+        </is>
+      </c>
+      <c r="C16" s="0">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monitores de pantalla táctil</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Pantallas o monitores de computador</t>
+        </is>
+      </c>
+      <c r="F16" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO TOTEM , TV y LICENCIA DE SISTEMA GESTOR DE FILA PARA TOTEM EN CENTROS DE SALUD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3810-23-LE26</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADQUISICION DE SOFTWARE DE DISEÑO CAD Y REVISION DE MODELOS BIM PARA LA DIRECCION DE OBRAS MUNICIPALES DE LA I. MUNICIPALIDAD DE PICHILEMU</t>
+        </is>
+      </c>
+      <c r="C17" s="0">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de gestión de licencias</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+        </is>
+      </c>
+      <c r="F17" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">adquisición de software de diseño cad y revisión de modelos bim para la dirección de obras municipales de la I. municipalidad de Pichilemu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45-48-LE26</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE MANTENCIÓN DE NUBES ACÚSTICAS PARA LAS DEPENDENCIAS DEL PRIMER PISO SENCE NIVEL CENTRAL</t>
+        </is>
+      </c>
+      <c r="C18" s="0">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios de control de la contaminación acústica</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios medioambientales / Servicios de seguimiento, control o rehabilitación de agentes contaminantes / Control de la contaminación acústica</t>
+        </is>
+      </c>
+      <c r="F18" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE MANTENCIÓN DE NUBES ACÚSTICAS PARA LAS DEPENDENCIAS DEL PRIMER PISO SENCE NIVEL CENTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598-20-LE26</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adquisición Licencias de Software para DIPRECA</t>
+        </is>
+      </c>
+      <c r="C19" s="0">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de gestión de licencias</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+        </is>
+      </c>
+      <c r="F19" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licencia Cloudflare Business por un periodo de 36 meses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598-20-LE26</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adquisición Licencias de Software para DIPRECA</t>
+        </is>
+      </c>
+      <c r="C20" s="0">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de gestión de licencias</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+        </is>
+      </c>
+      <c r="F20" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licencia Crowdsec por un periodo de 36 meses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598-20-LE26</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adquisición Licencias de Software para DIPRECA</t>
+        </is>
+      </c>
+      <c r="C21" s="0">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de gestión de licencias</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+        </is>
+      </c>
+      <c r="F21" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licencias Intellij Software (pack completo de 11 IDE, según detalle adjunto) por un periodo de 36 meses.</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
@@ -14503,7 +14225,7 @@
         </is>
       </c>
       <c r="C22" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
@@ -14516,7 +14238,7 @@
         </is>
       </c>
       <c r="F22" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
@@ -14525,36 +14247,36 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licencia Cloudflare Business por un periodo de 36 meses.</t>
+          <t xml:space="preserve">Licencia trae IA, entorno de desarrollo integrado Ultra por un periodo de 36 meses.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">598-20-LE26</t>
+          <t xml:space="preserve">875-7-LE26</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición Licencias de Software para DIPRECA</t>
+          <t xml:space="preserve">SERV. INFORMES Y PLATAFORMA DE PROYECTOS INVERSIÓN</t>
         </is>
       </c>
       <c r="C23" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Publicaciones periódicas</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Productos impresos y publicaciones / Medios impresos / Publicaciones impresas</t>
         </is>
       </c>
       <c r="F23" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
@@ -14563,70 +14285,70 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licencia Crowdsec por un periodo de 36 meses.</t>
+          <t xml:space="preserve">SERVICIO DE ELABORACIÓN Y ENTREGA DE INFORMES DE PROYECTOS DE INVERSIÓN EN CHILE Y ACCESO A UNA PLATAFORMA ONLINE DE SEGUIMIENTO DE PROYECTOS DE INVERSIÓN PARA LA AGENCIA DE PROMOCIÓN DE LA INVERSIÓN EXTRANJERA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">598-20-LE26</t>
+          <t xml:space="preserve">2785-78-LE26</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición Licencias de Software para DIPRECA</t>
+          <t xml:space="preserve">SDA 6375 SERVICIOS DE PUBLICIDAD Y DIFUSIÓN GESTIÓN MUNICIPAL EN MEDIOS DIGITALES Y PANTALLA LED</t>
         </is>
       </c>
       <c r="C24" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Campañas publicitarias</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios editoriales, de diseño, publicidad, gráficos y artistas / Publicidad / Agencias de publicidad</t>
         </is>
       </c>
       <c r="F24" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Mes</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licencias Intellij Software (pack completo de 11 IDE, según detalle adjunto) por un periodo de 36 meses.</t>
+          <t xml:space="preserve">Ítem 2.1 Servicio de difusión y publicidad en pantallas LED, según requerimientos técnicos indicados en Bases Administrativas y Técnicas de la Licitación. Ingresar oferta con valor neto mensual.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">598-20-LE26</t>
+          <t xml:space="preserve">2785-78-LE26</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición Licencias de Software para DIPRECA</t>
+          <t xml:space="preserve">SDA 6375 SERVICIOS DE PUBLICIDAD Y DIFUSIÓN GESTIÓN MUNICIPAL EN MEDIOS DIGITALES Y PANTALLA LED</t>
         </is>
       </c>
       <c r="C25" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Publicidad en Internet</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios editoriales, de diseño, publicidad, gráficos y artistas / Publicidad / Publicidad en medios no impresos</t>
         </is>
       </c>
       <c r="F25" s="0">
@@ -14634,12 +14356,12 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Mes</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licencia trae IA, entorno de desarrollo integrado Ultra por un periodo de 36 meses.</t>
+          <t xml:space="preserve">Ítem 2.2 Servicio de difusión y publicidad en medios digitales, según requerimientos técnicos indicados en Bases Administrativas y Técnicas de la Licitación. 2 Campañas de un mes cada una. Ingresar oferta con valor neto mensual.</t>
         </is>
       </c>
     </row>
@@ -14798,12 +14520,12 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1393093-103-LE26</t>
+          <t xml:space="preserve">1393093-98-LE26</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
+          <t xml:space="preserve">CONTRATACIÓN DE SERV. DE DESA.SOFTWARE RENDICIONES</t>
         </is>
       </c>
       <c r="C30" s="0">
@@ -14811,16 +14533,16 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Desarrolladores temporales de software</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
         </is>
       </c>
       <c r="F30" s="0">
-        <v>120.0</v>
+        <v>1.0</v>
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
@@ -14829,36 +14551,36 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LÍNEA 1: LICENCIA ESET PROTECT ENTRY</t>
+          <t xml:space="preserve">SERV. DESARROLLO SOFTWARE RENDICONES</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1393093-103-LE26</t>
+          <t xml:space="preserve">2069-141-LR26</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
+          <t xml:space="preserve">CGM ADQ. TORRE DE ENDOSCOPIA DIGESTIVA CON IA</t>
         </is>
       </c>
       <c r="C31" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Equipo endoscópico o carritos de procedimiento o accesorios</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Productos quirúrgicos / Equipo endoscópico, accesorios y productos relacionados</t>
         </is>
       </c>
       <c r="F31" s="0">
-        <v>130.0</v>
+        <v>2.0</v>
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
@@ -14867,36 +14589,36 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LÍNEA 2: PREY</t>
+          <t xml:space="preserve">TORRE DE ENDOSCOPIA DIGESTIVA CON INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1393093-103-LE26</t>
+          <t xml:space="preserve">5531-4-B226</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
+          <t xml:space="preserve">Servicios de publicidad digital para el DII</t>
         </is>
       </c>
       <c r="C32" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Campañas publicitarias</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios editoriales, de diseño, publicidad, gráficos y artistas / Publicidad / Agencias de publicidad</t>
         </is>
       </c>
       <c r="F32" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
@@ -14905,23 +14627,23 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LÍNEA 3: ADOBE CREATIVE CLOUD</t>
+          <t xml:space="preserve">Servicios de publicidad digital, para el Departamento de Ingeniería Industrial</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1393093-103-LE26</t>
+          <t xml:space="preserve">885-81-LP26</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
+          <t xml:space="preserve">Renovación de suscripciones para la plataforma de parchado virtual vRx Vicarius</t>
         </is>
       </c>
       <c r="C33" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
@@ -14934,54 +14656,54 @@
         </is>
       </c>
       <c r="F33" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LÍNEA 4: CAPCUT PRO</t>
+          <t xml:space="preserve">Renovación de suscripción por 3000 activos para la plataforma de parchado virtual vRx Vicarius.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1393093-103-LE26</t>
+          <t xml:space="preserve">986278-19-L126</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
+          <t xml:space="preserve">CONTRATO DE SUMINISTRO DE INSUMOS INFORMÁTICOS, AÑO 2026, CFT DE LA REGIÓN DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="C34" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Tóner</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Equipos, accesorios y suministros de oficina / Maquinarias, suministros y accesorios de oficina / Suministros para impresora, fax y fotocopiadora</t>
         </is>
       </c>
       <c r="F34" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LÍNEA 5: INSHOT PRO</t>
+          <t xml:space="preserve">CONTRATO DE SUMINISTRO DE INSUMOS INFORMÁTICOS, AÑO 2026, CFT DE LA REGIÓN DE LA ARAUCANÍA, SEGÚN BASES ADJUNTAS. EL OFERENTE DEBE POSTULAR EN MERCADO PUBLICO CON EL PRESUPUESTO NETO TOTAL DISPONIBLE DE LA INSTITUCIÓN: $3.800.352</t>
         </is>
       </c>
     </row>
@@ -14997,7 +14719,7 @@
         </is>
       </c>
       <c r="C35" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
@@ -15010,7 +14732,7 @@
         </is>
       </c>
       <c r="F35" s="0">
-        <v>1.0</v>
+        <v>120.0</v>
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
@@ -15019,7 +14741,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LÍNEA 6: TEAMVIEWER CORPORATE + 3 CANALES ADICIONALES</t>
+          <t xml:space="preserve">LÍNEA 1: LICENCIA ESET PROTECT ENTRY</t>
         </is>
       </c>
     </row>
@@ -15035,7 +14757,7 @@
         </is>
       </c>
       <c r="C36" s="0">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
@@ -15048,7 +14770,7 @@
         </is>
       </c>
       <c r="F36" s="0">
-        <v>115.0</v>
+        <v>130.0</v>
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
@@ -15057,36 +14779,36 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LÍNEA 7: OFFICE 365 A5 FOR FACULTY</t>
+          <t xml:space="preserve">LÍNEA 2: PREY</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069-141-LR26</t>
+          <t xml:space="preserve">1393093-103-LE26</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CGM ADQ. TORRE DE ENDOSCOPIA DIGESTIVA CON IA</t>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
         </is>
       </c>
       <c r="C37" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipo endoscópico o carritos de procedimiento o accesorios</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento y suministros médicos / Productos quirúrgicos / Equipo endoscópico, accesorios y productos relacionados</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F37" s="0">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
@@ -15095,36 +14817,36 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRE DE ENDOSCOPIA DIGESTIVA CON INTELIGENCIA ARTIFICIAL</t>
+          <t xml:space="preserve">LÍNEA 3: ADOBE CREATIVE CLOUD</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5531-4-B226</t>
+          <t xml:space="preserve">1393093-103-LE26</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de publicidad digital para el DII</t>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
         </is>
       </c>
       <c r="C38" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campañas publicitarias</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios editoriales, de diseño, publicidad, gráficos y artistas / Publicidad / Agencias de publicidad</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F38" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
@@ -15133,23 +14855,23 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de publicidad digital, para el Departamento de Ingeniería Industrial</t>
+          <t xml:space="preserve">LÍNEA 4: CAPCUT PRO</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">885-81-LP26</t>
+          <t xml:space="preserve">1393093-103-LE26</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renovación de suscripciones para la plataforma de parchado virtual vRx Vicarius</t>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
         </is>
       </c>
       <c r="C39" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
@@ -15162,41 +14884,41 @@
         </is>
       </c>
       <c r="F39" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renovación de suscripción por 3000 activos para la plataforma de parchado virtual vRx Vicarius.</t>
+          <t xml:space="preserve">LÍNEA 5: INSHOT PRO</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">986278-19-L126</t>
+          <t xml:space="preserve">1393093-103-LE26</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATO DE SUMINISTRO DE INSUMOS INFORMÁTICOS, AÑO 2026, CFT DE LA REGIÓN DE LA ARAUCANÍA</t>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
         </is>
       </c>
       <c r="C40" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tóner</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipos, accesorios y suministros de oficina / Maquinarias, suministros y accesorios de oficina / Suministros para impresora, fax y fotocopiadora</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F40" s="0">
@@ -15204,41 +14926,41 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATO DE SUMINISTRO DE INSUMOS INFORMÁTICOS, AÑO 2026, CFT DE LA REGIÓN DE LA ARAUCANÍA, SEGÚN BASES ADJUNTAS. EL OFERENTE DEBE POSTULAR EN MERCADO PUBLICO CON EL PRESUPUESTO NETO TOTAL DISPONIBLE DE LA INSTITUCIÓN: $3.800.352</t>
+          <t xml:space="preserve">LÍNEA 6: TEAMVIEWER CORPORATE + 3 CANALES ADICIONALES</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1393093-98-LE26</t>
+          <t xml:space="preserve">1393093-103-LE26</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DE SERV. DE DESA.SOFTWARE RENDICIONES</t>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS SOFTWARE P01</t>
         </is>
       </c>
       <c r="C41" s="0">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores temporales de software</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F41" s="0">
-        <v>1.0</v>
+        <v>115.0</v>
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
@@ -15247,7 +14969,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. DESARROLLO SOFTWARE RENDICONES</t>
+          <t xml:space="preserve">LÍNEA 7: OFFICE 365 A5 FOR FACULTY</t>
         </is>
       </c>
     </row>
@@ -16433,12 +16155,12 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">837-101-LP26</t>
+          <t xml:space="preserve">5413-71-LE26</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CDP 477 SERVICIO DE OPERACIÓN SISTEMA DE CONTROL CENTRALIZADO BMS Y SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL DE EDIFICIO INSTITUCIONAL SML SANTIAGO</t>
+          <t xml:space="preserve">SERVICIO DE PLATAFORMA DE LIBROS CONTABLES Y AUXILIARES ELECTRÓNICOS Y DOCUMENTOS TRIBUTARIOS ELECTRÓNICOS DTE PARA LA UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="C73" s="0">
@@ -16446,16 +16168,16 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de administración</t>
+          <t xml:space="preserve">Mantenimiento y soporte de sistemas propietarios</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
         </is>
       </c>
       <c r="F73" s="0">
-        <v>12.0</v>
+        <v>36.0</v>
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
@@ -16464,19 +16186,19 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE OPERACIÓN PARA EL SISTEMA DE CONTROL CENTRALIZADO (BMS) SOFTWARE ENTELIWEB</t>
+          <t xml:space="preserve">SERVICIOS DE EMISIÓN Y RECEPCIÓN DE DOCUMENTOS TRIBUTARIOS ELECTRÓNICO.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">837-101-LP26</t>
+          <t xml:space="preserve">5413-71-LE26</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CDP 477 SERVICIO DE OPERACIÓN SISTEMA DE CONTROL CENTRALIZADO BMS Y SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL DE EDIFICIO INSTITUCIONAL SML SANTIAGO</t>
+          <t xml:space="preserve">SERVICIO DE PLATAFORMA DE LIBROS CONTABLES Y AUXILIARES ELECTRÓNICOS Y DOCUMENTOS TRIBUTARIOS ELECTRÓNICOS DTE PARA LA UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="C74" s="0">
@@ -16484,16 +16206,16 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas de control de acceso o de seguridad</t>
+          <t xml:space="preserve">Desarrolladores de software</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipos y suministros de defensa, orden público, protección y seguridad / Seguridad, vigilancia y detección / Equipo de vigilancia y detección</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="F74" s="0">
-        <v>12.0</v>
+        <v>36.0</v>
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
@@ -16502,7 +16224,7 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE OPERACIÓN PARA EL SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL</t>
+          <t xml:space="preserve">SERVICIO DE PLATAFORMA DE LIBROS CONTABLES ELECTRÓNICOS.</t>
         </is>
       </c>
     </row>
@@ -16518,16 +16240,16 @@
         </is>
       </c>
       <c r="C75" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenimiento y soporte de sistemas propietarios</t>
+          <t xml:space="preserve">Desarrolladores de software</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="F75" s="0">
@@ -16540,36 +16262,36 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIOS DE EMISIÓN Y RECEPCIÓN DE DOCUMENTOS TRIBUTARIOS ELECTRÓNICO.</t>
+          <t xml:space="preserve">SERVICIO DE PLATAFORMA DE LIBROS AUXILIARES ELECTRÓNICOS.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413-71-LE26</t>
+          <t xml:space="preserve">837-101-LP26</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE PLATAFORMA DE LIBROS CONTABLES Y AUXILIARES ELECTRÓNICOS Y DOCUMENTOS TRIBUTARIOS ELECTRÓNICOS DTE PARA LA UNIVERSIDAD DE LOS LAGOS</t>
+          <t xml:space="preserve">CDP 477 SERVICIO DE OPERACIÓN SISTEMA DE CONTROL CENTRALIZADO BMS Y SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL DE EDIFICIO INSTITUCIONAL SML SANTIAGO</t>
         </is>
       </c>
       <c r="C76" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores de software</t>
+          <t xml:space="preserve">Software de administración</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
         </is>
       </c>
       <c r="F76" s="0">
-        <v>36.0</v>
+        <v>12.0</v>
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
@@ -16578,36 +16300,36 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE PLATAFORMA DE LIBROS CONTABLES ELECTRÓNICOS.</t>
+          <t xml:space="preserve">SERVICIO DE OPERACIÓN PARA EL SISTEMA DE CONTROL CENTRALIZADO (BMS) SOFTWARE ENTELIWEB</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413-71-LE26</t>
+          <t xml:space="preserve">837-101-LP26</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE PLATAFORMA DE LIBROS CONTABLES Y AUXILIARES ELECTRÓNICOS Y DOCUMENTOS TRIBUTARIOS ELECTRÓNICOS DTE PARA LA UNIVERSIDAD DE LOS LAGOS</t>
+          <t xml:space="preserve">CDP 477 SERVICIO DE OPERACIÓN SISTEMA DE CONTROL CENTRALIZADO BMS Y SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL DE EDIFICIO INSTITUCIONAL SML SANTIAGO</t>
         </is>
       </c>
       <c r="C77" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores de software</t>
+          <t xml:space="preserve">Sistemas de control de acceso o de seguridad</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Equipos y suministros de defensa, orden público, protección y seguridad / Seguridad, vigilancia y detección / Equipo de vigilancia y detección</t>
         </is>
       </c>
       <c r="F77" s="0">
-        <v>36.0</v>
+        <v>12.0</v>
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
@@ -16616,19 +16338,19 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE PLATAFORMA DE LIBROS AUXILIARES ELECTRÓNICOS.</t>
+          <t xml:space="preserve">SERVICIO DE OPERACIÓN PARA EL SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098-142-LE26</t>
+          <t xml:space="preserve">4778-14-LP26</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
+          <t xml:space="preserve">SERV. ADMINISTRADO CONTACT CENTER OMNICANAL CON IA</t>
         </is>
       </c>
       <c r="C78" s="0">
@@ -16636,16 +16358,16 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuentes de alimentación continua</t>
+          <t xml:space="preserve">Software para centrales de comunicación digital</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artículos eléctricos y de iluminación / Equipamiento y artículos eléctricos / Equipamiento para distribución y transformación eléctrica</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
         </is>
       </c>
       <c r="F78" s="0">
-        <v>30.0</v>
+        <v>24.0</v>
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
@@ -16654,43 +16376,119 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROCESADOR (CPU) intel i3-12100 LGA 1700</t>
+          <t xml:space="preserve">Servicio Administrado de Contact Center Omnicanal con IA</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">885-83-LE26</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios de soporte y mantenimiento de la plataforma de seguridad F5 de la Contraloría General de la República</t>
+        </is>
+      </c>
+      <c r="C79" s="0">
+        <v>1</v>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipo de seguridad de red de firewall</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de seguridad de red</t>
+        </is>
+      </c>
+      <c r="F79" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios de soporte y mantenimiento de su plataforma de seguridad, correspondiente a Balanceador de carga y cortafuego de aplicaciones F5, para zona productiva por un periodo de 12 meses</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C79" s="0">
+      <c r="C80" s="0">
+        <v>1</v>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuentes de alimentación continua</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artículos eléctricos y de iluminación / Equipamiento y artículos eléctricos / Equipamiento para distribución y transformación eléctrica</t>
+        </is>
+      </c>
+      <c r="F80" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROCESADOR (CPU) intel i3-12100 LGA 1700</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2098-142-LE26</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
+        </is>
+      </c>
+      <c r="C81" s="0">
         <v>2</v>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fuentes de alimentación continua</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Artículos eléctricos y de iluminación / Equipamiento y artículos eléctricos / Equipamiento para distribución y transformación eléctrica</t>
         </is>
       </c>
-      <c r="F79" s="0">
+      <c r="F81" s="0">
         <v>100.0</v>
       </c>
-      <c r="G79" s="0" t="inlineStr">
+      <c r="G81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="H81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DISCO DE ESTADO SOLIDO (SSD) 500 GB DISCO DE ESTADO SOLIDO (SSD) 500 GB-       Formato 2,5mm
 -       Tipo SSD
@@ -16699,39 +16497,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="0" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C80" s="0">
+      <c r="C82" s="0">
         <v>3</v>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fuentes de alimentación continua</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Artículos eléctricos y de iluminación / Equipamiento y artículos eléctricos / Equipamiento para distribución y transformación eléctrica</t>
         </is>
       </c>
-      <c r="F80" s="0">
+      <c r="F82" s="0">
         <v>30.0</v>
       </c>
-      <c r="G80" s="0" t="inlineStr">
+      <c r="G82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">PLACA MADRE H610M-HDV SOCKET LGA1700/ DDR4/ SATA3 USB3.2/ MICRO ATX-       Placa Madre Socket LGA1700
 -       DDR4/ SATA3 USB3.2/
@@ -16739,78 +16537,78 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="0" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C81" s="0">
+      <c r="C83" s="0">
         <v>4</v>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Pantallas de plasma (PDP)</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Pantallas o monitores de computador</t>
         </is>
       </c>
-      <c r="F81" s="0">
+      <c r="F83" s="0">
         <v>30.0</v>
       </c>
-      <c r="G81" s="0" t="inlineStr">
+      <c r="G83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr">
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">PANTALLA 24"-          Monitor plano 24”
 -          Conexión HDMI y VGA</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="0" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C82" s="0">
+      <c r="C84" s="0">
         <v>5</v>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Pantallas de plasma (PDP)</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Pantallas o monitores de computador</t>
         </is>
       </c>
-      <c r="F82" s="0">
+      <c r="F84" s="0">
         <v>100.0</v>
       </c>
-      <c r="G82" s="0" t="inlineStr">
+      <c r="G84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">BATERIAS UCG5-12V-       9AH
 -          12V
@@ -16818,39 +16616,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="0" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C83" s="0">
+      <c r="C85" s="0">
         <v>6</v>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fuentes de alimentación continua</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Artículos eléctricos y de iluminación / Equipamiento y artículos eléctricos / Equipamiento para distribución y transformación eléctrica</t>
         </is>
       </c>
-      <c r="F83" s="0">
+      <c r="F85" s="0">
         <v>30.0</v>
       </c>
-      <c r="G83" s="0" t="inlineStr">
+      <c r="G85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="H85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">GABINETE PC SLIM-          Tamaño Slim
 -          Formato Micro ATX 
@@ -16858,39 +16656,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="0" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C84" s="0">
+      <c r="C86" s="0">
         <v>7</v>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Teclados</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Dispositivos informáticos de entrada de datos</t>
         </is>
       </c>
-      <c r="F84" s="0">
+      <c r="F86" s="0">
         <v>150.0</v>
       </c>
-      <c r="G84" s="0" t="inlineStr">
+      <c r="G86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">TECLADO PARA COMPUTADOR -          Interfaz USB
 -          Idioma del teclado Español (con letra Ñ)
@@ -16900,39 +16698,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="0" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C85" s="0">
+      <c r="C87" s="0">
         <v>8</v>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Soporte de pared</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Artículos de fabricación y producción / Artículos de ferretería / Soportes y puntales</t>
         </is>
       </c>
-      <c r="F85" s="0">
+      <c r="F87" s="0">
         <v>20.0</v>
       </c>
-      <c r="G85" s="0" t="inlineStr">
+      <c r="G87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr">
+      <c r="H87" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">SOPORTE DE PARED PARA MONITOR SOPORTE DE PARED -       Para monitores de 14” a 24”
 -          Giro de 180 grados
@@ -16941,39 +16739,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="0" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C86" s="0">
+      <c r="C88" s="0">
         <v>9</v>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Artículo de cámara</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Maquinaria para fabricación y transformación industrial / Maquinaria y suministros de procesos industriales / Dispositivos de guía, posicionamiento y sujeción</t>
         </is>
       </c>
-      <c r="F86" s="0">
+      <c r="F88" s="0">
         <v>30.0</v>
       </c>
-      <c r="G86" s="0" t="inlineStr">
+      <c r="G88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H86" s="4" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">CAMARA WEB -       Resolución Full HD 1080p
 -       Ángulo de visión de 90° permite capturar más entorno en videoconferencias grupales.
@@ -16981,117 +16779,117 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="0" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C87" s="0">
+      <c r="C89" s="0">
         <v>10</v>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Memoria RAM dinámica (DRAM)</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Artículos de electrónica / Circuitos electrónicos / Circuitos integrados, memorias y microprocesadores</t>
         </is>
       </c>
-      <c r="F87" s="0">
+      <c r="F89" s="0">
         <v>60.0</v>
       </c>
-      <c r="G87" s="0" t="inlineStr">
+      <c r="G89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr">
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MEMORIA RAM -       DDR4
 -       Capacidad 4GB</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="0" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C88" s="0">
+      <c r="C90" s="0">
         <v>11</v>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Programas de desvío o conmutación</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
         </is>
       </c>
-      <c r="F88" s="0">
+      <c r="F90" s="0">
         <v>10.0</v>
       </c>
-      <c r="G88" s="0" t="inlineStr">
+      <c r="G90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ROUTER INALAMBRICO -       Router inalámbrico 4G y 5G, 
 -       Puertos Gigabit LAN y antenas de cobertura de wifi.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="0" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C89" s="0">
+      <c r="C91" s="0">
         <v>12</v>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Trackballs y mouse de computador</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Dispositivos informáticos de entrada de datos</t>
         </is>
       </c>
-      <c r="F89" s="0">
+      <c r="F91" s="0">
         <v>100.0</v>
       </c>
-      <c r="G89" s="0" t="inlineStr">
+      <c r="G91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr">
+      <c r="H91" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MOUSE PARA COMPUTADOR -          Interfaz del dispositivo USB
 -          Formato del mouse estándar
@@ -17100,39 +16898,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="0" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C90" s="0">
+      <c r="C92" s="0">
         <v>13</v>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cable de redes</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Maquinaria para generación y distribución de energía / Alambres y cables eléctricos y electrónicos / Cables eléctricos y accesorios</t>
         </is>
       </c>
-      <c r="F90" s="0">
+      <c r="F92" s="0">
         <v>8.0</v>
       </c>
-      <c r="G90" s="0" t="inlineStr">
+      <c r="G92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">CABLE RED -       UTP
 -          Categoría 6
@@ -17140,39 +16938,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="0" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C91" s="0">
+      <c r="C93" s="0">
         <v>14</v>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Parlantes</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Muebles, accesorios, electrodomésticos y productos electrónicos / Equipos y accesorios audiovisuales / Equipos audiovisuales y de electrónica menor</t>
         </is>
       </c>
-      <c r="F91" s="0">
+      <c r="F93" s="0">
         <v>20.0</v>
       </c>
-      <c r="G91" s="0" t="inlineStr">
+      <c r="G93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr">
+      <c r="H93" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">PARLANTE USB -          Formato alámbrico USB
 -          Entrada auxiliar jack 3,5mm
@@ -17180,39 +16978,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="0" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2098-142-LE26</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICION DE ARTICULOS INFORMATICOS Y TECNOLOGICOS PAC N° 115 HRAV.</t>
         </is>
       </c>
-      <c r="C92" s="0">
+      <c r="C94" s="0">
         <v>15</v>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Memoria de acceso aleatorio (RAM)</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E94" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Artículos de electrónica / Circuitos electrónicos / Circuitos integrados, memorias y microprocesadores</t>
         </is>
       </c>
-      <c r="F92" s="0">
+      <c r="F94" s="0">
         <v>10.0</v>
       </c>
-      <c r="G92" s="0" t="inlineStr">
+      <c r="G94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H92" s="4" t="inlineStr">
+      <c r="H94" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DISCO DURO EXTERNO 4TB -       Formato 2,5mm
 -          Conexión usb 3.0
@@ -17220,82 +17018,6 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4778-14-LP26</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERV. ADMINISTRADO CONTACT CENTER OMNICANAL CON IA</t>
-        </is>
-      </c>
-      <c r="C93" s="0">
-        <v>1</v>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Software para centrales de comunicación digital</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
-        </is>
-      </c>
-      <c r="F93" s="0">
-        <v>24.0</v>
-      </c>
-      <c r="G93" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicio Administrado de Contact Center Omnicanal con IA</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">885-83-LE26</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios de soporte y mantenimiento de la plataforma de seguridad F5 de la Contraloría General de la República</t>
-        </is>
-      </c>
-      <c r="C94" s="0">
-        <v>1</v>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipo de seguridad de red de firewall</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de seguridad de red</t>
-        </is>
-      </c>
-      <c r="F94" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G94" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios de soporte y mantenimiento de su plataforma de seguridad, correspondiente a Balanceador de carga y cortafuego de aplicaciones F5, para zona productiva por un periodo de 12 meses</t>
-        </is>
-      </c>
-    </row>
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
@@ -18442,12 +18164,12 @@
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239-2-LR26</t>
+          <t xml:space="preserve">2048-57-LP26</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio Marco Desarrollo de software</t>
+          <t xml:space="preserve">Convenio de Software de Gestión de Mantenimiento</t>
         </is>
       </c>
       <c r="C125" s="0">
@@ -18455,12 +18177,12 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores de software</t>
+          <t xml:space="preserve">Software de administración</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
         </is>
       </c>
       <c r="F125" s="0">
@@ -18468,24 +18190,24 @@
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Unidad no definida</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio Marco para la adquisición de los Servicios de Desarrollo y Mantención de Software, Servicios Profesionales TI y Cloud Computing</t>
+          <t xml:space="preserve">SOFTWARE DE GESTION DE MANTENIMIENTO (INGRESAR PRECIO TOTAL DEL CONVENIO, SEGUN ANEXO ECONOMICO N°1)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2563-34-LR26</t>
+          <t xml:space="preserve">2239-2-LR26</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
+          <t xml:space="preserve">Convenio Marco Desarrollo de software</t>
         </is>
       </c>
       <c r="C126" s="0">
@@ -18493,16 +18215,16 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cajas de conmutación de computadores</t>
+          <t xml:space="preserve">Desarrolladores de software</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="F126" s="0">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
@@ -18511,7 +18233,7 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Switch 48G PoE 4SFP+ (equivalente al modelo JL727B) / Control de Acceso</t>
+          <t xml:space="preserve">Convenio Marco para la adquisición de los Servicios de Desarrollo y Mantención de Software, Servicios Profesionales TI y Cloud Computing</t>
         </is>
       </c>
     </row>
@@ -18527,7 +18249,7 @@
         </is>
       </c>
       <c r="C127" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
@@ -18540,7 +18262,7 @@
         </is>
       </c>
       <c r="F127" s="0">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
@@ -18549,7 +18271,7 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Switch 48G PoE 4SFP+ (equivalente al modelo JL727B) /Aeroportuarios</t>
+          <t xml:space="preserve">Switch 48G PoE 4SFP+ (equivalente al modelo JL727B) / Control de Acceso</t>
         </is>
       </c>
     </row>
@@ -18565,7 +18287,7 @@
         </is>
       </c>
       <c r="C128" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
@@ -18578,7 +18300,7 @@
         </is>
       </c>
       <c r="F128" s="0">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
@@ -18587,7 +18309,7 @@
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Switch 24G PoE 4SFP+(equivalente al modelo JL261A) /Aeroportuario</t>
+          <t xml:space="preserve">Switch 48G PoE 4SFP+ (equivalente al modelo JL727B) /Aeroportuarios</t>
         </is>
       </c>
     </row>
@@ -18603,7 +18325,7 @@
         </is>
       </c>
       <c r="C129" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
@@ -18616,7 +18338,7 @@
         </is>
       </c>
       <c r="F129" s="0">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
@@ -18625,7 +18347,7 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Switch 12G PoE 2SFP+ (equivalente al modelo R8Q72A) /Aeroportuario</t>
+          <t xml:space="preserve">Switch 24G PoE 4SFP+(equivalente al modelo JL261A) /Aeroportuario</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18363,7 @@
         </is>
       </c>
       <c r="C130" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
@@ -18654,7 +18376,7 @@
         </is>
       </c>
       <c r="F130" s="0">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
@@ -18663,7 +18385,7 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Access Point Desktop (equivalente al modelo R3V46A) /Control de acceso</t>
+          <t xml:space="preserve">Switch 12G PoE 2SFP+ (equivalente al modelo R8Q72A) /Aeroportuario</t>
         </is>
       </c>
     </row>
@@ -18679,149 +18401,149 @@
         </is>
       </c>
       <c r="C131" s="0">
+        <v>5</v>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cajas de conmutación de computadores</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
+        </is>
+      </c>
+      <c r="F131" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access Point Desktop (equivalente al modelo R3V46A) /Control de acceso</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2563-34-LR26</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
+        </is>
+      </c>
+      <c r="C132" s="0">
         <v>6</v>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="D132" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cajas de conmutación de computadores</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
-      <c r="F131" s="0">
+      <c r="F132" s="0">
         <v>20.0</v>
       </c>
-      <c r="G131" s="0" t="inlineStr">
+      <c r="G132" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H131" s="4" t="inlineStr">
+      <c r="H132" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Access Point
 (equivalente al modelo JZ336A) /Control de Acceso</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="0" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2563-34-LR26</t>
         </is>
       </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
         </is>
       </c>
-      <c r="C132" s="0">
+      <c r="C133" s="0">
         <v>7</v>
       </c>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="D133" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cajas de conmutación de computadores</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
+      <c r="E133" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
-      <c r="F132" s="0">
+      <c r="F133" s="0">
         <v>11.0</v>
       </c>
-      <c r="G132" s="0" t="inlineStr">
+      <c r="G133" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H132" s="4" t="inlineStr">
+      <c r="H133" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Access Point
 (equivalente al modelo JZ336A) /Aeroportuarios</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="0" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2563-34-LR26</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
         </is>
       </c>
-      <c r="C133" s="0">
+      <c r="C134" s="0">
         <v>8</v>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="D134" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cajas de conmutación de computadores</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="E134" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
-      <c r="F133" s="0">
+      <c r="F134" s="0">
         <v>6.0</v>
       </c>
-      <c r="G133" s="0" t="inlineStr">
+      <c r="G134" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H133" s="4" t="inlineStr">
+      <c r="H134" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Access Point Exterior
 (equivalente al modelo R7T05A) /Control de Acceso</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2563-34-LR26</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
-        </is>
-      </c>
-      <c r="C134" s="0">
-        <v>9</v>
-      </c>
-      <c r="D134" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cajas de conmutación de computadores</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
-        </is>
-      </c>
-      <c r="F134" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G134" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Soporte anclaje para riel cielo falso plano 9/16'' Pack 10 unidades. /Aeroportuarios</t>
-        </is>
-      </c>
-    </row>
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
@@ -18834,7 +18556,7 @@
         </is>
       </c>
       <c r="C135" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
@@ -18856,7 +18578,7 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soporte anclaje para superficie sólida Pack 10 unidades. /Aeroportuarios</t>
+          <t xml:space="preserve">Soporte anclaje para riel cielo falso plano 9/16'' Pack 10 unidades. /Aeroportuarios</t>
         </is>
       </c>
     </row>
@@ -18872,110 +18594,110 @@
         </is>
       </c>
       <c r="C136" s="0">
+        <v>10</v>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cajas de conmutación de computadores</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
+        </is>
+      </c>
+      <c r="F136" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soporte anclaje para superficie sólida Pack 10 unidades. /Aeroportuarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2563-34-LR26</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
+        </is>
+      </c>
+      <c r="C137" s="0">
         <v>11</v>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D137" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cajas de conmutación de computadores</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
+      <c r="E137" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
-      <c r="F136" s="0">
+      <c r="F137" s="0">
         <v>10.0</v>
       </c>
-      <c r="G136" s="0" t="inlineStr">
+      <c r="G137" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr">
+      <c r="H137" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Módulo 10G SFP+ LC LR 10km
 (equivalente al modelo J9151E) /Control de Acceso</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="0" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2563-34-LR26</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B138" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
         </is>
       </c>
-      <c r="C137" s="0">
+      <c r="C138" s="0">
         <v>12</v>
       </c>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="D138" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cajas de conmutación de computadores</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="E138" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
-      <c r="F137" s="0">
+      <c r="F138" s="0">
         <v>10.0</v>
       </c>
-      <c r="G137" s="0" t="inlineStr">
+      <c r="G138" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H137" s="4" t="inlineStr">
+      <c r="H138" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Módulo FO (SM) 1G SFP LC LX 10km
 (equivalente al modelo J4859D) /Control de Acceso</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2563-34-LR26</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
-        </is>
-      </c>
-      <c r="C138" s="0">
-        <v>13</v>
-      </c>
-      <c r="D138" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cajas de conmutación de computadores</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
-        </is>
-      </c>
-      <c r="F138" s="0">
-        <v>24.0</v>
-      </c>
-      <c r="G138" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Módulo FO (SM) 1G SFP LC LX 10km (equivalente al modelo J4859D) /Aeroportuarios</t>
-        </is>
-      </c>
-    </row>
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
@@ -18988,7 +18710,7 @@
         </is>
       </c>
       <c r="C139" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -19001,7 +18723,7 @@
         </is>
       </c>
       <c r="F139" s="0">
-        <v>1.0</v>
+        <v>24.0</v>
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
@@ -19010,7 +18732,7 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipo de protección de enlaces de red frente a ataques DDoS y amenazas avanzadas, actuando directamente en el borde de la red (edge), donde se conectan los enlaces de Internet principal y de respaldo. /Control de Acceso</t>
+          <t xml:space="preserve">Módulo FO (SM) 1G SFP LC LX 10km (equivalente al modelo J4859D) /Aeroportuarios</t>
         </is>
       </c>
     </row>
@@ -19026,7 +18748,7 @@
         </is>
       </c>
       <c r="C140" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
@@ -19048,32 +18770,32 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licencia para el funcionamiento del equipo de protección de enlaces de red frente a ataques DDoS y amenazas avanzadas. /Control de Acceso</t>
+          <t xml:space="preserve">Equipo de protección de enlaces de red frente a ataques DDoS y amenazas avanzadas, actuando directamente en el borde de la red (edge), donde se conectan los enlaces de Internet principal y de respaldo. /Control de Acceso</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2785-80-LE26</t>
+          <t xml:space="preserve">2563-34-LR26</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“Servicios móviles de comunicaciones de voz y datos internet para la Municipalidad San Pedro de la Paz”</t>
+          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
         </is>
       </c>
       <c r="C141" s="0">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio telefónico local</t>
+          <t xml:space="preserve">Cajas de conmutación de computadores</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios básicos y de información pública / Telecomunicaciones / Telefonía local y de larga distancia</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
       <c r="F141" s="0">
@@ -19086,7 +18808,7 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de telecomunicaciones de acuerdo a las especificacione stécnicas y bases administrativas</t>
+          <t xml:space="preserve">Licencia para el funcionamiento del equipo de protección de enlaces de red frente a ataques DDoS y amenazas avanzadas. /Control de Acceso</t>
         </is>
       </c>
     </row>
@@ -19203,12 +18925,12 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2048-57-LP26</t>
+          <t xml:space="preserve">2785-80-LE26</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio de Software de Gestión de Mantenimiento</t>
+          <t xml:space="preserve">“Servicios móviles de comunicaciones de voz y datos internet para la Municipalidad San Pedro de la Paz”</t>
         </is>
       </c>
       <c r="C145" s="0">
@@ -19216,12 +18938,12 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de administración</t>
+          <t xml:space="preserve">Servicio telefónico local</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
+          <t xml:space="preserve">Servicios básicos y de información pública / Telecomunicaciones / Telefonía local y de larga distancia</t>
         </is>
       </c>
       <c r="F145" s="0">
@@ -19229,12 +18951,12 @@
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad no definida</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOFTWARE DE GESTION DE MANTENIMIENTO (INGRESAR PRECIO TOTAL DEL CONVENIO, SEGUN ANEXO ECONOMICO N°1)</t>
+          <t xml:space="preserve">Servicios de telecomunicaciones de acuerdo a las especificacione stécnicas y bases administrativas</t>
         </is>
       </c>
     </row>
@@ -20436,12 +20158,12 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">726931-1-LE26</t>
+          <t xml:space="preserve">948354-135-LP26</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLATAFORMA INTEGRAL ALUMNI Y EMPLEABILIDAD UTA</t>
+          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE UNA CABINA SANITARIA CON EQUIPO MAMÓGRAFO PARA USO DE MAMOGRAFÍA DIGITALIZADA PORTÁTIL PARA EL HOSPITAL DIPRECA</t>
         </is>
       </c>
       <c r="C177" s="0">
@@ -20449,37 +20171,37 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de desarrollo de plataforma Web</t>
+          <t xml:space="preserve">Equipo para radiografías mamográficas</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Productos para imágenes y de medicina nuclear / Artículos radiográficos de diagnóstico médico</t>
         </is>
       </c>
       <c r="F177" s="0">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Mes</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de servicio de plataforma integral ALUMNI y empleabilidad para estudiantes, egresados y titulados de la Universidad de Tarapacá, por un periodo de 24 meses de duración.</t>
+          <t xml:space="preserve">Servicio de Arriendo de una Cabina Sanitaria con Equipo Mamógrafo para Uso de Mamografía Digitalizada Portátil</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">948354-135-LP26</t>
+          <t xml:space="preserve">726931-1-LE26</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE ARRIENDO DE UNA CABINA SANITARIA CON EQUIPO MAMÓGRAFO PARA USO DE MAMOGRAFÍA DIGITALIZADA PORTÁTIL PARA EL HOSPITAL DIPRECA</t>
+          <t xml:space="preserve">PLATAFORMA INTEGRAL ALUMNI Y EMPLEABILIDAD UTA</t>
         </is>
       </c>
       <c r="C178" s="0">
@@ -20487,25 +20209,25 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipo para radiografías mamográficas</t>
+          <t xml:space="preserve">Software de desarrollo de plataforma Web</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento y suministros médicos / Productos para imágenes y de medicina nuclear / Artículos radiográficos de diagnóstico médico</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
         </is>
       </c>
       <c r="F178" s="0">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de Arriendo de una Cabina Sanitaria con Equipo Mamógrafo para Uso de Mamografía Digitalizada Portátil</t>
+          <t xml:space="preserve">Adquisición de servicio de plataforma integral ALUMNI y empleabilidad para estudiantes, egresados y titulados de la Universidad de Tarapacá, por un periodo de 24 meses de duración.</t>
         </is>
       </c>
     </row>
@@ -20816,12 +20538,12 @@
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3970-8-LE26</t>
+          <t xml:space="preserve">1575-15-LE26</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">01 SISTEMA DE EVIDENCIA DIGITAL Y ACCESORIOS OS9</t>
+          <t xml:space="preserve">MANTENCION DE EQUIPOS INFORMATICOS</t>
         </is>
       </c>
       <c r="C187" s="0">
@@ -20829,12 +20551,12 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adaptadores de telefonía o hardware</t>
+          <t xml:space="preserve">Fotocopiadoras</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Componentes para tecnología de la información, difusión o telecomunicaciones / Módulos, interfaces, procesadores y placas de sistema</t>
+          <t xml:space="preserve">Equipos, accesorios y suministros de oficina / Maquinarias, suministros y accesorios de oficina / Multicopistas, fotocopiadoras, fax y multifuncionales</t>
         </is>
       </c>
       <c r="F187" s="0">
@@ -20847,19 +20569,19 @@
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN 01 SISTEMA DE EVIDENCIA DIGITAL Y ACCESORIOS PARA EL DEPARTAMENTO INVESTIGACIÓN DE ORGANIZACIONES CRIMINALES O.S.9</t>
+          <t xml:space="preserve">“CONTRATO DE SUMINISTRO DE MANTENCION Y REPARACION DE IMPRESORAS, ESCANERS, PLOTTERS, PROYECTORES PARA JARDINES INFANTILES Y OFICINAS DE LA REGIÓN DE O´HIGGINS</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5394-22-LE26</t>
+          <t xml:space="preserve">3970-8-LE26</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE CONSULTORÍA DE CIBERSEGURIDAD UMAG</t>
+          <t xml:space="preserve">01 SISTEMA DE EVIDENCIA DIGITAL Y ACCESORIOS OS9</t>
         </is>
       </c>
       <c r="C188" s="0">
@@ -20867,12 +20589,12 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asesorías Informáticas</t>
+          <t xml:space="preserve">Adaptadores de telefonía o hardware</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Consultorías o asesorías en gestión empresarial / Servicios de consultoría en gestión de empresas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Componentes para tecnología de la información, difusión o telecomunicaciones / Módulos, interfaces, procesadores y placas de sistema</t>
         </is>
       </c>
       <c r="F188" s="0">
@@ -20880,24 +20602,24 @@
       </c>
       <c r="G188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINEA GLOBAL: CONTRATACIÓN DE SERVICIOS DE CONSULTORÍA DE CIBERSEGURIDAD PARA EL FORTALECIMIENTO DE LA GESTIÓN ADMINISTRATIVA Y TRANSFORMACION DIGITAL INSTITUCIONAL DE LA UNIVERSIDAD DE MAGALLANES.</t>
+          <t xml:space="preserve">ADQUISICIÓN 01 SISTEMA DE EVIDENCIA DIGITAL Y ACCESORIOS PARA EL DEPARTAMENTO INVESTIGACIÓN DE ORGANIZACIONES CRIMINALES O.S.9</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575-15-LE26</t>
+          <t xml:space="preserve">5394-22-LE26</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANTENCION DE EQUIPOS INFORMATICOS</t>
+          <t xml:space="preserve">SERVICIO DE CONSULTORÍA DE CIBERSEGURIDAD UMAG</t>
         </is>
       </c>
       <c r="C189" s="0">
@@ -20905,12 +20627,12 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fotocopiadoras</t>
+          <t xml:space="preserve">Asesorías Informáticas</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipos, accesorios y suministros de oficina / Maquinarias, suministros y accesorios de oficina / Multicopistas, fotocopiadoras, fax y multifuncionales</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Consultorías o asesorías en gestión empresarial / Servicios de consultoría en gestión de empresas</t>
         </is>
       </c>
       <c r="F189" s="0">
@@ -20918,12 +20640,12 @@
       </c>
       <c r="G189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“CONTRATO DE SUMINISTRO DE MANTENCION Y REPARACION DE IMPRESORAS, ESCANERS, PLOTTERS, PROYECTORES PARA JARDINES INFANTILES Y OFICINAS DE LA REGIÓN DE O´HIGGINS</t>
+          <t xml:space="preserve">LINEA GLOBAL: CONTRATACIÓN DE SERVICIOS DE CONSULTORÍA DE CIBERSEGURIDAD PARA EL FORTALECIMIENTO DE LA GESTIÓN ADMINISTRATIVA Y TRANSFORMACION DIGITAL INSTITUCIONAL DE LA UNIVERSIDAD DE MAGALLANES.</t>
         </is>
       </c>
     </row>
@@ -21432,12 +21154,12 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4051-16-LP26</t>
+          <t xml:space="preserve">591-26-LP26</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO ADMINISTRADO DE INTERNET RED DE DATOS Y</t>
+          <t xml:space="preserve">PLATAFORMA DE OBSERVABILIDAD AVANZADA MULTICLOUD PARA FONASA.</t>
         </is>
       </c>
       <c r="C203" s="0">
@@ -21445,12 +21167,12 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proveedores de servicio de Internet (ISP)</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Servicios para internet</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F203" s="0">
@@ -21463,19 +21185,19 @@
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Municipio requiere contratar el Servicio Administrado de Internet, Red de Datos y Telefonía IP para la Ilustre Municipalidad de Ollagüe y que implica la ejecución de diseños preliminares, adquisición de materiales, instalación, montaje, configuración y</t>
+          <t xml:space="preserve">FONASA requiere fortalecer sus capacidades de monitoreo y diagnóstico de sus plataformas críticas. Actualmente, opera bajo un modelo de Nube Híbrida y Multicloud, con servicios desplegados en Amazon Web Services (AWS), Oracle Cloud Infrastructure (OCI) y</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">591-26-LP26</t>
+          <t xml:space="preserve">885-84-LE26</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLATAFORMA DE OBSERVABILIDAD AVANZADA MULTICLOUD PARA FONASA.</t>
+          <t xml:space="preserve">Soporte mantención y monitoreo plataforma legacy IBM Spectrum para la Contraloría General de la República</t>
         </is>
       </c>
       <c r="C204" s="0">
@@ -21483,12 +21205,12 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Mantenimiento y soporte de hardware</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
         </is>
       </c>
       <c r="F204" s="0">
@@ -21496,24 +21218,24 @@
       </c>
       <c r="G204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FONASA requiere fortalecer sus capacidades de monitoreo y diagnóstico de sus plataformas críticas. Actualmente, opera bajo un modelo de Nube Híbrida y Multicloud, con servicios desplegados en Amazon Web Services (AWS), Oracle Cloud Infrastructure (OCI) y</t>
+          <t xml:space="preserve">Servicio de soporte, mantención y monitoreo de la plataforma legacy IBM Spectrum, por un periodo de 12 meses.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">885-84-LE26</t>
+          <t xml:space="preserve">4051-16-LP26</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soporte mantención y monitoreo plataforma legacy IBM Spectrum para la Contraloría General de la República</t>
+          <t xml:space="preserve">SERVICIO ADMINISTRADO DE INTERNET RED DE DATOS Y</t>
         </is>
       </c>
       <c r="C205" s="0">
@@ -21521,12 +21243,12 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenimiento y soporte de hardware</t>
+          <t xml:space="preserve">Proveedores de servicio de Internet (ISP)</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Servicios para internet</t>
         </is>
       </c>
       <c r="F205" s="0">
@@ -21534,12 +21256,12 @@
       </c>
       <c r="G205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de soporte, mantención y monitoreo de la plataforma legacy IBM Spectrum, por un periodo de 12 meses.</t>
+          <t xml:space="preserve">El Municipio requiere contratar el Servicio Administrado de Internet, Red de Datos y Telefonía IP para la Ilustre Municipalidad de Ollagüe y que implica la ejecución de diseños preliminares, adquisición de materiales, instalación, montaje, configuración y</t>
         </is>
       </c>
     </row>
@@ -23627,12 +23349,12 @@
     <row r="260">
       <c r="A260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-81-LP26</t>
+          <t xml:space="preserve">5482-101-LR26</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGF - PLATAFORMA INGLES</t>
+          <t xml:space="preserve">Plataforma IA para video y seguridad urbana</t>
         </is>
       </c>
       <c r="C260" s="0">
@@ -23640,12 +23362,12 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enseñanza conversacional de idiomas extranjeros</t>
+          <t xml:space="preserve">Software de desarrollo de plataforma Web</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Sistemas educativos complementarios / Escuelas de idiomas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
         </is>
       </c>
       <c r="F260" s="0">
@@ -23658,57 +23380,57 @@
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DE SERVICIO DE PLATAFORMA INTEGRAL DE CAPACITACIÓN EN IDIOMA INGLÉS (MODALIDAD E-LEARNING CON TUTORIA)</t>
+          <t xml:space="preserve">Setup o configuración inicial del servicio e instalación</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3447-145-LR26</t>
+          <t xml:space="preserve">5482-101-LR26</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición e Implementación Plataforma Integral</t>
+          <t xml:space="preserve">Plataforma IA para video y seguridad urbana</t>
         </is>
       </c>
       <c r="C261" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de programación de sistemas operativos</t>
+          <t xml:space="preserve">Software de desarrollo de plataforma Web</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Ingeniería en computación e informática</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
         </is>
       </c>
       <c r="F261" s="0">
-        <v>1.0</v>
+        <v>26.0</v>
       </c>
       <c r="G261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Mes</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición e Implementación de Plataforma Integral de Gestión Municipal y Servicios Traspasados para la Municipalidad de Alto Hospicio. (INGRESAR VALOR TOTAL NETO)</t>
+          <t xml:space="preserve">Servicio mensual (Operación)</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5482-101-LR26</t>
+          <t xml:space="preserve">29-81-LP26</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plataforma IA para video y seguridad urbana</t>
+          <t xml:space="preserve">AGF - PLATAFORMA INGLES</t>
         </is>
       </c>
       <c r="C262" s="0">
@@ -23716,12 +23438,12 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de desarrollo de plataforma Web</t>
+          <t xml:space="preserve">Enseñanza conversacional de idiomas extranjeros</t>
         </is>
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
+          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Sistemas educativos complementarios / Escuelas de idiomas</t>
         </is>
       </c>
       <c r="F262" s="0">
@@ -23734,45 +23456,45 @@
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Setup o configuración inicial del servicio e instalación</t>
+          <t xml:space="preserve">CONTRATACIÓN DE SERVICIO DE PLATAFORMA INTEGRAL DE CAPACITACIÓN EN IDIOMA INGLÉS (MODALIDAD E-LEARNING CON TUTORIA)</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5482-101-LR26</t>
+          <t xml:space="preserve">3447-145-LR26</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plataforma IA para video y seguridad urbana</t>
+          <t xml:space="preserve">Adquisición e Implementación Plataforma Integral</t>
         </is>
       </c>
       <c r="C263" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de desarrollo de plataforma Web</t>
+          <t xml:space="preserve">Servicios de programación de sistemas operativos</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Ingeniería en computación e informática</t>
         </is>
       </c>
       <c r="F263" s="0">
-        <v>26.0</v>
+        <v>1.0</v>
       </c>
       <c r="G263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio mensual (Operación)</t>
+          <t xml:space="preserve">Adquisición e Implementación de Plataforma Integral de Gestión Municipal y Servicios Traspasados para la Municipalidad de Alto Hospicio. (INGRESAR VALOR TOTAL NETO)</t>
         </is>
       </c>
     </row>
